--- a/docs/examples/demo-cko-2_FERG.xlsx
+++ b/docs/examples/demo-cko-2_FERG.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C440"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -517,7 +517,7 @@
         <v>[R_01_闪光]</v>
       </c>
       <c r="C11" t="str">
-        <v>白色光: 0.01 cd·s/m²</v>
+        <v>b白色光:0.01cd.m-2,5ms</v>
       </c>
     </row>
     <row r="12">
@@ -528,7 +528,7 @@
         <v>[R_01_闪光背景]</v>
       </c>
       <c r="C12" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="13">
@@ -539,7 +539,7 @@
         <v>[R_01_采样]</v>
       </c>
       <c r="C13" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="14">
@@ -550,7 +550,7 @@
         <v>[R_01_分析时间]</v>
       </c>
       <c r="C14" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="15">
@@ -572,7 +572,7 @@
         <v>[R_01_详细数据(uv)]</v>
       </c>
       <c r="C16" t="str">
-        <v>-1.07,-1.99,-2.66,-2.98,-2.91,-2.46,-1.69,-0.7,0.38,1.41,2.26,2.81,3,2.79,2.22,1.36,0.33,-0.75,-1.74,-2.49,-2.92,-2.97,-2.63,-1.95,-1.02,0.05,1.11,2.03,2.68,2.98,2.89,2.42,1.64,0.63,-0.45,-1.48,-2.32,-2.87,-3.04,-2.83,-2.25,-1.4,-0.37,0.69,1.64,2.36,2.74,2.73,2.33,1.58,0.57,-0.57,-1.71,-2.7,-3.44,-3.85,-3.87,-3.54,-2.92,-2.11,-1.25,-0.47,0.08,0.29,0.1,-0.51,-1.52,-2.85,-4.39,-6,-7.55,-8.9,-9.97,-10.71,-11.11,-11.22,-11.14,-10.99,-10.92,-11.04,-11.49,-12.34,-13.61,-15.29,-17.31,-19.56,-21.89,-24.16,-26.22,-27.97,-29.33,-30.27,-30.81,-31.02,-31.02,-30.92,-30.85,-30.93,-31.23,-31.79,-32.61,-33.61,-34.69,-35.71,-36.53,-37,-36.99,-36.41,-35.24,-33.48,-31.2,-28.5,-25.51,-22.37,-19.22,-16.15,-13.25,-10.51,-7.92,-5.39,-2.81,-0.06,3.01,6.5,10.5,15.04,20.12,25.66,31.57,37.69,43.89,50.02,55.94,61.58,66.9,71.91,76.66,81.27,85.84,90.52,95.43,100.66,106.27,112.25,118.56,125.11,131.77,138.39,144.83,150.96,156.68,161.94,166.73,171.12,175.17,179.03,182.81,186.65,190.65,194.88,199.36,204.05,208.88,213.72,218.44,222.88,226.91,230.42,233.35,235.68,237.44,238.73,239.65,240.33,240.92,241.53,242.24,243.1,244.09,245.16,246.19,247.08,247.67,247.82,247.45,246.46,244.85,242.64,239.92,236.8,233.41,229.92,226.46,223.13,219.99,217.06,214.31,211.66,209,206.18,203.1,199.63,195.7,191.29,186.42,181.15,175.6,169.91,164.24,158.72,153.48,148.59,144.09,139.96,136.13,132.49,128.92,125.29,121.47,117.37,112.95,108.21,103.2,98.03,92.8,87.68,82.81,78.29,74.23,70.66,67.57,64.89,62.53,60.36,58.23,56.01,53.6,50.93,47.97,44.75,41.36,37.91,34.54,31.37,28.54,26.14,24.22,22.78,21.76,21.07,20.58,20.16,19.65,18.94,17.95,16.64,15.02,13.15,11.14,9.11,7.21,5.56,4.27,3.4,2.97,2.93,3.21,3.68,4.2,4.64,4.87,4.78,4.34,3.53,2.41,1.08,-0.35,-1.74,-2.95,-3.86,-4.4,-4.55,-4.3,-3.75,-2.99,-2.16,-1.41,-0.85,-0.61,-0.74,-1.25,-2.12,-3.26,-4.55,-5.85,-7.04,-7.97,-8.56,-8.77,-8.6,-8.11,-7.38,-6.55,-5.76,-5.15,-4.82,-4.86,-5.3,-6.11,-7.23,-8.54,-9.91,-11.2,-12.29,-13.06,-13.47,-13.48,-13.16,-12.57,-11.84,-11.11,-10.52,-10.18,-10.2,-10.6,-11.4,-12.52,-13.88,-15.34,-16.77,-18.02,-18.99,-19.59,-19.81,-19.67,-19.24,-18.62,-17.96,-17.39,-17.05,-17.03,-17.4,-18.15,-19.26,-20.63,-22.14,-23.65,-25.02,-26.14,-26.92,-27.3,-27.31,-26.99,-26.46,-25.83,-25.25,-24.85,-24.75,-25.01,-25.67,-26.68,-27.99,-29.47,-30.99,-32.41,-33.6,-34.46,-34.93,-35.02,-34.75,-34.23,-33.56,-32.9,-32.38,-32.11,-32.19,-32.65,-33.48,-34.62,-35.97,-37.4,-38.76,-39.92,-40.77,-41.25,-41.32,-41.03,-40.43,-39.66,-38.83,-38.1,-37.6,-37.4,-37.58,-38.14,-39.02,-40.15,-41.38,-42.59,-43.64,-44.4,-44.8,-44.79,-44.4,-43.68,-42.74,-41.7,-40.72,-39.91,-39.4,-39.25,-39.47,-40.04,-40.88,-41.87,-42.88,-43.76,-44.4,-44.68,-44.57,-44.06,-43.21,-42.09,-40.85,-39.61,-38.52,-37.69,-37.2,-37.1,-37.36,-37.91,-38.66,-39.47,-40.2,-40.72,-40.92,-40.74,-40.15,-39.2,-37.97,-36.57,-35.14,-33.82,-32.73,-31.98,-31.6,-31.6,-31.93,-32.49,-33.16,-33.79,-34.26,-34.44,-34.26,-33.68,-32.73,-31.47,-30.01,-28.48,-27.03,-25.78,-24.85,-24.28,-24.11,-24.29,-24.74,-25.35,-25.96,-26.46,-26.7,-26.61,-26.13,-25.27,-24.09,-22.67,-21.15,-19.66,-18.35,-17.33,-16.67,-16.4,-16.51,-16.92,-17.53,-18.2,-18.79,-19.17,-19.23,-18.93,-18.24,-17.2,-15.9,-14.47,-13.02,-11.72,-10.68,-9.98,-9.68,-9.76,-10.17</v>
+        <v>-7.48,-5.59,-3.66,-1.84,-0.27,0.93,1.66,1.87,1.54,0.71,-0.55,-2.12,-3.88,-5.66,-7.32,-8.72,-9.74,-10.29,-10.34,-9.88,-8.97,-7.68,-6.14,-4.49,-2.87,-1.44,-0.33,0.36,0.53,0.18,-0.69,-2.02,-3.71,-5.62,-7.64,-9.59,-11.35,-12.72,-13.7,-14.13,-14.08,-13.49,-12.54,-11.12,-9.64,-8.13,-6.72,-5.44,-4.69,-4.23,-4.6,-5.23,-6.3,-8.03,-9.77,-11.98,-14.08,-16.24,-18.08,-19.51,-19.9,-19.52,-19.55,-19.89,-18.28,-18.21,-16.7,-15.03,-14.12,-12.28,-11.47,-12.31,-12.93,-14.4,-19.8,-22.08,-23.64,-27.41,-27.77,-30.07,-30.49,-29.75,-36.29,-33.31,-37.82,-30.32,-34.58,-32.66,-31.77,-31.15,-29.4,-24.07,-21.33,-24.42,-27.79,-20.8,-24.73,-28.02,-33.37,-33.1,-29.89,-29.39,-34.04,-32.89,-29.36,-28.49,-17.83,-13.94,-15.37,-10.61,-3.47,-1.57,-0.96,2.34,7.47,13.69,13.22,13.46,16.77,16.28,14.11,29.53,22.9,22.65,32.39,43.56,45.13,37.25,51.04,47.68,62.73,61.29,83.11,69.81,93.06,97.11,101.34,86.35,99.6,88.72,96.23,108.75,94.3,118.45,119.27,118.37,119.18,125,131.23,119.55,150.67,148.39,147.15,163.95,139.18,162.57,166.46,166.04,162.62,148.58,174.87,186.16,150.81,165.1,186.52,159.38,148.65,157.05,148.02,191.45,190.86,156.55,168.01,172.91,160.17,173.53,163.73,161.19,172.38,193.53,174.38,182.18,148.72,182.27,159.06,162.32,158.55,160.58,135.42,123.66,134.84,131.25,140.9,133.01,128.24,132.35,128.61,118.24,109.37,129.48,106.22,98.19,112.65,92.09,106.61,89.63,90.71,77.89,65.75,75.25,72.69,70.86,62.25,57.59,57.51,47.23,53.24,54.23,43.07,52.33,44.75,47.67,38.43,35.06,30.85,33.51,22.85,24.09,16.76,12.81,8.83,8.8,6.88,7.96,1.94,5.22,4.51,4.98,7.29,5.16,7.75,5.29,7.17,6.25,4.66,2.31,1.3,-0.61,-3.77,-5.71,-8.72,-9.93,-11.09,-12.48,-13.08,-12.57,-11.19,-10.33,-8.51,-7.15,-5.21,-4.37,-3.18,-2.27,-1.46,-2.29,-2.51,-3.67,-5.2,-7.79,-9.18,-11.1,-12.86,-14.63,-15.23,-15.31,-15.02,-15,-13.78,-11.63,-11.19,-8.6,-6.6,-6.87,-5.22,-4.9,-5.81,-6.83,-6.75,-7.96,-10.29,-14.1,-13.95,-15.51,-19.06,-21.09,-20.37,-22.5,-21.05,-21.73,-19.77,-16.6,-17.4,-15.55,-15.58,-11.31,-11.81,-13.5,-12.41,-13.07,-14.93,-16.99,-18.99,-19.87,-23.35,-25.58,-26.75,-27.41,-29.87,-27.88,-26.81,-29.22,-29.92,-26.09,-27.45,-19.27,-19.88,-18.86,-18.05,-20.75,-20.14,-26.18,-27.44,-25.02,-25.11,-31.13,-32.36,-32.09,-32.11,-33.48,-37.38,-36.78,-33.27,-28.01,-25.01,-29.61,-23.98,-23.02,-30.08,-26.81,-21.73,-19.75,-26.32,-31.81,-28.32,-28.21,-31.77,-28.81,-38.53,-34.45,-44.69,-44.3,-31.03,-38.16,-31.53,-29.28,-33.91,-24.57,-36.92,-22.06,-23.8,-24.59,-23.12,-25.58,-35.6,-32.13,-41.08,-43.4,-38.79,-44.04,-46.28,-43.92,-43.12,-47.54,-43.05,-41.22,-37.91,-33.86,-33.15,-42.42,-35.23,-30.03,-40.4,-32.3,-38.29,-44.06,-42.33,-38.07,-47.58,-47.73,-39.77,-49.8,-48.45,-43.12,-55.23,-56.65,-53.61,-51.82,-45.8,-36.18,-33.16,-42.61,-41.41,-38.62,-38.92,-33.06,-42.07,-36.3,-40,-38.09,-46.8,-39.15,-48.93,-42.57,-42.65,-53.14,-52.84,-44.96,-44.83,-33.89,-33.54,-41.94,-30.33,-28.81,-31.67,-34.24,-27.95,-26.27,-29.45,-28.8,-29.46,-33.31,-31.08,-37.69,-42.39,-34.8,-41.05,-42.22,-30.76,-30.14,-27.25,-35.95,-33.79,-26.34,-26.59,-25.42,-25.66,-22.93,-17.88,-24.84,-25.38,-22.76,-23.92,-27.41,-25.8,-26.66,-26.63,-30.57,-30.91,-33.43,-26.68,-29.25,-26.61,-28.08,-24.69,-19.85,-15.73,-19.1,-19.13,-15.86,-18.94,-20.56,-20.85,-18.61,-21.13,-23.79,-28.59,-27.19,-30.1,-26.89,-27.31,-30.67,-27.72,-25.76,-25.29,-21.38,-19.82,-19.72,-18.46,-17.81</v>
       </c>
     </row>
     <row r="17">
@@ -583,7 +583,7 @@
         <v>[R_01_标记]</v>
       </c>
       <c r="C17" t="str">
-        <v>a: 17.4ms -55.2uv b: 36.4ms 253.5uv</v>
+        <v>a: 14.9ms -29.2uv b: 33.5ms 56.6uv</v>
       </c>
     </row>
     <row r="18">
@@ -616,7 +616,7 @@
         <v>[L_01_闪光]</v>
       </c>
       <c r="C20" t="str">
-        <v>白色光: 0.01 cd·s/m²</v>
+        <v>b白色光:0.01cd.m-2,5ms</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +627,7 @@
         <v>[L_01_闪光背景]</v>
       </c>
       <c r="C21" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="22">
@@ -638,7 +638,7 @@
         <v>[L_01_采样]</v>
       </c>
       <c r="C22" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="23">
@@ -649,7 +649,7 @@
         <v>[L_01_分析时间]</v>
       </c>
       <c r="C23" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="24">
@@ -671,7 +671,7 @@
         <v>[L_01_详细数据(uv)]</v>
       </c>
       <c r="C25" t="str">
-        <v>0.02,0.04,0.06,0.08,0.1,0.12,0.14,0.16,0.18,0.2,0.22,0.25,0.27,0.29,0.31,0.33,0.35,0.37,0.39,0.41,0.43,0.45,0.47,0.49,0.51,0.53,0.55,0.57,0.58,0.6,0.62,0.64,0.66,0.67,0.69,0.71,0.72,0.73,0.75,0.76,0.77,0.77,0.78,0.78,0.77,0.77,0.76,0.74,0.72,0.69,0.65,0.61,0.55,0.48,0.41,0.31,0.2,0.08,-0.07,-0.23,-0.42,-0.63,-0.87,-1.13,-1.43,-1.76,-2.13,-2.53,-2.98,-3.46,-3.99,-4.56,-5.17,-5.84,-6.55,-7.31,-8.11,-8.97,-9.87,-10.81,-11.8,-12.82,-13.88,-14.97,-16.09,-17.24,-18.39,-19.55,-20.72,-21.87,-23.01,-24.12,-25.2,-26.22,-27.19,-28.09,-28.91,-29.64,-30.26,-30.76,-31.14,-31.38,-31.48,-31.41,-31.18,-30.77,-30.18,-29.4,-28.42,-27.24,-25.85,-24.25,-22.45,-20.43,-18.2,-15.76,-13.12,-10.27,-7.22,-3.98,-0.54,3.07,6.85,10.8,14.91,19.17,23.57,28.09,32.74,37.5,42.36,47.31,52.34,57.45,62.61,67.83,73.1,78.4,83.74,89.09,94.45,99.82,105.18,110.53,115.86,121.17,126.44,131.67,136.86,141.99,147.06,152.06,156.98,161.82,166.56,171.21,175.75,180.18,184.49,188.67,192.71,196.61,200.36,203.95,207.38,210.63,213.7,216.59,219.29,221.79,224.08,226.17,228.04,229.69,231.12,232.33,233.31,234.06,234.58,234.86,234.92,234.74,234.32,233.68,232.81,231.72,230.4,228.87,227.12,225.17,223.01,220.66,218.12,215.39,212.5,209.43,206.21,202.85,199.34,195.7,191.94,188.07,184.1,180.04,175.9,171.69,167.42,163.09,158.72,154.33,149.91,145.47,141.04,136.6,132.19,127.79,123.42,119.09,114.8,110.56,106.38,102.26,98.21,94.23,90.33,86.52,82.78,79.14,75.59,72.13,68.77,65.51,62.34,59.28,56.32,53.46,50.7,48.05,45.49,43.04,40.68,38.42,36.26,34.19,32.21,30.33,28.53,26.82,25.19,23.64,22.17,20.78,19.45,18.2,17.02,15.9,14.84,13.84,12.9,12.01,11.17,10.38,9.64,8.94,8.28,7.65,7.07,6.51,5.99,5.5,5.04,4.6,4.18,3.79,3.41,3.06,2.72,2.39,2.08,1.79,1.5,1.22,0.96,0.7,0.45,0.2,-0.04,-0.28,-0.51,-0.75,-0.98,-1.2,-1.43,-1.66,-1.89,-2.11,-2.34,-2.58,-2.81,-3.05,-3.28,-3.53,-3.77,-4.02,-4.27,-4.53,-4.79,-5.05,-5.32,-5.6,-5.88,-6.16,-6.45,-6.74,-7.04,-7.35,-7.66,-7.97,-8.29,-8.61,-8.94,-9.28,-9.62,-9.97,-10.32,-10.67,-11.03,-11.4,-11.77,-12.15,-12.53,-12.91,-13.3,-13.69,-14.09,-14.49,-14.9,-15.31,-15.72,-16.14,-16.56,-16.98,-17.4,-17.83,-18.26,-18.69,-19.13,-19.57,-20,-20.44,-20.88,-21.32,-21.77,-22.21,-22.65,-23.09,-23.53,-23.97,-24.41,-24.85,-25.29,-25.72,-26.15,-26.58,-27.01,-27.43,-27.85,-28.27,-28.68,-29.09,-29.49,-29.89,-30.28,-30.67,-31.05,-31.42,-31.79,-32.15,-32.51,-32.85,-33.19,-33.52,-33.85,-34.16,-34.47,-34.77,-35.05,-35.33,-35.6,-35.86,-36.11,-36.35,-36.58,-36.79,-37,-37.2,-37.38,-37.55,-37.71,-37.86,-38,-38.13,-38.24,-38.34,-38.43,-38.51,-38.57,-38.63,-38.67,-38.69,-38.71,-38.71,-38.7,-38.68,-38.65,-38.6,-38.54,-38.47,-38.39,-38.29,-38.18,-38.07,-37.94,-37.79,-37.64,-37.48,-37.3,-37.12,-36.92,-36.71,-36.49,-36.27,-36.03,-35.78,-35.53,-35.26,-34.99,-34.71,-34.41,-34.12,-33.81,-33.49,-33.17,-32.84,-32.51,-32.17,-31.82,-31.47,-31.11,-30.74,-30.38,-30,-29.62,-29.24,-28.86,-28.47,-28.08,-27.68,-27.28,-26.89,-26.48,-26.08,-25.68,-25.27,-24.87,-24.46,-24.06,-23.65,-23.24,-22.84,-22.43,-22.03,-21.63,-21.23,-20.83,-20.43,-20.04,-19.65,-19.26,-18.87,-18.49,-18.11,-17.73,-17.36,-16.99,-16.63,-16.26,-15.91,-15.55,-15.21,-14.86,-14.52,-14.19,-13.86,-13.54,-13.22,-12.9,-12.59,-12.29,-11.99</v>
+        <v>2.58,6.5,11.01,15.34,18.77,20.73,20.91,19.31,16.26,12.34,8.27,4.82,2.62,2.08,3.33,6.15,10.05,14.33,18.23,21.05,22.29,21.7,19.38,15.74,11.38,7.08,3.57,1.44,1.05,2.41,5.25,9,12.96,16.37,18.55,19.07,17.77,14.84,10.72,6.11,1.76,-1.61,-3.46,-3.53,-1.85,1.2,5.02,8.87,12,13.8,13.89,12.21,8.98,4.74,0.24,-3.79,-6.68,-7.95,-7.4,-5.12,-1.66,2.43,6.42,9.56,11,10.83,9.03,5.56,1.49,-2.72,-6.38,-8.62,-9.26,-7.9,-5.54,-1.63,2.33,5.88,9.5,9.86,8.65,6.05,2.16,-1.28,-5.63,-8.82,-12.16,-13.14,-12.37,-9.84,-6.65,-2.25,2.88,2.74,4.54,0.1,0.01,-8.82,-13.24,-15.09,-15.68,-21.25,-22.4,-22.8,-20.07,-17.13,-12.53,-7.99,-5.26,-4.48,-5.62,-15.03,-11.33,-22.4,-25.02,-29.51,-21,-29.29,-22,-19.2,-11.88,-5.2,-5.58,2.19,-2.91,3.34,3.55,3.35,-0.76,1.04,-0.88,4.94,5.56,7.87,16.99,22.46,36.77,32.57,40.25,45.4,50.83,50.29,48.62,42.98,36.37,51.11,45.02,52.4,55.14,72.53,78.01,81.11,92.59,97.95,115.52,100.73,96.51,111.4,107.46,102.01,121.19,124.87,112.08,111.41,134.78,147.44,165.04,171.74,158.37,173.06,171.38,176.71,143.96,162.83,144.63,151.19,161.7,163.85,166.67,161.84,208.66,211.11,192.6,182.62,190.41,179.99,177.42,191.2,181.28,194.4,184.33,190.67,165.83,180.62,205.71,204.63,193.57,195.61,207.2,195.14,166.89,156.38,179.64,145.26,149.36,171.56,148.77,171.66,147.8,147.95,144.64,140.47,157.06,134.82,148.85,136.59,122.14,121.69,101.67,106.93,106.89,87.62,91.02,94.34,103.39,109.65,105.49,89.99,91.45,82.59,81.22,69.32,56.75,60.46,55.64,44.95,49.79,53.13,45.65,54.42,48.02,49.28,50.9,41.91,37.02,32.94,23.91,20.22,19.3,14.18,15.55,17.83,17.18,22.66,25.89,23.22,24.07,23.27,21.01,16.83,12,5.34,4.07,1.57,-0.43,1.04,3.91,7.75,11.52,14.1,16.39,17.78,15.47,13.5,8.17,4.21,-0.29,-3.89,-4.38,-4.17,-3.05,0.63,4.39,8.25,11,13.65,13.29,10.57,8.46,3.4,-1.78,-5.64,-8.08,-10.17,-8.97,-6.43,-3.48,0.23,3.85,5.49,7.9,6.76,4.43,-0.51,-3.52,-9.81,-11.91,-16.41,-15.75,-16.57,-13.74,-9.89,-7.95,-4.24,0.16,-1.64,-1.63,-3.82,-9.22,-12.43,-17.07,-22.7,-24.82,-21.84,-22.94,-19.75,-15.86,-11,-10.27,-6.83,-7.62,-6.24,-11.22,-12.4,-17.03,-20.96,-22.65,-27.97,-26.85,-21.75,-21.78,-15.53,-10.78,-8,-6.24,-9.16,-12.27,-14.78,-14.51,-18.11,-22.77,-25.96,-30.36,-22.63,-23.13,-22.65,-16.42,-7.96,-7.53,-11.55,-12.12,-6.13,-14.67,-13.8,-26.72,-25.6,-24.54,-29.05,-31.21,-31.19,-24.9,-20.93,-20.85,-15.06,-6.51,-13.06,-9.17,-18.93,-23.86,-30.69,-27.1,-37.13,-28.57,-33.06,-32.08,-27.92,-27.81,-24.32,-25.2,-15.72,-26.27,-17.62,-27.06,-40.88,-40.86,-33.69,-40.11,-42.28,-47.94,-32.45,-42.65,-34.99,-24.16,-24.23,-32.35,-20.85,-38.62,-35.92,-48.43,-53.13,-55.16,-52.31,-56.66,-50.37,-42.42,-40.01,-26.41,-36.84,-33.35,-25.61,-37.41,-38.41,-34.87,-38.82,-40.8,-49.86,-46.6,-50.76,-46,-33.08,-38.77,-33.63,-26.97,-28.51,-34.88,-30.88,-26.21,-36.42,-38.79,-40.97,-42.96,-44.51,-37.46,-35.71,-39.09,-20.08,-15.89,-20.07,-18.7,-25.36,-16.95,-32.84,-23.96,-31.38,-28.53,-41.76,-33.75,-28.22,-28.23,-20.22,-22.01,-17.14,-19.98,-12.38,-19.53,-22.82,-24.49,-30.82,-28.58,-36.4,-37.78,-32.19,-33.93,-29.61,-18.31,-12.34,-9.44,-11.94,-9.38,-12.57,-15.06,-18.29,-28.59,-26.44,-36.32,-30.46,-34.96,-26.14,-22.35,-20.87,-17.12,-11.81,-13.42,-11.06,-18.21,-19.12,-23.63,-30.99,-32.64,-33.83</v>
       </c>
     </row>
     <row r="26">
@@ -682,7 +682,7 @@
         <v>[L_01_标记]</v>
       </c>
       <c r="C26" t="str">
-        <v>a: 17.4ms -51.9uv b: 36.4ms 238.3uv</v>
+        <v>a: 14.8ms -31.7uv b: 33.6ms 74.5uv</v>
       </c>
     </row>
     <row r="27">
@@ -693,7 +693,7 @@
         <v>[R_02_名字]</v>
       </c>
       <c r="C27" t="str">
-        <v>FERG(2)_dMax</v>
+        <v>FERG(2)_dRod</v>
       </c>
     </row>
     <row r="28">
@@ -715,7 +715,7 @@
         <v>[R_02_闪光]</v>
       </c>
       <c r="C29" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.03cd.m-2,5ms</v>
       </c>
     </row>
     <row r="30">
@@ -726,7 +726,7 @@
         <v>[R_02_闪光背景]</v>
       </c>
       <c r="C30" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="31">
@@ -737,7 +737,7 @@
         <v>[R_02_采样]</v>
       </c>
       <c r="C31" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="32">
@@ -748,7 +748,7 @@
         <v>[R_02_分析时间]</v>
       </c>
       <c r="C32" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="33">
@@ -770,7 +770,7 @@
         <v>[R_02_详细数据(uv)]</v>
       </c>
       <c r="C34" t="str">
-        <v>0.02,0.04,0.06,0.08,0.1,0.12,0.14,0.16,0.18,0.2,0.22,0.24,0.26,0.28,0.3,0.32,0.34,0.35,0.37,0.39,0.4,0.41,0.42,0.43,0.43,0.44,0.43,0.42,0.41,0.39,0.36,0.32,0.27,0.2,0.12,0.02,-0.09,-0.24,-0.41,-0.61,-0.84,-1.12,-1.43,-1.8,-2.22,-2.69,-3.23,-3.84,-4.53,-5.3,-6.16,-7.11,-8.15,-9.3,-10.56,-11.94,-13.42,-15.03,-16.75,-18.59,-20.55,-22.61,-24.79,-27.06,-29.43,-31.88,-34.39,-36.95,-39.55,-42.16,-44.76,-47.33,-49.83,-52.25,-54.55,-56.7,-58.67,-60.42,-61.93,-63.16,-64.07,-64.63,-64.82,-64.59,-63.93,-62.8,-61.19,-59.06,-56.41,-53.22,-49.46,-45.15,-40.26,-34.81,-28.78,-22.2,-15.06,-7.37,0.83,9.55,18.76,28.43,38.54,49.07,59.99,71.26,82.86,94.76,106.93,119.33,131.94,144.72,157.65,170.69,183.82,197,210.21,223.43,236.61,249.75,262.81,275.76,288.59,301.26,313.76,326.06,338.13,349.96,361.51,372.78,383.73,394.34,404.59,414.47,423.94,432.99,441.6,449.75,457.43,464.61,471.27,477.42,483.02,488.08,492.57,496.49,499.84,502.61,504.79,506.38,507.4,507.82,507.68,506.96,505.68,503.85,501.49,498.6,495.2,491.32,486.97,482.17,476.95,471.33,465.33,458.98,452.31,445.35,438.11,430.64,422.95,415.08,407.05,398.89,390.63,382.29,373.9,365.49,357.07,348.66,340.3,332,323.77,315.64,307.62,299.73,291.97,284.36,276.91,269.63,262.52,255.58,248.83,242.26,235.88,229.68,223.67,217.84,212.19,206.71,201.4,196.26,191.28,186.45,181.77,177.22,172.81,168.52,164.35,160.28,156.31,152.44,148.65,144.95,141.31,137.74,134.23,130.78,127.37,124.01,120.69,117.41,114.16,110.94,107.75,104.59,101.46,98.35,95.26,92.2,89.17,86.16,83.18,80.22,77.3,74.4,71.54,68.71,65.91,63.16,60.44,57.77,55.14,52.55,50.01,47.53,45.09,42.7,40.37,38.1,35.88,33.72,31.61,29.57,27.58,25.65,23.78,21.97,20.22,18.53,16.89,15.31,13.78,12.31,10.89,9.53,8.21,6.94,5.72,4.55,3.42,2.33,1.28,0.27,-0.7,-1.64,-2.54,-3.42,-4.26,-5.08,-5.87,-6.64,-7.38,-8.11,-8.81,-9.5,-10.17,-10.83,-11.47,-12.1,-12.72,-13.33,-13.93,-14.52,-15.11,-15.69,-16.27,-16.84,-17.41,-17.97,-18.53,-19.09,-19.65,-20.21,-20.77,-21.33,-21.89,-22.45,-23.01,-23.57,-24.13,-24.69,-25.25,-25.82,-26.38,-26.95,-27.52,-28.09,-28.66,-29.23,-29.8,-30.38,-30.95,-31.53,-32.1,-32.68,-33.25,-33.82,-34.4,-34.97,-35.54,-36.11,-36.68,-37.25,-37.81,-38.37,-38.93,-39.49,-40.04,-40.59,-41.13,-41.67,-42.21,-42.74,-43.27,-43.79,-44.3,-44.81,-45.32,-45.81,-46.3,-46.78,-47.26,-47.72,-48.18,-48.63,-49.07,-49.5,-49.92,-50.33,-50.74,-51.13,-51.51,-51.88,-52.24,-52.59,-52.93,-53.25,-53.56,-53.87,-54.15,-54.43,-54.7,-54.95,-55.18,-55.41,-55.62,-55.82,-56,-56.17,-56.33,-56.47,-56.6,-56.72,-56.82,-56.9,-56.98,-57.03,-57.08,-57.1,-57.12,-57.12,-57.1,-57.07,-57.03,-56.97,-56.9,-56.81,-56.71,-56.6,-56.47,-56.33,-56.17,-56,-55.82,-55.62,-55.41,-55.19,-54.96,-54.71,-54.45,-54.18,-53.89,-53.6,-53.29,-52.97,-52.64,-52.3,-51.94,-51.58,-51.21,-50.83,-50.44,-50.04,-49.63,-49.21,-48.78,-48.34,-47.9,-47.45,-46.99,-46.53,-46.06,-45.58,-45.1,-44.61,-44.11,-43.61,-43.11,-42.6,-42.09,-41.57,-41.05,-40.53,-40,-39.47,-38.94,-38.41,-37.88,-37.34,-36.8,-36.27,-35.73,-35.19,-34.65,-34.11,-33.58,-33.04,-32.5,-31.97,-31.44,-30.91,-30.38,-29.85,-29.33,-28.81,-28.29,-27.78,-27.27,-26.76,-26.26,-25.76,-25.26,-24.77,-24.29,-23.81,-23.33,-22.86,-22.39,-21.93,-21.47,-21.02,-20.57,-20.13,-19.7,-19.27,-18.85,-18.43,-18.02,-17.62,-17.22,-16.83,-16.44,-16.06,-15.69,-15.32,-14.96,-14.61,-14.26,-13.92</v>
+        <v>-17.65,-17.35,-17.04,-16.72,-16.37,-16.01,-15.65,-15.27,-14.88,-14.49,-14.1,-13.7,-13.31,-12.92,-12.54,-12.17,-11.81,-11.46,-11.12,-10.81,-10.51,-10.23,-9.98,-9.75,-9.55,-9.37,-9.22,-9.1,-9.01,-8.95,-8.92,-8.92,-8.95,-9.01,-9.1,-9.23,-9.38,-9.56,-9.76,-9.99,-10.25,-10.53,-10.82,-11.15,-11.48,-11.84,-12.2,-12.57,-12.97,-13.36,-13.75,-14.18,-14.58,-14.97,-15.38,-15.75,-16.19,-16.52,-16.94,-17.35,-17.63,-18,-18.45,-18.83,-19.17,-19.25,-19.7,-19.64,-20.37,-20.66,-21.14,-21.11,-20.95,-21.87,-22.45,-21.92,-22.9,-22.6,-22.86,-22.74,-25.49,-23.39,-23.76,-27.26,-27.32,-25.85,-25.78,-28.22,-30.97,-29.15,-27.7,-33.4,-31.16,-34.84,-29.49,-36.97,-35.22,-32.09,-32.79,-37.84,-30.93,-38.69,-41.22,-34.27,-35.15,-31.67,-37.01,-30.92,-32.05,-39.86,-35.88,-38.1,-29.57,-32.08,-27.86,-33.19,-26.33,-25.27,-27.53,-21.74,-18.95,-15.28,-17.62,-11.61,-5.92,-6.08,-7.79,2.15,-1.56,9.14,12.74,15.92,12.38,18.16,20.03,27.16,32.64,37.75,29.53,36.25,38.09,57.56,49.6,57.98,68.26,75.98,64.72,86.46,84.43,88.38,75.4,95.29,110.38,90.73,103.52,113.97,107.16,107.08,106.76,139.54,117.66,123.12,145.8,151.53,152.62,160.57,147.22,161.4,173.37,163.38,160.25,163.09,160.27,162.39,166.34,201.67,184.79,199.22,178.13,173.13,184.37,188.58,195.51,182.26,183.77,181.36,180.82,183.18,165.06,180.97,168.03,158.25,173.46,174.88,172.28,180.54,150.55,165.62,140.44,162.98,136.66,150.67,132.66,146.73,138.74,111.75,120.01,131,111.53,107.03,100.96,92.19,102.98,96.76,86.29,76.2,76.27,78.98,70.38,70.75,60.49,47.96,47.15,41.5,47.46,44.5,40.35,39.05,27.77,23.47,24.32,17.94,19.43,14.87,17.86,10.67,11.82,9.08,10.92,4.27,5.61,2.01,3.14,2.3,2.32,-0.5,1.2,-0.21,-0.34,-0.12,-0.63,-1.12,-0.9,-1.02,-1.86,-0.61,-1.12,-0.67,-1.31,-0.27,-0.3,0.01,0.15,0.58,0.35,0.32,0.56,1.21,1.16,1.64,1.6,1.64,1.87,1.58,1.34,1.73,0.59,1.09,1.2,0.35,0.14,-0.45,-0.35,-1.38,-1.35,-3.17,-2.93,-3.28,-3.92,-4.28,-4.95,-5.87,-7.96,-8.83,-8.42,-8.95,-10.65,-12.6,-11.88,-14.21,-12.69,-14.33,-16.58,-16.73,-16.27,-16.8,-18.48,-17.89,-20.16,-22.01,-19.39,-22.79,-23.67,-21.36,-21.44,-23.54,-24.28,-22.3,-23.2,-25.55,-24.43,-21.68,-23.25,-26.13,-21.6,-26,-23.52,-23,-23.87,-22.03,-21.94,-22.53,-18.19,-17.55,-23.75,-22.15,-21.03,-22.54,-19.53,-19.9,-14.82,-19.62,-14.82,-15.04,-14.65,-11.35,-14.97,-17.43,-13.56,-10.19,-15.64,-13.41,-10.55,-16.22,-19.1,-9.68,-15.05,-8.91,-20.08,-20.13,-10.1,-11.2,-19.16,-13.97,-16.37,-13.97,-24.03,-19.16,-14.59,-16.31,-22.07,-29.83,-26.82,-24.08,-25.17,-31,-25.32,-32.78,-25.78,-38.09,-38.59,-36.82,-33.11,-41.42,-30.39,-37.88,-42.05,-33.72,-46.51,-40.02,-33.19,-39.33,-34.84,-47.64,-45.59,-44.44,-50.58,-50.34,-46.13,-47.88,-37.25,-51.21,-52.74,-40.26,-43.56,-41.5,-47.87,-47.36,-50.08,-48.42,-34,-36.6,-36.06,-32.66,-33.22,-30.12,-41.91,-31.42,-38.47,-39.22,-32.16,-41.79,-38.34,-32.11,-33.23,-27.91,-32.29,-32.88,-31.44,-22.64,-22.31,-18.68,-19.46,-24.79,-24.03,-19.05,-17.06,-20.14,-26.88,-20.57,-13.51,-25.95,-20.67,-12.58,-11.22,-23.44,-14.02,-13.54,-22.7,-23.47,-12.41,-21.93,-13.67,-11.68,-22.13,-21.97,-17.74,-22.75,-16.42,-15.74,-16.17,-17.04,-19.48,-21.68,-25.17,-23.28,-25.17,-27.16,-22.65,-26.18,-20.05,-24.89,-20.61,-20.87,-24.56,-24.76,-23.17,-22.27,-25.24,-25.85,-28.77,-25.6,-26.42,-26.1,-23.07,-23.54,-20.83,-23.45,-23.69,-20.85,-21.13,-22.03,-22.64,-21.84,-16.25,-15.97,-18.73,-15.98,-13.69,-15.5</v>
       </c>
     </row>
     <row r="35">
@@ -781,7 +781,7 @@
         <v>[R_02_标记]</v>
       </c>
       <c r="C35" t="str">
-        <v>a: 19.4ms -110.5uv b: 40.4ms 494.0uv</v>
+        <v>a: 17.0ms -29.0uv b: 37.6ms 122.2uv</v>
       </c>
     </row>
     <row r="36">
@@ -792,7 +792,7 @@
         <v>[L_02_名字]</v>
       </c>
       <c r="C36" t="str">
-        <v>FERG(2)_dMax</v>
+        <v>FERG(2)_dRod</v>
       </c>
     </row>
     <row r="37">
@@ -814,7 +814,7 @@
         <v>[L_02_闪光]</v>
       </c>
       <c r="C38" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.03cd.m-2,5ms</v>
       </c>
     </row>
     <row r="39">
@@ -825,7 +825,7 @@
         <v>[L_02_闪光背景]</v>
       </c>
       <c r="C39" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="40">
@@ -836,7 +836,7 @@
         <v>[L_02_采样]</v>
       </c>
       <c r="C40" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="41">
@@ -847,7 +847,7 @@
         <v>[L_02_分析时间]</v>
       </c>
       <c r="C41" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="42">
@@ -869,7 +869,7 @@
         <v>[L_02_详细数据(uv)]</v>
       </c>
       <c r="C43" t="str">
-        <v>1.1,2.05,2.71,2.99,2.85,2.31,1.45,0.38,-0.74,-1.76,-2.53,-2.95,-2.95,-2.54,-1.77,-0.76,0.36,1.42,2.29,2.83,2.97,2.69,2.02,1.06,-0.06,-1.18,-2.15,-2.84,-3.16,-3.07,-2.58,-1.77,-0.77,0.27,1.2,1.86,2.15,2.01,1.42,0.45,-0.8,-2.2,-3.59,-4.82,-5.78,-6.4,-6.65,-6.59,-6.31,-5.95,-5.67,-5.62,-5.96,-6.77,-8.1,-9.94,-12.21,-14.81,-17.56,-20.33,-22.97,-25.35,-27.43,-29.18,-30.66,-31.97,-33.23,-34.58,-36.17,-38.08,-40.39,-43.08,-46.11,-49.34,-52.62,-55.76,-58.59,-60.93,-62.65,-63.7,-64.04,-63.73,-62.86,-61.54,-59.91,-58.09,-56.16,-54.16,-52.08,-49.84,-47.34,-44.42,-40.92,-36.68,-31.59,-25.58,-18.62,-10.77,-2.13,7.15,16.9,26.93,37.1,47.28,57.41,67.47,77.51,87.61,97.91,108.53,119.58,131.15,143.27,155.91,168.98,182.37,195.9,209.38,222.64,235.54,247.97,259.87,271.28,282.24,292.88,303.32,313.69,324.11,334.66,345.35,356.15,366.96,377.65,388.04,397.96,407.25,415.77,423.45,430.26,436.25,441.5,446.15,450.33,454.18,457.83,461.34,464.73,467.95,470.93,473.52,475.57,476.92,477.46,477.08,475.76,473.52,470.44,466.66,462.33,457.64,452.75,447.79,442.84,437.93,433.03,428.06,422.9,417.43,411.51,405.04,397.98,390.33,382.14,373.54,364.67,355.71,346.85,338.24,330.01,322.21,314.85,307.88,301.2,294.68,288.16,281.53,274.68,267.56,260.18,252.58,244.89,237.25,229.82,222.75,216.17,210.16,204.74,199.89,195.5,191.44,187.56,183.7,179.7,175.48,170.97,166.19,161.2,156.11,151.06,146.2,141.67,137.57,133.97,130.86,128.17,125.81,123.63,121.46,119.15,116.57,113.63,110.31,106.63,102.68,98.59,94.51,90.59,86.97,83.74,80.96,78.61,76.62,74.87,73.22,71.5,69.58,67.35,64.74,61.74,58.42,54.87,51.24,47.69,44.36,41.4,38.87,36.81,35.2,33.93,32.89,31.91,30.86,29.58,27.99,26.04,23.73,21.14,18.39,15.63,13,10.66,8.72,7.23,6.22,5.62,5.34,5.22,5.12,4.88,4.36,3.5,2.26,0.66,-1.2,-3.2,-5.19,-7.01,-8.53,-9.65,-10.33,-10.58,-10.46,-10.1,-9.65,-9.27,-9.1,-9.26,-9.81,-10.77,-12.08,-13.65,-15.33,-16.97,-18.42,-19.56,-20.29,-20.6,-20.52,-20.13,-19.56,-18.97,-18.51,-18.32,-18.49,-19.09,-20.09,-21.43,-23,-24.64,-26.2,-27.53,-28.52,-29.1,-29.26,-29.06,-28.6,-28,-27.44,-27.06,-26.99,-27.32,-28.06,-29.2,-30.64,-32.26,-33.9,-35.41,-36.65,-37.52,-37.97,-38.01,-37.71,-37.19,-36.58,-36.06,-35.76,-35.8,-36.24,-37.1,-38.32,-39.8,-41.41,-42.99,-44.39,-45.47,-46.15,-46.41,-46.27,-45.82,-45.18,-44.51,-43.97,-43.68,-43.76,-44.25,-45.13,-46.35,-47.79,-49.29,-50.71,-51.89,-52.73,-53.14,-53.13,-52.74,-52.07,-51.25,-50.45,-49.82,-49.49,-49.53,-49.98,-50.81,-51.94,-53.24,-54.55,-55.72,-56.6,-57.11,-57.19,-56.85,-56.15,-55.21,-54.18,-53.21,-52.45,-52.02,-51.98,-52.34,-53.06,-54.04,-55.14,-56.2,-57.07,-57.62,-57.76,-57.47,-56.78,-55.76,-54.55,-53.3,-52.16,-51.27,-50.74,-50.61,-50.88,-51.47,-52.29,-53.17,-53.97,-54.53,-54.75,-54.54,-53.91,-52.9,-51.6,-50.16,-48.73,-47.46,-46.49,-45.9,-45.72,-45.92,-46.43,-47.11,-47.81,-48.38,-48.68,-48.61,-48.11,-47.2,-45.93,-44.43,-42.84,-41.32,-40.01,-39.03,-38.46,-38.29,-38.5,-38.98,-39.58,-40.17,-40.58,-40.68,-40.39,-39.68,-38.57,-37.16,-35.55,-33.91,-32.39,-31.13,-30.24,-29.77,-29.71,-29.99,-30.5,-31.1,-31.63,-31.95,-31.93,-31.5,-30.66,-29.45,-27.97,-26.35,-24.76,-23.33,-22.22,-21.49,-21.19,-21.29,-21.7,-22.31,-22.96,-23.48,-23.76,-23.67,-23.17,-22.26,-21.02,-19.55,-17.99,-16.51,-15.25,-14.33,-13.83,-13.74,-14.04,-14.62,-15.34,-16.06,-16.61,-16.86,-16.74,-16.2,-15.27,-14.03,-12.61</v>
+        <v>6.71,7.66,8.57,9.43,10.24,10.99,11.69,12.33,12.91,13.44,13.89,14.29,14.62,14.89,15.09,15.23,15.3,15.31,15.25,15.14,14.96,14.72,14.42,14.07,13.66,13.2,12.69,12.14,11.54,10.89,10.21,9.5,8.75,7.97,7.17,6.35,5.5,4.64,3.77,2.9,2.01,1.12,0.24,-0.64,-1.51,-2.37,-3.22,-4.05,-4.86,-5.64,-6.4,-7.13,-7.84,-8.52,-9.16,-9.76,-10.33,-10.87,-11.35,-11.83,-12.24,-12.62,-12.95,-13.29,-13.52,-13.75,-13.91,-14.02,-14.23,-14.35,-14.32,-14.29,-14.4,-14.4,-14.28,-14.19,-14.03,-14.12,-14.38,-14.24,-13.84,-13.86,-13.56,-13.64,-13.2,-13.29,-14.38,-13.88,-14.73,-14.37,-14.72,-13.49,-15.09,-14.1,-15.08,-13.42,-16.72,-15.26,-16.26,-18.05,-18.32,-18.64,-15.23,-21.53,-19.26,-20.14,-16.73,-23.16,-16.83,-24.04,-19.12,-24.7,-19.29,-21.42,-19.97,-24.3,-23.13,-22.34,-19.05,-17.74,-13.64,-13.96,-14.91,-18.25,-15.48,-19.12,-10.95,-6.66,-5.45,-0.67,0.78,-0.79,4.81,2.92,3.77,5.09,12.58,16.37,27.43,23.97,25.4,28.69,37.37,35.95,45.39,48.01,42.03,58.81,63.2,68.52,61.4,69.61,77.74,72.81,93.22,96.56,94.9,102.37,108.1,103.93,113.9,97.3,121.06,125.46,132.45,139.1,121.61,131.34,135.67,133.54,130.81,141.18,135.26,137.75,145.83,146.05,145.31,174.1,181.9,185.43,186.45,161.56,184.86,169.48,178.53,191.93,171.78,164.34,171.5,188.21,165.42,158.32,192.91,160.91,181.98,186.23,171.06,186.72,171.1,163.14,177.44,185.96,168.15,182.22,166.77,164.98,165.9,155.6,161.69,160.78,143.41,143.8,140.24,152.57,143.18,128.42,129.9,122.45,123.11,125.36,128.75,112.61,107.44,98.96,98.47,109.09,107.4,86.84,101.97,100.68,81.23,81.35,82.89,76.7,81.67,73.37,67.21,65.17,68.27,68.26,70.32,63.19,60.75,55.87,54.82,61.35,53.52,54.97,52.74,52.65,49.66,44.45,44.88,44.76,43.32,42.73,39.52,37.57,38.43,36.55,34.72,33.19,32.31,32.32,31.22,28.14,28.2,26.19,24.74,22.55,21.15,19.94,18.42,17.86,15.91,14.34,13.57,12.61,10.6,9.3,7.51,6.58,5.35,4.26,2.41,0.32,-0.28,-2.15,-2.83,-4.69,-5.89,-6.96,-7.76,-8.37,-9.89,-11.38,-12.62,-12.99,-13.81,-15.42,-14.61,-16.43,-16.22,-17.46,-18.03,-17.2,-18.4,-18.18,-18.08,-19.49,-19.81,-20.02,-17.99,-19.24,-19.24,-18.18,-18.59,-17.74,-17.29,-17.69,-17.16,-13.45,-12.35,-13.5,-12.16,-11.32,-9.71,-7.73,-6.87,-8.58,-4.63,-8.05,-2.97,-2.15,-4.7,1.18,0.21,1.91,-0.05,3.02,0.63,2.32,3.6,6.16,7.27,4.58,7.93,6.19,9.94,11.32,12.69,11.42,9.93,12.12,15.19,14.73,14.24,10.46,10.03,13.13,8.03,14.82,15.11,13.89,10.35,11.56,4.83,6.11,8.25,7.89,-0.18,1.34,-1.05,-2.04,-3.47,1.16,-8.43,-3.92,-6.65,-2.91,-12.28,-6.57,-7.22,-17.07,-19.11,-11.04,-19.32,-19.26,-18.16,-22.43,-25.1,-28.38,-24.14,-30.89,-35.14,-27.12,-26.75,-32.18,-34.05,-38.06,-43.07,-32.21,-42.8,-37.08,-46.78,-34.26,-37.76,-47.32,-47.22,-39.21,-48.59,-43.42,-41.77,-44.3,-49.3,-32.94,-41.08,-31.66,-38.47,-41.22,-44.3,-30,-36.57,-41.55,-37.01,-30.43,-38.92,-32.78,-33.98,-35.23,-29.81,-23.86,-22.61,-29.17,-17.02,-18.59,-28.96,-19.89,-22.66,-24.63,-9.42,-9.35,-21.73,-13.52,-18.57,-7.37,-2.37,-9.19,-15.51,-7.73,-1.45,-0.85,-2.56,-5.41,1.48,-8.55,-4.91,5.94,-3.5,-2.77,6.01,1.6,3.62,5.08,-1.78,-0.7,2.58,5.78,-2.33,3.05,2.18,-0.72,8.31,2.85,3.38,-0.96,6.72,4.54,5.38,-1.79,0.98,3.52,1.28,0.05,3.86,-0.72,0.56,-2.26,-5.57,0.2,-4.88,-0.74,-1.12,-1.75,-5.14,-6.42,-3.2,-8.42,-7.62,-6.6</v>
       </c>
     </row>
     <row r="44">
@@ -880,7 +880,7 @@
         <v>[L_02_标记]</v>
       </c>
       <c r="C44" t="str">
-        <v>a: 19.4ms -103.9uv b: 40.4ms 464.4uv</v>
+        <v>a: 17.0ms -28.1uv b: 37.5ms 126.1uv</v>
       </c>
     </row>
     <row r="45">
@@ -891,7 +891,7 @@
         <v>[R_03_名字]</v>
       </c>
       <c r="C45" t="str">
-        <v>FERG(3)_dOps</v>
+        <v>FERG(3)_dRod</v>
       </c>
     </row>
     <row r="46">
@@ -913,7 +913,7 @@
         <v>[R_03_闪光]</v>
       </c>
       <c r="C47" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.10cd.m-2,5ms</v>
       </c>
     </row>
     <row r="48">
@@ -924,7 +924,7 @@
         <v>[R_03_闪光背景]</v>
       </c>
       <c r="C48" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="49">
@@ -935,7 +935,7 @@
         <v>[R_03_采样]</v>
       </c>
       <c r="C49" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="50">
@@ -946,7 +946,7 @@
         <v>[R_03_分析时间]</v>
       </c>
       <c r="C50" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="51">
@@ -968,7 +968,7 @@
         <v>[R_03_详细数据(uv)]</v>
       </c>
       <c r="C52" t="str">
-        <v>-5.4,-4.34,-3.56,-3.17,-3.19,-3.63,-4.42,-5.44,-6.55,-7.61,-8.46,-9.01,-9.19,-9,-8.49,-7.75,-6.91,-6.11,-5.48,-5.12,-5.08,-5.38,-5.96,-6.72,-7.52,-8.23,-8.69,-8.79,-8.47,-7.72,-6.61,-5.24,-3.79,-2.43,-1.36,-0.75,-0.71,-1.31,-2.53,-4.29,-6.43,-8.75,-11.03,-13.04,-14.57,-15.48,-15.66,-15.11,-13.86,-12.04,-9.81,-7.35,-4.86,-2.51,-0.47,1.18,2.35,3.03,3.25,3.03,2.43,1.49,0.26,-1.25,-3.02,-5.06,-7.36,-9.88,-12.56,-15.32,-18,-20.41,-22.35,-23.58,-23.89,-23.1,-21.11,-17.89,-13.54,-8.25,-2.32,3.85,9.82,15.12,19.29,21.95,22.81,21.7,18.63,13.73,7.29,-0.28,-8.48,-16.75,-24.54,-31.33,-36.67,-40.22,-41.78,-41.25,-38.69,-34.29,-28.3,-21.09,-13.05,-4.64,3.73,11.63,18.66,24.48,28.79,31.37,32.05,30.74,27.44,22.25,15.36,7.05,-2.3,-12.21,-22.15,-31.55,-39.81,-46.38,-50.79,-52.68,-51.82,-48.17,-41.89,-33.31,-22.94,-11.44,0.46,11.97,22.32,30.83,36.95,40.3,40.7,38.17,32.95,25.45,16.23,5.94,-4.74,-15.12,-24.59,-32.62,-38.82,-42.94,-44.86,-44.62,-42.35,-38.3,-32.79,-26.17,-18.83,-11.15,-3.5,3.76,10.31,15.87,20.19,23.1,24.44,24.17,22.27,18.83,14.02,8.1,1.4,-5.71,-12.78,-19.37,-25.07,-29.5,-32.38,-33.53,-32.9,-30.57,-26.76,-21.78,-16.03,-9.98,-4.06,1.29,5.72,8.97,10.89,11.47,10.79,9.04,6.47,3.38,0.07,-3.19,-6.17,-8.71,-10.72,-12.17,-13.1,-13.59,-13.73,-13.61,-13.33,-12.93,-12.43,-11.84,-11.12,-10.23,-9.16,-7.89,-6.45,-4.89,-3.31,-1.84,-0.6,0.27,0.66,0.5,-0.22,-1.46,-3.13,-5.06,-7.07,-8.98,-10.57,-11.71,-12.28,-12.25,-11.64,-10.55,-9.13,-7.55,-6.02,-4.7,-3.75,-3.26,-3.24,-3.68,-4.46,-5.46,-6.51,-7.46,-8.16,-8.51,-8.49,-8.09,-7.4,-6.53,-5.62,-4.81,-4.24,-4.01,-4.15,-4.66,-5.47,-6.47,-7.53,-8.48,-9.19,-9.56,-9.52,-9.08,-8.28,-7.23,-6.08,-4.97,-4.07,-3.49,-3.32,-3.57,-4.22,-5.17,-6.3,-7.44,-8.45,-9.18,-9.53,-9.46,-8.97,-8.15,-7.09,-5.96,-4.92,-4.1,-3.62,-3.55,-3.9,-4.61,-5.6,-6.71,-7.79,-8.69,-9.28,-9.48,-9.26,-8.65,-7.74,-6.65,-5.54,-4.56,-3.86,-3.52,-3.61,-4.09,-4.92,-5.97,-7.09,-8.13,-8.95,-9.42,-9.48,-9.12,-8.4,-7.41,-6.29,-5.2,-4.3,-3.7,-3.5,-3.72,-4.32,-5.24,-6.33,-7.44,-8.42,-9.14,-9.48,-9.4,-8.92,-8.1,-7.05,-5.93,-4.88,-4.07,-3.59,-3.53,-3.88,-4.59,-5.58,-6.7,-7.78,-8.69,-9.29,-9.5,-9.29,-8.68,-7.77,-6.69,-5.57,-4.59,-3.87,-3.52,-3.59,-4.07,-4.89,-5.94,-7.06,-8.11,-8.93,-9.4,-9.48,-9.13,-8.42,-7.43,-6.32,-5.23,-4.32,-3.71,-3.5,-3.71,-4.31,-5.21,-6.3,-7.42,-8.4,-9.12,-9.47,-9.41,-8.93,-8.12,-7.08,-5.95,-4.91,-4.08,-3.6,-3.52,-3.86,-4.57,-5.56,-6.67,-7.76,-8.67,-9.28,-9.5,-9.3,-8.7,-7.8,-6.71,-5.6,-4.61,-3.88,-3.53,-3.59,-4.06,-4.87,-5.91,-7.03,-8.08,-8.91,-9.4,-9.48,-9.14,-8.44,-7.46,-6.34,-5.25,-4.34,-3.72,-3.5,-3.7,-4.29,-5.19,-6.28,-7.39,-8.38,-9.11,-9.47,-9.42,-8.95,-8.14,-7.1,-5.98,-4.93,-4.1,-3.61,-3.52,-3.85,-4.55,-5.53,-6.64,-7.74,-8.65,-9.27,-9.5,-9.31,-8.72,-7.82,-6.74,-5.62,-4.63,-3.9,-3.53,-3.58,-4.04,-4.85,-5.88,-7.01,-8.06,-8.89,-9.39,-9.48,-9.16,-8.46,-7.48,-6.37,-5.28,-4.35,-3.73,-3.5,-3.69,-4.27,-5.17,-6.25,-7.37,-8.36,-9.1,-9.47,-9.42,-8.97,-8.16,-7.13,-6,-4.95,-4.11,-3.61,-3.52,-3.84,-4.53,-5.51,-6.62,-7.71,-8.64,-9.26,-9.5,-9.32,-8.74,-7.85,-6.76</v>
+        <v>13.02,14.93,14.83,12.66,8.8,3.92,-1.08,-5.3,-7.96,-8.63,-7.25,-4.14,-0.01,4.28,7.81,9.82,9.85,7.84,4.12,-0.63,-5.54,-9.68,-12.28,-12.89,-11.41,-8.18,-3.85,0.69,4.54,6.91,7.33,5.71,2.35,-2.06,-6.68,-10.59,-12.97,-13.38,-11.76,-8.29,-3.7,1.04,5.22,7.97,8.74,7.32,4.28,-0.15,-4.41,-8.41,-10.63,-11.53,-9.88,-6.63,-1.88,2.74,7.13,8.94,9.66,8.02,5.31,-0.26,-3.89,-9.6,-10.97,-14.15,-12.75,-10.68,-5.45,-0.28,2.13,5.05,5.34,3.62,-3.94,-8.63,-10.74,-15.83,-24.71,-20.26,-24.75,-21.6,-17.54,-16.53,-7.42,-6.31,-4.23,-8.73,-15.12,-16.76,-24.52,-24.73,-29.36,-38.39,-31.87,-24.59,-22.92,-16.58,-11.57,-10.26,-5.61,-8.07,-12.47,-10.82,-19.06,-12.61,-21.94,-19.6,-17.2,-9.36,0.22,4.36,5.03,12.26,17.52,20.91,22.6,17.09,26.78,17.21,26.7,25.55,22.75,28.84,39.21,52.87,53.18,63.33,61.75,77.76,71.9,78.88,74.73,63.85,84.86,76.18,87.34,78.91,100.82,102.14,110.36,126.92,116.3,122.01,119.57,144.18,120.37,114.12,129.94,130.1,118.96,142.34,139.05,139.38,155.94,158.96,182.17,183.41,165.55,177.34,159.98,174.46,167.46,158.65,143.42,170.27,176.09,169.96,170.1,197.18,199.65,165.23,166.63,177.52,152.33,142.24,149.05,140.19,143.34,162.11,164.62,151.93,154.4,156.99,169.42,153.84,140.08,150.19,130.43,119.91,130.82,121.55,122.85,104.51,97.64,116.44,106.8,113.64,107.49,118.82,99.37,102.97,83.39,79.22,79.41,74.05,65.62,54.06,71.6,67.87,62.46,73.35,71.58,67.94,60.19,51.23,38.7,40.03,31.71,29.23,24.47,28.17,23.98,27.18,30.55,33.08,36.13,35.77,33.46,25.9,21.95,12.98,6.98,5.58,2.73,3.71,9.15,10.34,17.56,19.71,19.32,18.26,15.78,12.52,7.84,2.9,-3.16,-6.02,-6.13,-4.08,-1.71,2.67,6.41,10.3,11.98,11.23,8.86,4.71,-0.45,-5.5,-10.47,-12.72,-13.15,-12.4,-9.02,-5.14,-0.46,2.16,3.55,3.85,0.88,-3.13,-8.26,-12.85,-18.04,-20.78,-20.33,-20.3,-17.01,-12.91,-9.55,-4.43,-3.43,-3.38,-5.02,-8.77,-14.68,-18.45,-23.58,-25.37,-27.85,-25.91,-23.69,-17.52,-13.07,-10.18,-9.58,-8.76,-10.28,-11.58,-16.8,-21.88,-26.67,-29.73,-27.5,-28.9,-22.91,-20.5,-14.29,-9.76,-8.57,-7.32,-9.52,-14.71,-19.4,-24.29,-28.23,-30.34,-29.32,-29.99,-21.69,-19.31,-17.83,-9.27,-10.06,-5.4,-6.77,-10.24,-18.02,-23.3,-28.55,-30.13,-32.27,-29.63,-21.85,-20.55,-16.82,-16.02,-9.71,-13.87,-10.93,-17.58,-19.86,-29.1,-31.16,-28.23,-34.16,-32.63,-29.76,-22.71,-21.7,-21.93,-12.12,-19.87,-15.67,-24.89,-29.76,-34.62,-31.78,-40.24,-45.43,-48.15,-36.26,-39.8,-35.88,-28.04,-32.75,-25.92,-26.49,-29.74,-30.23,-44.95,-42.83,-48.86,-44.84,-47.28,-48.54,-47.39,-36.97,-32.27,-32.01,-27.71,-35,-33.64,-33,-44.72,-43.19,-45.81,-60.4,-58.64,-55.63,-47.11,-45.19,-41.05,-34.88,-36.99,-38.1,-35.58,-32.25,-42.33,-47.05,-55.81,-56.92,-52.41,-45.02,-40.55,-35.43,-36.44,-23.09,-34.72,-20.32,-34.22,-36.16,-36.76,-37.66,-43.68,-38.29,-47.59,-38.34,-39.07,-38.41,-22.03,-27.93,-20.51,-15.8,-30.66,-28.75,-31.98,-41.89,-36.72,-39.95,-47.19,-37.19,-30.33,-27.82,-22.76,-19.49,-21.38,-21.02,-21.07,-24.1,-35.51,-33.36,-43.42,-43.86,-46.85,-43.3,-30.3,-33.4,-30.26,-23.94,-18.65,-19.65,-25.38,-28.77,-32.75,-38.54,-37.96,-40.32,-45.78,-43.49,-38.85,-30.94,-25.9,-19.18,-23.86,-21.89,-21.64,-30.33,-33.07,-38.3,-38.66,-39.39,-42.13,-39.45,-32.84,-26.38,-21.31,-20.25,-16.86,-19.52,-19.52,-23.33,-28.57,-32.98,-33.15,-34.49,-36.92,-31.74,-30.27,-22.78,-21.07,-14.99,-11.42,-14.3,-13.67,-16.3,-19.95,-28.25,-28.19</v>
       </c>
     </row>
     <row r="53">
@@ -979,7 +979,7 @@
         <v>[R_03_标记]</v>
       </c>
       <c r="C53" t="str">
-        <v>85.8uv</v>
+        <v>a: 19.1ms -22.4uv b: 40.6ms 108.5uv</v>
       </c>
     </row>
     <row r="54">
@@ -990,7 +990,7 @@
         <v>[L_03_名字]</v>
       </c>
       <c r="C54" t="str">
-        <v>FERG(3)_dOps</v>
+        <v>FERG(3)_dRod</v>
       </c>
     </row>
     <row r="55">
@@ -1012,7 +1012,7 @@
         <v>[L_03_闪光]</v>
       </c>
       <c r="C56" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.10cd.m-2,5ms</v>
       </c>
     </row>
     <row r="57">
@@ -1023,7 +1023,7 @@
         <v>[L_03_闪光背景]</v>
       </c>
       <c r="C57" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="58">
@@ -1034,7 +1034,7 @@
         <v>[L_03_采样]</v>
       </c>
       <c r="C58" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="59">
@@ -1045,7 +1045,7 @@
         <v>[L_03_分析时间]</v>
       </c>
       <c r="C59" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="60">
@@ -1067,7 +1067,7 @@
         <v>[L_03_详细数据(uv)]</v>
       </c>
       <c r="C61" t="str">
-        <v>-4.07,-3.02,-3.55,-5.33,-7.36,-8.51,-8.13,-6.38,-4.19,-2.72,-2.77,-4.36,-6.71,-8.65,-9.26,-8.32,-6.46,-4.79,-4.32,-5.4,-7.52,-9.6,-10.53,-9.76,-7.62,-5.09,-3.34,-3.07,-4.17,-5.78,-6.78,-6.39,-4.6,-2.2,-0.39,-0.12,-1.64,-4.32,-7.03,-8.7,-8.91,-8.04,-7.1,-7.12,-8.58,-11.12,-13.71,-15.14,-14.65,-12.35,-9.1,-6.1,-4.25,-3.7,-3.82,-3.58,-2.14,0.61,3.96,6.69,7.65,6.36,3.24,-0.64,-4.13,-6.51,-7.92,-9.13,-11.1,-14.36,-18.61,-22.82,-25.65,-26.11,-24.03,-20.09,-15.49,-11.31,-8,-5.22,-2.14,2.02,7.38,13.25,18.32,21.23,21.2,18.38,13.69,8.37,3.36,-1.15,-5.66,-10.95,-17.5,-25.03,-32.45,-38.25,-41.17,-40.69,-37.27,-32.02,-26.13,-20.34,-14.6,-8.31,-0.84,7.96,17.36,25.98,32.23,35.02,34.16,30.38,24.88,18.76,12.48,5.79,-1.93,-11.15,-21.61,-32.24,-41.44,-47.69,-50.15,-48.98,-45.13,-39.83,-33.96,-27.71,-20.64,-12.12,-1.95,9.29,20.23,29.22,34.91,36.83,35.43,31.85,27.21,22.13,16.5,9.71,1.19,-9.01,-20.01,-30.31,-38.29,-42.93,-44.11,-42.6,-39.57,-35.99,-32.13,-27.61,-21.67,-13.86,-4.45,5.45,14.29,20.67,23.9,24.27,22.76,20.52,18.23,15.82,12.63,7.85,1.17,-6.91,-15.15,-22.05,-26.5,-28.23,-27.86,-26.5,-25.15,-24.18,-23.18,-21.25,-17.63,-12.18,-5.61,0.76,5.59,8.12,8.47,7.55,6.49,6.05,6.25,6.37,5.41,2.69,-1.69,-6.82,-11.4,-14.31,-15.16,-14.45,-13.25,-12.6,-13.01,-14.11,-14.96,-14.54,-12.37,-8.79,-4.85,-1.83,-0.53,-0.98,-2.38,-3.58,-3.7,-2.6,-0.92,0.24,-0.05,-2.01,-5.05,-8.01,-9.76,-9.79,-8.45,-6.74,-5.8,-6.24,-7.89,-9.83,-10.93,-10.45,-8.46,-5.79,-3.65,-2.94,-3.84,-5.7,-7.38,-7.89,-6.88,-4.88,-2.96,-2.19,-3.04,-5.16,-7.51,-8.94,-8.8,-7.24,-5.18,-3.78,-3.82,-5.32,-7.48,-9.15,-9.43,-8.13,-5.91,-3.92,-3.16,-4.01,-5.98,-7.98,-8.92,-8.3,-6.42,-4.28,-3.03,-3.33,-5.04,-7.26,-8.82,-8.91,-7.49,-5.34,-3.61,-3.23,-4.41,-6.52,-8.45,-9.17,-8.28,-6.27,-4.19,-3.15,-3.69,-5.53,-7.68,-8.99,-8.76,-7.11,-4.92,-3.36,-3.24,-4.65,-6.82,-8.61,-9.06,-7.94,-5.84,-3.88,-3.11,-3.94,-5.92,-8.01,-9.09,-8.58,-6.76,-4.6,-3.24,-3.41,-5.02,-7.21,-8.81,-8.98,-7.62,-5.45,-3.64,-3.14,-4.22,-6.3,-8.29,-9.11,-8.34,-6.38,-4.28,-3.15,-3.6,-5.39,-7.56,-8.96,-8.84,-7.27,-5.08,-3.44,-3.22,-4.54,-6.69,-8.54,-9.09,-8.06,-5.99,-3.98,-3.11,-3.84,-5.77,-7.88,-9.06,-8.66,-6.9,-4.73,-3.29,-3.35,-4.88,-7.07,-8.74,-9.02,-7.75,-5.6,-3.73,-3.12,-4.11,-6.16,-8.18,-9.1,-8.43,-6.52,-4.4,-3.18,-3.52,-5.24,-7.43,-8.91,-8.9,-7.41,-5.23,-3.51,-3.18,-4.41,-6.54,-8.44,-9.1,-8.17,-6.14,-4.09,-3.12,-3.74,-5.62,-7.76,-9.02,-8.73,-7.05,-4.86,-3.34,-3.29,-4.75,-6.92,-8.67,-9.05,-7.87,-5.75,-3.82,-3.11,-4,-6.01,-8.07,-9.09,-8.52,-6.67,-4.52,-3.22,-3.45,-5.1,-7.29,-8.85,-8.95,-7.54,-5.37,-3.59,-3.15,-4.29,-6.4,-8.35,-9.11,-8.27,-6.29,-4.21,-3.14,-3.65,-5.47,-7.64,-8.98,-8.8,-7.19,-5,-3.4,-3.25,-4.61,-6.78,-8.59,-9.08,-7.99,-5.9,-3.92,-3.11,-3.89,-5.86,-7.96,-9.07,-8.61,-6.82,-4.65,-3.26,-3.38,-4.96,-7.15,-8.79,-9,-7.67,-5.51,-3.68,-3.13,-4.17,-6.25,-8.25,-9.11,-8.37,-6.44,-4.32,-3.16,-3.57,-5.33,-7.51,-8.94,-8.87,-7.33,-5.14,-3.47,-3.2,-4.49,-6.63,-8.5,-9.1,-8.1,-6.05,-4.03,-3.11,-3.8,-5.71,-7.84,-9.04,-8.69,-6.96,-4.78,-3.31,-3.33,-4.83</v>
+        <v>7.76,11.4,14.19,15.82,16.1,14.97,12.49,8.87,4.43,-0.45,-5.33,-9.79,-13.41,-15.91,-17.07,-16.84,-15.27,-12.56,-9.03,-5.05,-1.06,2.51,5.28,6.93,7.28,6.26,3.93,0.49,-3.74,-8.37,-12.97,-17.12,-20.4,-22.54,-23.32,-22.66,-20.66,-17.46,-13.43,-8.93,-4.47,-0.33,3.02,5.24,6.12,5.76,3.82,0.98,-2.82,-6.95,-10.94,-14.87,-17.46,-19.44,-20.14,-18.82,-16.48,-12.92,-8.97,-4.49,0.55,4.82,7.56,10.07,10.5,10.45,8.69,5.59,1.25,-3.17,-8.07,-13.91,-14.64,-18.71,-20.5,-20.36,-17.01,-14.75,-10.49,-6.67,-4.53,-1.55,-0.51,0.74,5.83,3.26,0.72,-5.45,-5.64,-13.54,-19.75,-20.42,-24.78,-34.48,-32.32,-29.16,-27.16,-33.51,-27.66,-16.5,-18.66,-16.23,-4.15,-3.06,0.84,-9.15,-9.14,-6.08,-11.89,-6.99,-20.94,-17.08,-16.77,-24.35,-16.53,-20.08,-15.18,-10.91,-3.09,9.79,9.14,22.01,19.04,34.9,34.58,33.82,43.36,41.09,37.28,33.62,32.99,30.52,43.8,33.74,32.95,50.71,65.48,50.1,66.65,79.79,84.85,104.58,92.85,111.76,102.52,115.01,128.04,110.29,116.55,127.57,128.5,127.55,113.19,127.24,126.51,122.76,127.34,149.54,129.79,145.33,163.25,172.7,154.11,179.84,168.57,186.55,164.42,180.98,167.77,153.13,154.9,148.22,158.73,140.26,158.02,139.84,177.76,177.34,183.32,174.61,157.57,158.53,178.96,176.39,180.68,169.14,165.69,157.47,182.89,160.89,162.12,158.02,133.29,117.66,127.17,112.36,128.85,122.73,119.63,120.08,126.57,147.68,135.85,120.27,133.37,126.17,137.08,117.04,105.84,97.67,103.86,78.79,90.06,90,63.48,69.72,62.12,73.55,78.66,68.79,86.25,73.23,82.68,84,75.66,79.17,69.73,59.18,53.19,57.81,47.88,42.4,35.48,32.28,29.42,25.1,31.2,28.86,32.92,32.81,32.42,38.92,39.34,44.78,38.02,38.23,35.61,29.31,26.26,19.6,17.48,10.26,5.5,1.59,-0.26,0.19,-0.02,4.12,5.41,10.42,14.33,14.39,18.44,20.7,19.07,19.18,16.6,12.17,6.35,1.62,-3.24,-7.96,-13.09,-16.64,-18.89,-18.48,-16.97,-15.25,-12.08,-8.97,-5.15,-1.58,1.04,2.17,2.88,1.16,-0.56,-4.78,-9.24,-14.27,-19.59,-24.58,-28.49,-31.41,-32.39,-32.58,-29.67,-28.78,-24.04,-21.06,-17.48,-13.41,-7.73,-8.05,-6.72,-7.65,-9.07,-12.34,-16.86,-20.82,-25.74,-28.76,-30.78,-33.05,-34.92,-35.2,-32.2,-27.49,-24.19,-19.15,-15.84,-12,-8.22,-7.21,-1.59,-6.92,-7.58,-5.94,-10.82,-14.31,-23.33,-28.25,-29.71,-31.8,-33.85,-29.04,-29.24,-28.78,-20.8,-17.59,-10.66,-11.61,-6.29,-4.09,-3.62,-6.62,-9.08,-13.09,-11.59,-16.06,-28.33,-33.48,-33.58,-36.74,-33.77,-41.2,-32.94,-32.2,-33.13,-30.68,-26.47,-23.68,-22.62,-15.73,-20.48,-11.61,-17.23,-23.62,-26.57,-35.96,-33.79,-38.7,-49.14,-52.08,-54.09,-57.49,-52.55,-48.28,-52.8,-47.55,-36.34,-35.27,-27.93,-31.99,-30.46,-24.85,-37.3,-27.97,-40.22,-37.09,-45.46,-55.87,-61.24,-51.81,-58.85,-64.72,-52.3,-52.18,-46.78,-38.88,-39.97,-38.76,-26.29,-28.09,-36.02,-24.72,-28.32,-31.74,-27.49,-40.8,-48.86,-53.29,-49.91,-44.47,-47.99,-44.18,-47.56,-50.11,-45.4,-41.02,-34.35,-22.44,-27.89,-13.74,-16.66,-24.07,-17.33,-29.62,-22.96,-34.94,-38.15,-43.93,-41.37,-41.89,-38.8,-45.31,-48.9,-46.68,-34.17,-36.95,-28.15,-21.3,-15.88,-23.17,-20.68,-10.71,-22.08,-15.72,-23.91,-29.22,-32.64,-40.18,-38.1,-45.4,-42.86,-43.89,-44.15,-38.11,-44.17,-32.86,-26.94,-29.03,-19.47,-15.65,-14.65,-21.4,-19.93,-25.69,-24.42,-28.45,-37.79,-44.86,-42.68,-45.44,-50.81,-49.68,-45.15,-42.14,-35.8,-33.26,-28.15,-26.45,-17.47,-15.64,-13.04,-17.07,-13.97,-18.74,-22.98,-25.62,-27.71,-34.57,-38.85,-38.76,-38.88,-36.39,-35.19,-30.78,-28.72,-22.15</v>
       </c>
     </row>
     <row r="62">
@@ -1078,7 +1078,7 @@
         <v>[L_03_标记]</v>
       </c>
       <c r="C62" t="str">
-        <v>82uv</v>
+        <v>a: 19.1ms -18.2uv b: 40.7ms 68.2uv</v>
       </c>
     </row>
     <row r="63">
@@ -1089,7 +1089,7 @@
         <v>[R_04_名字]</v>
       </c>
       <c r="C63" t="str">
-        <v>FERG(4)_lCone</v>
+        <v>FERG(4)_dRod</v>
       </c>
     </row>
     <row r="64">
@@ -1111,7 +1111,7 @@
         <v>[R_04_闪光]</v>
       </c>
       <c r="C65" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:0.30cd.m-2,5ms</v>
       </c>
     </row>
     <row r="66">
@@ -1122,7 +1122,7 @@
         <v>[R_04_闪光背景]</v>
       </c>
       <c r="C66" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="67">
@@ -1133,7 +1133,7 @@
         <v>[R_04_采样]</v>
       </c>
       <c r="C67" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="68">
@@ -1144,7 +1144,7 @@
         <v>[R_04_分析时间]</v>
       </c>
       <c r="C68" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="69">
@@ -1166,7 +1166,7 @@
         <v>[R_04_详细数据(uv)]</v>
       </c>
       <c r="C70" t="str">
-        <v>2.04,2.99,2.35,0.46,-1.68,-2.92,-2.61,-0.91,1.27,2.78,2.81,1.34,-0.84,-2.57,-2.94,-1.74,0.39,2.31,3,2.09,0.07,-1.98,-2.98,-2.4,-0.53,1.61,2.9,2.65,0.98,-1.21,-2.75,-2.83,-1.41,0.76,2.53,2.94,1.79,-0.33,-2.27,-3.02,-2.17,-0.18,1.88,2.92,2.37,0.52,-1.66,-3.02,-2.86,-1.27,0.87,2.4,2.46,1,-1.27,-3.18,-3.78,-2.83,-0.91,0.85,1.4,0.33,-1.95,-4.39,-5.88,-5.84,-4.53,-2.91,-2.13,-2.94,-5.25,-8.22,-10.68,-11.78,-11.41,-10.28,-9.54,-10.16,-12.41,-15.73,-18.99,-21.13,-21.69,-21.06,-20.27,-20.42,-22.12,-25.11,-28.44,-30.93,-31.83,-31.16,-29.73,-28.7,-28.93,-30.54,-32.84,-34.65,-35,-33.56,-30.86,-28.01,-26.07,-25.52,-25.99,-26.45,-25.79,-23.37,-19.41,-14.83,-10.81,-8.13,-6.79,-5.99,-4.58,-1.66,2.91,8.45,13.81,17.98,20.62,22.24,23.91,26.7,31.13,36.83,42.79,47.87,51.42,53.59,55.3,57.71,61.61,67,73.11,78.76,83.04,85.75,87.53,89.52,92.72,97.5,103.36,109.22,113.97,117.09,118.89,120.34,122.6,126.32,131.36,136.82,141.53,144.66,146.16,146.79,147.69,149.8,153.33,157.64,161.6,164.18,164.98,164.45,163.66,163.7,165.11,167.62,170.23,171.8,171.62,169.8,167.22,165.04,164.11,164.49,165.44,165.82,164.67,161.77,157.7,153.6,150.51,148.86,148.23,147.57,145.79,142.3,137.38,132.01,127.35,124.14,122.29,120.98,119.04,115.64,110.67,104.88,99.41,95.26,92.7,91.16,89.56,86.84,82.56,77.14,71.62,67.14,64.29,62.85,61.88,60.22,57.14,52.68,47.68,43.31,40.45,39.22,38.93,38.43,36.74,33.55,29.41,25.43,22.65,21.56,21.77,22.26,21.89,20.04,16.9,13.4,10.71,9.58,10,11.14,11.85,11.21,9.08,6.12,3.48,2.14,2.44,3.85,5.29,5.66,4.48,2.08,-0.51,-2.17,-2.25,-0.92,0.9,2.04,1.72,-0.08,-2.56,-4.56,-5.18,-4.22,-2.35,-0.69,-0.26,-1.41,-3.67,-5.94,-7.14,-6.75,-5.09,-3.16,-2.1,-2.59,-4.48,-6.88,-8.63,-8.9,-7.67,-5.71,-4.18,-4.01,-5.41,-7.75,-9.91,-10.87,-10.23,-8.46,-6.64,-5.85,-6.66,-8.75,-11.16,-12.74,-12.77,-11.39,-9.47,-8.18,-8.34,-10.02,-12.47,-14.54,-15.27,-14.43,-12.62,-10.96,-10.48,-11.61,-13.89,-16.28,-17.66,-17.46,-15.96,-14.1,-13.06,-13.54,-15.46,-17.96,-19.88,-20.36,-19.31,-17.47,-15.96,-15.78,-17.17,-19.57,-21.86,-22.99,-22.53,-20.87,-19.08,-18.26,-19.01,-21.09,-23.55,-25.24,-25.42,-24.13,-22.22,-20.86,-20.91,-22.5,-24.91,-27.02,-27.83,-27.04,-25.22,-23.45,-22.81,-23.76,-25.91,-28.24,-29.62,-29.42,-27.86,-25.87,-24.6,-24.84,-26.53,-28.87,-30.7,-31.11,-29.97,-27.95,-26.19,-25.69,-26.77,-28.91,-31.01,-32,-31.39,-29.54,-27.45,-26.27,-26.64,-28.38,-30.56,-32.04,-32.03,-30.51,-28.3,-26.55,-26.17,-27.34,-29.41,-31.24,-31.81,-30.78,-28.65,-26.5,-25.41,-25.9,-27.65,-29.64,-30.75,-30.3,-28.45,-26.09,-24.39,-24.15,-25.41,-27.38,-28.92,-29.09,-27.68,-25.33,-23.17,-22.22,-22.86,-24.62,-26.43,-27.18,-26.35,-24.23,-21.8,-20.22,-20.17,-21.53,-23.43,-24.7,-24.5,-22.79,-20.32,-18.24,-17.5,-18.33,-20.12,-21.77,-22.22,-21.07,-18.77,-16.37,-14.99,-15.19,-16.7,-18.55,-19.58,-19.09,-17.16,-14.66,-12.75,-12.29,-13.35,-15.21,-16.71,-16.9,-15.51,-13.13,-10.86,-9.75,-10.25,-11.92,-13.74,-14.57,-13.83,-11.76,-9.32,-7.66,-7.53,-8.84,-10.77,-12.15,-12.11,-10.54,-8.14,-6.07,-5.29,-6.1,-7.95,-9.72,-10.37,-9.42,-7.27,-4.95,-3.58,-3.79,-5.36,-7.35,-8.59,-8.34,-6.62,-4.26,-2.42,-1.99,-3.11,-5.1,-6.81,-7.26,-6.12,-3.92,-1.76,-0.71,-1.26,-3.05,-5.05,-6.14,-5.66,-3.82,-1.53,0.05,0.14,-1.26</v>
+        <v>-4.59,0.82,0.63,-5.22,-13.18,-18.39,-17.69,-11.65,-4.2,-0.16,-2.16,-9.03,-16.5,-19.9,-17.14,-9.98,-2.96,-0.52,-4.17,-11.6,-18.06,-19.44,-14.78,-6.96,-0.81,-0.13,-5.21,-12.74,-17.81,-17.09,-10.88,-2.93,1.9,0.74,-5.5,-12.7,-16.12,-13.42,-6.1,1.4,4.53,1.52,-5.56,-12.05,-13.67,-9.23,-1.37,5.12,6.28,1.53,-6,-11.43,-11.23,-5.42,2.43,7.42,6.47,0.22,-7.34,-11.44,-9.46,-2.73,4.55,7.69,4.63,-2.72,-9.95,-12.4,-8.81,-1.65,4.56,5.45,0.69,-7.38,-13.91,-14.52,-10.13,-2.44,2.05,0.36,-5.56,-14.14,-20.01,-18.25,-12.31,-6.59,-3.13,-7.93,-15.07,-22.63,-28.15,-23.43,-20.11,-13.55,-11.92,-18.57,-26.99,-33.04,-38.85,-35.25,-28.2,-20.08,-23.72,-30.75,-40.38,-48.39,-40.2,-40.36,-30.07,-34.03,-26.45,-36.66,-44,-51.7,-48.6,-41.68,-35.98,-33.82,-32.78,-37.09,-48.46,-49.96,-38.2,-31.38,-18.54,-21.04,-17.79,-22.56,-32.72,-29.83,-13.89,-11.49,7.51,1.46,0.88,1,-2.95,3.14,12.24,26.42,30.41,32.16,24.43,29.45,29.13,36.48,43.4,55.9,70.4,69.48,58.73,54.41,65.33,79.09,89.31,86.09,101.43,89.69,91.2,102.94,93.15,101.98,114.92,141.82,141.87,133.11,133.3,118.7,136.94,152.92,154.81,159.65,171.2,149.5,164.4,161.4,172.51,147.84,192.86,181.93,180.69,143.52,167.3,180.41,162.08,160.52,185.82,193.21,173.22,175,178.48,150.35,180.8,187.76,186.31,179.77,165.59,166.1,159.39,161.02,157.24,163.11,157.2,153.68,154.32,127.73,125.4,129.67,133.09,128.54,136.39,133.82,109.55,97.06,116.26,119.13,106.85,118.15,110.83,90.94,77.45,71.4,87.02,81.4,89.84,78.54,82.45,70.2,52.11,56.12,54.36,62.61,66.4,57.94,48.1,37.36,30.16,32.66,33.63,41.72,44.12,33.25,26.92,15.21,16.81,18.4,22.91,28.61,25.38,18.7,10.51,3.33,1.41,6.6,12.48,13.94,11.38,4.2,-5.18,-8.47,-8.38,-1.21,4.72,6.06,2.58,-6.16,-13.72,-15.92,-12.77,-5.58,-0.11,0.68,-5.26,-13.5,-19.12,-19.53,-14.49,-6.86,-2.47,-3.2,-10.11,-17.8,-22.29,-20.42,-13.45,-5.73,-2.89,-6.1,-13.51,-20.21,-22.73,-18.87,-11.16,-5.19,-2.69,-7.55,-14.91,-21.44,-21.42,-14.96,-8.44,-1.86,-2.67,-8.4,-17.1,-21.48,-18.94,-11.55,-5.43,0.78,-3.58,-8.63,-17.09,-19.24,-16.46,-10.41,-3.08,1.05,-6.32,-12.03,-18.94,-18.96,-12.93,-5.88,-1.49,-2.12,-6.13,-15.75,-22.2,-19.36,-13.05,-8.2,-3.66,-4.2,-13.05,-21.51,-26.09,-24.85,-16.86,-7.48,-10.61,-12.04,-16.58,-23.53,-32.4,-21.16,-15.44,-11.16,-9.04,-21.73,-31.05,-33.27,-33.07,-29.55,-17.71,-14.17,-20.7,-28.18,-36.81,-38.66,-35.97,-27.49,-18.32,-21.82,-20.96,-30.47,-41.78,-41.74,-38.03,-31.04,-23.8,-24.03,-30.52,-40.01,-37.82,-40.64,-39.84,-34.21,-18.82,-20.18,-38.68,-38.01,-38.65,-40.66,-33.66,-26.48,-18.13,-28.02,-37.18,-41.53,-39.02,-43.22,-28.53,-26.1,-17.69,-25.17,-33.68,-43.38,-45.22,-36.7,-32.57,-28.18,-33.02,-23.87,-31.76,-48.88,-48.46,-31.68,-27.45,-32.01,-31.69,-31.12,-33.06,-38.98,-40.76,-38.47,-23.77,-17.43,-26.35,-30.19,-38.65,-38.95,-33.81,-34.83,-31.81,-28.99,-40.92,-43.14,-52.33,-51.68,-40.47,-35.46,-24.38,-30.5,-44.49,-38.7,-44.55,-51.03,-38.89,-36.79,-27.94,-38.27,-46.49,-41.25,-40.19,-39.35,-38.81,-28.84,-23.93,-29.93,-35.13,-48.89,-41.88,-44.43,-30.82,-33.94,-32.87,-35.91,-43.99,-42.94,-46.8,-35.44,-33.97,-20.8,-24.81,-32.63,-45.21,-44.44,-36.7,-27.38,-19.89,-22.41,-29.16,-30.01,-37.52,-33.44,-27.18,-25.97,-12,-15.7,-26.99,-34.18,-29.62,-33.08,-20.23,-14.37,-9.57,-13.44,-21.63,-25.69,-26.4,-22.59,-18.29,-12.58,-7.66,-14.56,-18.94,-23.6,-24.07,-16.58</v>
       </c>
     </row>
     <row r="71">
@@ -1177,7 +1177,7 @@
         <v>[R_04_标记]</v>
       </c>
       <c r="C71" t="str">
-        <v>a: 23.4ms -39.0uv b: 48.4ms 169.0uv</v>
+        <v>a: 19.8ms -29.9uv b: 44.9ms 198.6uv</v>
       </c>
     </row>
     <row r="72">
@@ -1188,7 +1188,7 @@
         <v>[L_04_名字]</v>
       </c>
       <c r="C72" t="str">
-        <v>FERG(4)_lCone</v>
+        <v>FERG(4)_dRod</v>
       </c>
     </row>
     <row r="73">
@@ -1210,7 +1210,7 @@
         <v>[L_04_闪光]</v>
       </c>
       <c r="C74" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:0.30cd.m-2,5ms</v>
       </c>
     </row>
     <row r="75">
@@ -1221,7 +1221,7 @@
         <v>[L_04_闪光背景]</v>
       </c>
       <c r="C75" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="76">
@@ -1232,7 +1232,7 @@
         <v>[L_04_采样]</v>
       </c>
       <c r="C76" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="77">
@@ -1243,7 +1243,7 @@
         <v>[L_04_分析时间]</v>
       </c>
       <c r="C77" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="78">
@@ -1265,7 +1265,7 @@
         <v>[L_04_详细数据(uv)]</v>
       </c>
       <c r="C79" t="str">
-        <v>2.7,2.36,-0.62,-2.91,-1.93,1.22,3,1.41,-1.76,-2.96,-0.83,2.22,2.78,0.22,-2.59,-2.49,0.41,2.85,2.09,-1.01,-2.98,-1.6,1.58,2.98,1.04,-2.07,-2.86,-0.43,2.48,2.61,-0.19,-2.78,-2.25,0.8,2.95,1.77,-1.4,-3.01,-1.26,1.89,2.89,0.61,-2.39,-2.76,-0.09,2.6,2.27,-0.73,-3.07,-2.15,0.94,2.69,1.07,-2.18,-3.5,-1.5,1.44,1.88,-0.84,-3.86,-4.01,-1.37,0.8,-0.26,-3.73,-6.13,-5.24,-2.57,-1.7,-4.25,-8.04,-9.59,-7.98,-5.91,-6.66,-10.42,-14.04,-14.61,-12.69,-11.68,-14.02,-18.41,-21.28,-20.78,-18.87,-19.05,-22.49,-26.64,-28.11,-26.46,-24.67,-25.77,-29.45,-32.37,-31.89,-29.05,-27.35,-28.85,-31.81,-32.65,-29.98,-26.12,-24.52,-25.88,-27.35,-25.74,-21.12,-16.72,-15.34,-16.18,-15.78,-11.9,-6.03,-1.77,-0.75,-0.85,1.42,7,13.21,16.72,17.34,18.16,22.12,28.67,34.4,36.86,37.29,39.25,44.6,51.4,56.12,57.57,58.23,61.5,67.84,74.27,77.71,78.44,79.77,84.34,91.12,96.6,98.69,99.09,101.36,106.91,113.44,117.46,118.27,118.67,121.85,127.8,133.27,135.47,135.14,135.74,139.55,145.1,148.8,148.99,147.76,148.63,152.56,156.89,158.31,156.56,154.75,155.82,159.28,161.71,160.65,157.32,155.27,156.39,158.79,158.92,155.57,151.22,149.27,150.22,151.13,148.89,143.78,139.1,137.52,138.07,137.24,132.94,126.84,122.53,121.47,121.38,118.82,113.03,106.83,103.45,102.9,102,97.93,91.42,85.95,83.83,83.64,81.8,76.64,70.25,66.15,65.35,65.21,62.43,56.73,51.21,48.82,49.12,48.7,45.08,39.45,35.36,34.73,35.68,34.67,30.45,25.47,23.14,23.98,25.05,23.24,18.78,14.94,14.4,16.22,16.87,14.24,9.96,7.6,8.63,10.8,10.63,7.33,3.69,2.93,5.1,6.99,5.78,2.14,-0.46,0.31,3.02,4.12,1.87,-1.65,-2.93,-0.94,1.69,1.65,-1.37,-4.31,-4.18,-1.43,0.56,-0.71,-4.1,-6.05,-4.63,-1.68,-0.75,-3.13,-6.37,-7.07,-4.67,-2.09,-2.45,-5.58,-8.18,-7.56,-4.64,-2.93,-4.57,-7.96,-9.52,-7.73,-4.85,-4.34,-7.02,-10.13,-10.42,-7.82,-5.5,-6.33,-9.64,-11.97,-10.99,-8.06,-6.75,-8.81,-12.21,-13.42,-11.37,-8.65,-8.62,-11.61,-14.56,-14.46,-11.74,-9.76,-11.05,-14.49,-16.52,-15.19,-12.31,-11.44,-13.88,-17.22,-18.04,-15.74,-13.24,-13.67,-16.88,-19.6,-19.1,-16.28,-14.64,-16.34,-19.82,-21.48,-19.8,-16.99,-16.52,-19.26,-22.44,-22.81,-20.28,-17.99,-18.83,-22.16,-24.55,-23.61,-20.7,-19.38,-21.41,-24.81,-26.03,-23.97,-21.22,-21.12,-24.05,-26.96,-26.83,-24.05,-21.97,-23.15,-26.48,-28.44,-27.02,-24.02,-22.99,-25.27,-28.47,-29.16,-26.72,-24.04,-24.26,-27.27,-29.81,-29.13,-26.11,-24.22,-25.67,-28.91,-30.36,-28.45,-25.37,-24.62,-27.06,-29.98,-30.1,-27.28,-24.69,-25.2,-28.21,-30.3,-29.07,-25.84,-24.17,-25.85,-28.92,-29.82,-27.44,-24.34,-23.87,-26.43,-29,-28.55,-25.42,-22.96,-23.75,-26.73,-28.35,-26.6,-23.23,-21.82,-23.72,-26.58,-26.94,-24.17,-21.12,-20.97,-23.62,-25.84,-24.86,-21.5,-19.27,-20.37,-23.29,-24.45,-22.25,-18.86,-17.78,-19.91,-22.55,-22.42,-19.34,-16.46,-16.68,-19.44,-21.3,-19.86,-16.4,-14.48,-15.92,-18.78,-19.51,-16.96,-13.66,-12.99,-15.36,-17.79,-17.22,-13.96,-11.34,-11.99,-14.84,-16.38,-14.55,-11.1,-9.57,-11.38,-14.18,-14.52,-11.71,-8.61,-8.39,-11.01,-13.23,-12.26,-8.91,-6.66,-7.75,-10.69,-11.9,-9.76,-6.4,-5.34,-7.51,-10.22,-10.18,-7.2,-4.37,-4.65,-7.49,-9.47,-8.15,-4.79,-2.96,-4.49,-7.47,-8.35,-5.94,-2.76,-2.19,-4.68,-7.26,-6.86,-3.75,-1.26,-2.03,-5.03,-6.74,-5.09,-1.79,-0.39,-2.34,-5.3,-5.82,-3.19,-0.24,-0.16,-2.92,-5.31,-4.54</v>
+        <v>-35.24,-32.97,-27.18,-20.61,-16.33,-16.39,-20.88,-27.89,-34.37,-37.51,-35.98,-30.57,-23.77,-18.73,-17.76,-21.36,-27.95,-34.59,-38.33,-37.49,-32.46,-25.48,-19.69,-17.65,-20.24,-26.25,-32.92,-37.17,-37.02,-32.44,-25.39,-18.95,-15.89,-17.46,-22.84,-29.46,-34.21,-34.8,-30.82,-23.9,-16.99,-13.05,-13.67,-18.43,-25,-30.28,-31.72,-28.52,-21.95,-14.82,-10.18,-9.98,-14.15,-20.71,-26.55,-28.94,-26.7,-20.73,-13.61,-8.47,-7.54,-11.19,-17.73,-24.18,-27.59,-26.43,-21.21,-14.29,-8.91,-7.4,-10.41,-16.91,-23.9,-28.58,-28.42,-24.38,-17.74,-12.05,-10.14,-12.71,-19.09,-26.46,-32.19,-33.46,-29.94,-25.27,-19.79,-17,-19.34,-25.08,-34.5,-39.75,-42.86,-41.87,-34.07,-28.01,-28.54,-29.89,-34.88,-40.86,-52.45,-53.32,-55.38,-50.54,-38.53,-36.33,-39.7,-42.6,-55.93,-59.65,-66.3,-57.89,-56.73,-45.9,-48.06,-44.33,-50.58,-52.44,-56.72,-66.51,-60.15,-56.58,-47.58,-33.97,-33.25,-37.21,-43.64,-47.32,-48.2,-47.4,-41.42,-28.37,-15.91,-10.44,-7.46,-15.74,-13.88,-14.44,-8.88,-8.52,-1.29,14.27,29.75,25.25,23.99,28.7,22.82,29.16,32.35,45.84,59.99,53.35,66.52,77.73,59.85,65.54,73.08,78.75,84.49,101.21,91.87,95.2,99.61,111.05,100.14,89.89,101.24,127.55,116.63,141.89,129.62,151.76,131.59,121.91,125.65,130.76,151.17,145.97,175.53,169.52,179.61,146.01,144.14,154.34,169.41,158.9,147.05,157.3,162.63,179.11,190.89,179.92,159.46,167.49,148.55,170.25,167.57,163.04,192.57,186.08,170.35,131.04,130.18,162.89,166.79,163.33,152.99,169.7,147.67,143.94,128.59,133.74,123.78,103.31,125.51,114.68,107.27,122.47,93.8,85.84,85.57,78.49,95.9,93.88,92.87,99.2,94.23,79.75,73.35,52.17,44.72,58.86,63.59,56.02,55.63,60.63,43.81,38.07,34.14,26.81,22.85,29.15,36.96,32.25,33.05,24.78,15.25,11.5,2.88,7.77,8.44,16.85,17.12,14.68,10.44,2.27,-4.81,-8.07,-9.88,-6.15,1.23,5.74,4.3,0.93,-6.5,-15.3,-19.22,-19.61,-15.94,-8.92,-4.63,-2.56,-6.14,-12.68,-19.45,-24.9,-26.12,-22.15,-15.56,-9.63,-7.28,-9.12,-14.74,-22.71,-27.74,-28.6,-25.94,-19.06,-12.82,-9.55,-10.46,-14.73,-21.23,-27.56,-28.76,-25.88,-20.03,-13.05,-8.73,-9.38,-11.81,-18.46,-25.37,-27.77,-25.31,-19.31,-13.32,-6.43,-6.48,-10.14,-15.85,-21.64,-25.19,-26.19,-19.22,-14.11,-6.87,-4.59,-6.28,-13.39,-20.5,-23.95,-23.33,-19.64,-11.3,-6.75,-4.94,-8.14,-11.64,-19.37,-26.06,-27.64,-24.73,-15.82,-9.89,-6.58,-9.71,-11.13,-22.75,-26.67,-30.43,-29.83,-21.15,-17.72,-12.91,-12.3,-13.15,-25.06,-29.89,-32.39,-31.4,-26.35,-22.86,-18.91,-20.82,-22.67,-25.53,-33.91,-34.86,-39.99,-32,-25.7,-21.48,-17.98,-27.7,-36.35,-42.76,-46.91,-44.78,-35.72,-33.74,-24.17,-25.21,-29.14,-33.13,-42.29,-42.19,-42.48,-46.42,-35.96,-35.72,-26.82,-25.61,-31.81,-38.01,-52.74,-52.2,-43.09,-44.63,-35.86,-24.23,-35.97,-33.96,-42.52,-53.14,-47.68,-38.5,-36.37,-30.6,-19.67,-22.26,-36.23,-37.23,-45.8,-54.14,-49.02,-33.94,-39.43,-20.22,-18.79,-25.42,-29,-34.97,-44.55,-38.42,-36.91,-39.35,-26.61,-25.16,-35.01,-35.1,-39.97,-45.48,-45.48,-42.34,-42.22,-29.72,-31.14,-30.39,-28.58,-32.6,-40.59,-43.34,-49.44,-30.95,-22.13,-29.91,-22.75,-33.78,-42.63,-51.6,-50.16,-45.49,-39.93,-35.33,-28.76,-32.98,-30.03,-30.42,-43.46,-52.39,-50.02,-45.72,-39.65,-19.53,-26.46,-36.4,-42.28,-46.37,-38.68,-39.37,-38.77,-29.79,-28.09,-26.79,-29.55,-27.24,-34.17,-38.55,-45.84,-30.46,-33.1,-21.89,-18.42,-18.23,-22.73,-28.57,-32.1,-34.48,-31.56,-21.05,-20.87,-13.17,-13.7,-19.37,-23.74,-33.31,-27.78,-23.44,-22.8,-14.42,-8.12,-10.3,-11.09,-17.12,-26.14,-21.42,-22.15,-18.19,-4.74</v>
       </c>
     </row>
     <row r="80">
@@ -1276,7 +1276,7 @@
         <v>[L_04_标记]</v>
       </c>
       <c r="C80" t="str">
-        <v>a: 23.4ms -36.7uv b: 48.4ms 158.9uv</v>
+        <v>a: 19.8ms -30.2uv b: 44.8ms 204.1uv</v>
       </c>
     </row>
     <row r="81">
@@ -1287,7 +1287,7 @@
         <v>[R_05_名字]</v>
       </c>
       <c r="C81" t="str">
-        <v>FERG(5)_Flicker</v>
+        <v>FERG(5)_dRod</v>
       </c>
     </row>
     <row r="82">
@@ -1298,7 +1298,7 @@
         <v>[R_05_放大器]</v>
       </c>
       <c r="C82" t="str">
-        <v>1-300 Hz</v>
+        <v>1-75 Hz</v>
       </c>
     </row>
     <row r="83">
@@ -1309,7 +1309,7 @@
         <v>[R_05_闪光]</v>
       </c>
       <c r="C83" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:1.0cd.m-2,5ms</v>
       </c>
     </row>
     <row r="84">
@@ -1320,7 +1320,7 @@
         <v>[R_05_闪光背景]</v>
       </c>
       <c r="C84" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="85">
@@ -1331,7 +1331,7 @@
         <v>[R_05_采样]</v>
       </c>
       <c r="C85" t="str">
-        <v>刺激间隔: 50.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="86">
@@ -1342,7 +1342,7 @@
         <v>[R_05_分析时间]</v>
       </c>
       <c r="C86" t="str">
-        <v>500 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="87">
@@ -1364,7 +1364,7 @@
         <v>[R_05_详细数据(uv)]</v>
       </c>
       <c r="C88" t="str">
-        <v>-7.27,-8.31,-11.99,-14.96,-14.65,-12.18,-11.09,-13.38,-17.27,-19.21,-17.87,-15.62,-15.9,-19.35,-23.07,-23.92,-22.01,-20.58,-22.38,-26.56,-29.62,-29.34,-27.26,-26.96,-30,-34.19,-36.02,-34.6,-32.64,-33.41,-37.03,-40.35,-40.46,-37.96,-36.24,-37.71,-41.05,-42.69,-40.81,-37.38,-35.93,-37.59,-39.81,-39.21,-35.4,-31.38,-30.21,-31.54,-32.03,-29.09,-23.81,-19.73,-18.87,-19.49,-18.05,-13.17,-7.24,-3.72,-3.26,-3.04,0.12,6.1,11.65,13.99,13.93,14.93,19.2,25.21,29.38,30.07,29.44,30.98,35.58,40.53,42.54,41.43,40.31,42.1,46.22,49.26,48.79,46.09,44.72,46.51,49.53,50.23,47.46,43.75,42.49,44.12,45.66,44.06,39.64,35.74,34.99,36.37,36.35,32.91,27.78,24.55,24.62,25.66,24.26,19.71,14.89,12.98,13.94,14.56,12.05,7.22,3.53,3.26,4.91,4.92,1.65,-2.77,-4.83,-3.59,-1.73,-2.55,-6.27,-9.78,-10.14,-7.9,-6.48,-8.32,-12.19,-14.54,-13.5,-11.02,-10.64,-13.56,-17.28,-18.43,-16.53,-14.57,-15.64,-19.45,-22.68,-22.7,-20.53,-19.67,-22.21,-26.43,-28.78,-27.82,-25.84,-26.31,-29.92,-33.86,-34.92,-33.09,-31.59,-33.2,-37.17,-40,-39.41,-36.86,-35.89,-38.16,-41.56,-42.56,-40.19,-37.08,-36.55,-38.82,-40.8,-39.53,-35.51,-32.13,-31.87,-33.51,-33.5,-29.95,-24.77,-21.52,-21.41,-21.97,-19.84,-14.51,-8.96,-6.29,-6.28,-5.63,-1.7,4.52,9.48,11.09,10.98,12.7,17.71,23.69,27.17,27.38,27.1,29.55,34.71,39.38,40.71,39.44,39.01,41.72,46.13,48.67,47.64,45.13,44.65,47.22,50.18,50.23,47.11,43.89,43.57,45.67,46.82,44.53,40.01,36.82,36.89,38.36,37.68,33.64,28.69,26.26,26.88,27.63,25.41,20.46,16.07,14.93,16.11,16.11,12.8,7.83,4.78,5.14,6.65,5.84,1.93,-2.3,-3.61,-1.97,-0.57,-2.25,-6.32,-9.33,-8.95,-6.6,-5.86,-8.44,-12.3,-13.92,-12.27,-9.98,-10.39,-13.8,-17.16,-17.48,-15.2,-13.72,-15.55,-19.53,-22.12,-21.38,-19.14,-18.97,-22.14,-26.21,-27.77,-26.25,-24.56,-25.83,-29.86,-33.36,-33.63,-31.57,-30.68,-33.1,-37.2,-39.41,-38.2,-35.8,-35.67,-38.62,-41.87,-42.17,-39.45,-36.85,-37.25,-39.95,-41.52,-39.6,-35.56,-32.96,-33.55,-35.31,-34.69,-30.64,-25.77,-23.41,-23.92,-24.24,-21.39,-15.78,-10.79,-8.99,-9.24,-8.01,-3.37,2.87,7.12,8.07,8.1,10.64,16.24,21.99,24.73,24.6,24.85,28.2,33.73,37.95,38.65,37.41,37.8,41.35,45.84,47.77,46.31,44.19,44.66,47.84,50.56,49.95,46.66,44.11,44.7,47.08,47.71,44.81,40.41,38.04,38.82,40.18,38.78,34.28,29.71,28.12,29.14,29.42,26.41,21.24,17.45,17.04,18.24,17.49,13.48,8.59,6.26,7.12,8.29,6.62,2.23,-1.62,-2.19,-0.34,0.44,-2.05,-6.27,-8.65,-7.62,-5.37,-5.41,-8.62,-12.27,-13.1,-11,-9.1,-10.31,-14.04,-16.87,-16.39,-13.93,-13.07,-15.6,-19.55,-21.39,-19.98,-17.89,-18.48,-22.14,-25.86,-26.59,-24.67,-23.45,-25.51,-29.76,-32.67,-32.2,-30.11,-29.94,-33.07,-37.1,-38.59,-36.88,-34.82,-35.57,-39.03,-41.94,-41.54,-38.64,-36.72,-37.99,-40.93,-41.96,-39.46,-35.61,-33.89,-35.22,-36.88,-35.59,-31.2,-26.82,-25.4,-26.34,-26.26,-22.72,-17.03,-12.76,-11.76,-12.07,-10.17,-4.93,1.11,4.57,4.99,5.36,8.72,14.74,20.07,22.07,21.78,22.72,26.91,32.61,36.23,36.38,35.38,36.67,40.93,45.29,46.57,44.83,43.28,44.72,48.33,50.65,49.42,46.15,44.42,45.85,48.31,48.31,44.93,40.85,39.38,40.73,41.79,39.66,34.88,30.88,30.12,31.34,31.01,27.29,22.11,19.03,19.25,20.27,18.71,14.14,9.52,7.96,9.16,9.81,7.29,2.6,-0.71,-0.58,1.28,1.31,-1.92,-6.09,-7.75,-6.19,-4.25,-5.13,-8.8,-12.06,-12.11</v>
+        <v>-2.34,4.63,13.19,12.63,3.65,-2.46,2,11.53,14.32,7,-1.12,0.3,9.66,15.47,10.68,1.53,-0.28,7.79,15.92,14.23,5.13,0.33,6.13,15.61,17.22,9.26,2.02,4.87,14.55,19.26,13.39,4.58,4.13,12.87,20.11,17.02,7.69,3.97,10.7,19.59,19.68,10.9,4.36,8.32,17.79,20.93,13.82,5.23,5.8,14.75,20.63,16.09,6.34,3.48,10.89,18.51,16.94,7.6,1.36,5.97,15.11,16.89,7.98,-0.39,1.22,10.09,14.27,8.83,-1.36,-3.88,4.61,11.1,7.08,-3.94,-6.76,-3.1,5.88,4.11,-5.37,-12.3,-8.14,-1.02,2.36,-6.95,-15.27,-13.72,-8.9,-3.53,-7.01,-16.64,-23.41,-10.48,-8.87,-2.49,-15.1,-20.64,-14.31,-6.07,-2.33,-13.66,-17.62,-13.58,-11.41,-4.8,-8.63,-14.71,-17.36,-9.77,-0.21,-0.18,-10.32,-10.44,0.64,7.6,10.45,4.02,2.08,6.98,25.38,24.54,18.12,12.09,16.67,26.7,39.51,40.48,36.72,34.96,50.68,57.52,51.29,47.67,54.23,65.19,76.94,83.02,75.09,68.63,72.23,86.94,88.36,95.61,87.94,94.74,100.26,113.1,118.55,116.71,101.37,103.38,144.34,147.31,134.92,110.81,142.83,137.68,144.07,139.28,144.39,125.75,139.58,174.81,153.42,160.13,171.22,168.99,178.12,170.47,172.85,146.05,168.65,164.02,199.1,181.17,152.44,164.96,184.01,166.37,165.22,183.12,162.72,156,204.3,178.46,182.98,161.59,173.69,194.8,195.67,158.4,178.85,152.52,175.69,165.22,182.49,165.17,161.61,147.19,151.11,144.29,150.27,127.92,147.5,162.04,141.16,127.78,126.41,139.65,145.25,134.16,135.66,111.57,114.24,130.08,121.9,108.41,102.84,88.39,100.77,97.47,107.5,92.58,77.66,92.18,91.55,88.73,86.7,63.89,73.91,71.28,71.32,67.46,62.66,51.18,61.48,60.78,54.03,45.55,43.35,44.19,46.35,49.19,40.89,29.17,27.4,38.73,38.37,30.27,19.78,20.52,28.55,31.68,25.56,16.37,12.74,15.22,23.89,22.45,12.74,5.35,8.08,16.71,19.48,10.72,3.01,2.68,10.61,16.02,11.62,1.87,-1.44,5.91,12.92,11.88,1.93,-3.92,1.25,9.54,11.99,3.91,-3.49,-2.14,7.7,12.25,6.7,-3.09,-4.09,4.48,12.65,9.68,-0.69,-4.49,1.65,10.23,11.55,3.97,-4.6,0.19,8.91,12.57,6.06,-3.46,-2.83,5.23,11.46,8.7,-1.29,-4.3,2.64,9.58,8.4,0.31,-6.28,-2.82,7.04,11.36,0.54,-5.38,-3.07,2.82,10.2,4.14,-4.32,-10.56,-1.57,5.49,1.17,-4.75,-10.59,-7.14,3.23,3.49,-9.39,-14.47,-9.51,-4.04,-1.78,-3.82,-18.95,-15.89,-5.66,0.46,-3.96,-13.85,-24.04,-12.28,-8.19,-2.53,-15.25,-24.4,-16.07,-14.7,-8.61,-18.21,-24.81,-26.81,-11.22,-9.82,-17.19,-20.36,-25.44,-13.69,-11.35,-12.11,-26.36,-30.16,-18.66,-12.24,-5.13,-15.27,-21.49,-19.79,-12.03,-6.33,-19.78,-25.96,-33.7,-19.34,-13.14,-12.14,-28.72,-34.83,-21.82,-8.27,-4.84,-21.15,-25.38,-26.17,-19.84,-4.28,-15.26,-20.19,-18.79,-14.2,-7.38,-21.96,-17.13,-27.27,-14.11,-15.18,-13.64,-14.84,-24.6,-26.11,-16.23,-12.69,-17.8,-30.59,-30.49,-17.48,-18.35,-22.01,-20.81,-33.5,-15.99,-6.81,-22.42,-22.81,-25.28,-17.53,-22.53,-22.59,-32.03,-35.73,-22.47,-14.26,-18.24,-21.11,-32.22,-27.84,-27.26,-14.32,-25.63,-29.73,-29.33,-19.47,-23.47,-21.47,-22.13,-30.03,-25.19,-14.42,-11.31,-23.54,-24.04,-31.18,-18.18,-17.17,-23.77,-33.3,-25.62,-15.5,-8.27,-10.3,-17.84,-23.15,-20.07,-15.8,-11.08,-18.03,-28.66,-18.88,-16.4,-6.36,-14.15,-15.96,-23.12,-7.41,-4.15,-5.31,-16.31,-20.5,-9.6,0.93,-2.21,-11.32,-14.61,-13.96,-5.2,5.19,-4.96,-9.8,-11.88,-4.68,1.16,0.01,-11.65,-12.09,-2.15,3.03,6.29,-4.48,-8.44,-5.92,2.85,5.09,-0.2,-9.4,-5.57,1.99</v>
       </c>
     </row>
     <row r="89">
@@ -1375,7 +1375,7 @@
         <v>[R_05_标记]</v>
       </c>
       <c r="C89" t="str">
-        <v>幅值: 37.7uv 相位: 50°</v>
+        <v>a: 21.9ms -21.5uv b: 48.9ms 135.4uv</v>
       </c>
     </row>
     <row r="90">
@@ -1386,7 +1386,7 @@
         <v>[L_05_名字]</v>
       </c>
       <c r="C90" t="str">
-        <v>FERG(5)_Flicker</v>
+        <v>FERG(5)_dRod</v>
       </c>
     </row>
     <row r="91">
@@ -1397,7 +1397,7 @@
         <v>[L_05_放大器]</v>
       </c>
       <c r="C91" t="str">
-        <v>1-300 Hz</v>
+        <v>1-75 Hz</v>
       </c>
     </row>
     <row r="92">
@@ -1408,7 +1408,7 @@
         <v>[L_05_闪光]</v>
       </c>
       <c r="C92" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:1.0cd.m-2,5ms</v>
       </c>
     </row>
     <row r="93">
@@ -1419,7 +1419,7 @@
         <v>[L_05_闪光背景]</v>
       </c>
       <c r="C93" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="94">
@@ -1430,7 +1430,7 @@
         <v>[L_05_采样]</v>
       </c>
       <c r="C94" t="str">
-        <v>刺激间隔: 50.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="95">
@@ -1441,7 +1441,7 @@
         <v>[L_05_分析时间]</v>
       </c>
       <c r="C95" t="str">
-        <v>500 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="96">
@@ -1463,7 +1463,7 @@
         <v>[L_05_详细数据(uv)]</v>
       </c>
       <c r="C97" t="str">
-        <v>-13.23,-16.25,-20.15,-18.7,-15.42,-17.15,-21.52,-21.32,-17.7,-18.09,-22.59,-23.79,-20.36,-19.49,-23.72,-26.29,-23.53,-21.58,-25.14,-28.84,-27.1,-24.31,-26.81,-31.25,-30.72,-27.39,-28.54,-33.17,-33.86,-30.31,-29.9,-34.14,-35.88,-32.41,-30.39,-33.65,-36.14,-33.02,-29.5,-31.28,-34.12,-31.56,-26.79,-26.77,-29.49,-27.64,-22.02,-20.06,-22.23,-21.17,-15.19,-11.39,-12.64,-12.37,-6.6,-1.26,-1.35,-1.79,3.23,9.6,10.77,9.75,13.54,20.31,22.69,21.27,23.47,29.94,33.32,31.72,32.15,37.65,41.71,40.16,38.82,42.79,47.11,45.84,42.92,44.96,49.11,48.3,44.16,44.09,47.65,47.42,42.58,40.43,43.04,43.45,38.47,34.52,35.9,36.94,32.4,27.09,27.1,28.65,25.04,18.97,17.59,19.44,17.14,10.95,8.28,10.18,9.39,3.69,-0.04,1.61,2.32,-2.36,-6.84,-5.75,-3.76,-7.01,-11.9,-11.63,-8.72,-10.36,-15.26,-16.01,-12.68,-12.69,-17.23,-19.11,-15.91,-14.46,-18.31,-21.26,-18.72,-16.14,-19.04,-22.89,-21.44,-18.16,-19.91,-24.36,-24.28,-20.77,-21.27,-25.91,-27.28,-24,-23.25,-27.59,-30.29,-27.63,-25.72,-29.27,-32.98,-31.2,-28.3,-30.62,-34.87,-34.1,-30.45,-31.2,-35.4,-35.63,-31.54,-30.5,-34.08,-35.15,-30.95,-28.12,-30.54,-32.2,-28.21,-23.77,-24.62,-26.54,-23.08,-17.39,-16.45,-18.29,-15.63,-9.19,-6.45,-7.9,-6.21,0.34,4.69,3.9,4.51,10.54,16.09,16.12,15.66,20.58,26.77,27.69,26.28,29.58,35.79,37.55,35.4,36.78,42.36,44.81,42.21,41.55,45.92,48.84,46.12,43.55,46.27,49.37,46.88,42.72,43.52,46.49,44.55,39.3,38.12,40.67,39.51,33.78,30.78,32.63,32.39,26.83,22.34,23.28,23.99,19.2,13.69,13.58,15.11,11.58,5.62,4.41,6.51,4.55,-1.28,-3.56,-1.22,-1.5,-6.68,-9.9,-7.72,-6.43,-10.53,-14.48,-12.86,-10.32,-13.05,-17.46,-16.77,-13.43,-14.65,-19.21,-19.69,-16.1,-15.86,-20.23,-21.99,-18.71,-17.19,-21.01,-24,-21.53,-19.02,-21.99,-25.98,-24.69,-21.54,-23.41,-28.01,-28.09,-24.7,-25.28,-29.99,-31.43,-28.18,-27.37,-31.64,-34.24,-31.43,-29.28,-32.55,-35.94,-33.79,-30.43,-32.23,-35.93,-34.57,-30.25,-30.27,-33.72,-33.17,-28.25,-26.33,-29.01,-29.2,-24.08,-20.31,-21.8,-22.56,-17.7,-12.37,-12.37,-13.5,-9.32,-2.92,-1.31,-2.59,0.55,7.41,10.52,9.33,11.16,17.78,22.14,21.24,21.62,27.34,32.51,32.06,31.01,35.24,40.7,40.81,38.49,40.81,45.99,46.69,43.42,43.6,47.98,49.24,45.42,43.5,46.62,48.33,44.42,40.65,42.2,44.22,40.69,35.51,35.35,37.46,34.73,28.74,26.89,28.86,27.23,21.09,17.74,19.34,18.96,13.33,8.82,9.8,10.67,6.1,0.85,1.04,2.96,-0.13,-5.64,-6.38,-3.76,-5.15,-10.44,-12.18,-9.28,-8.99,-13.62,-16.34,-13.66,-11.88,-15.52,-19.08,-17.1,-14.21,-16.63,-20.8,-19.92,-16.41,-17.49,-21.97,-22.43,-18.84,-18.6,-23.02,-24.89,-21.73,-20.31,-24.26,-27.41,-25.1,-22.71,-25.8,-29.92,-28.74,-25.66,-27.55,-32.15,-32.22,-28.75,-29.18,-33.71,-34.94,-31.41,-30.24,-34.09,-36.26,-32.94,-30.2,-32.82,-35.56,-32.71,-28.57,-29.54,-32.4,-30.2,-24.98,-24.06,-26.59,-25.15,-19.31,-16.46,-18.25,-17.59,-11.66,-7.09,-7.82,-7.92,-2.45,3.45,3.96,3.21,7.69,14.34,16.11,14.88,17.96,24.67,27.58,26.07,27.45,33.56,37.33,35.75,35.35,40.2,44.47,43.06,40.96,44.07,48.4,47.36,43.84,44.91,48.86,48.35,43.84,42.78,45.95,46.06,41.11,38.07,40.14,40.88,36.06,31.41,32.16,33.47,29.33,23.59,22.93,24.66,21.64,15.43,13.41,15.32,13.72,7.68,4.47,6.27,6.2,0.92,-3.23,-1.83,-0.48,-4.53,-9.26,-8.56,-6.08,-8.59,-13.54,-13.76,-10.59,-11.45,-16.23,-17.53,-14.2,-13.48</v>
+        <v>14.35,11.36,13.73,18.97,21.71,19.11,13.75,11.01,13.64,18.96,21.59,18.87,13.58,11.1,13.98,19.36,21.87,19.03,13.81,11.58,14.69,20.11,22.46,19.49,14.32,12.32,15.63,21.05,23.22,20.09,14.96,13.15,16.64,22.01,23.97,20.64,15.51,13.86,17.47,22.74,24.46,20.9,15.7,14.18,17.8,22.98,24.36,20.66,15.4,13.89,17.71,22.47,23.43,19.39,13.9,12.36,16.12,20.5,21.42,16.5,11.87,9.79,14.09,18.32,18.64,13.73,6.48,6.15,10.02,13.84,13.98,7.98,2.53,0.57,3.42,8.53,7.56,-1.13,-2.53,-6.48,-5.39,4.09,1.39,-8.57,-7.81,-11.76,-10.27,-5.12,-7.55,-9.01,-10.38,-14.79,-11.29,-7.44,-11.31,-6.93,-16.83,-15.19,-14.88,0.11,0.53,-4.03,-13.08,-11.55,3.7,6,9.67,4.05,7.44,2.26,12.52,21.62,21.83,16.04,14.12,22.07,27.94,35.18,41.74,42.61,41.5,48.9,54.48,65.65,68.68,56.92,63.74,69.55,71.33,92.62,94.92,81.08,91.75,99.92,98.65,106.96,121.26,114.4,111.91,108.09,121.27,145.53,141.07,139.9,118.31,144.16,151.75,145.6,143.58,147.92,165.83,165.12,174.08,187.5,172.28,176.35,153.69,171.16,171.96,199.82,196.01,180.47,166.41,159.79,171.2,177.85,186.42,192.87,169.52,177.1,204.42,179.28,186.41,178.07,173.38,184.24,163.09,185.02,196.74,176.44,166.08,152.78,158.82,161.1,178.15,165.59,146.89,170.42,145.87,155.57,165.22,126.57,145.01,139.57,127.29,127.2,137.91,109.11,109.34,106.48,122.4,124.57,106.39,94.61,95.51,91.92,102.09,90.6,85.83,91.52,85.32,87.09,85.98,79.61,70.21,67.56,64.13,60.22,66.01,65.5,56.6,49.76,52.29,49.32,50.65,50.27,45.45,36.7,34.52,40.99,43.18,41.7,37.9,29.97,28.6,30.41,32.19,31.99,27.24,20.02,19.37,24.19,26.6,27.33,20.18,15.43,14.15,19.07,22.6,21.98,15.37,10.92,10.03,15.03,18.23,17.83,11.84,7.06,7,12.06,15.3,14.22,8.49,4.56,5,9.67,13.45,12.32,6.52,2.89,3.32,8.63,11.4,10.18,5.87,1.18,3.18,7.51,11.41,9.34,4.47,0.43,2.44,8.17,10.63,8.49,4.3,-0.06,2.79,6.25,10.1,8.5,4.83,1.03,2.51,7.3,9.36,9.35,3.58,-0.47,1.12,7.93,9.33,6.5,4.38,0.45,2.57,7.95,10.16,7.88,2.47,-0.37,2.84,6.06,7.11,7.81,0.38,-5,0.15,6.65,3.63,4.52,0.7,-2.62,0.63,1.32,7.2,2.88,-4.95,-5.56,-4.04,-3.39,1.66,-5.7,-9.83,-13.71,-10.97,-1.38,1.16,-6.74,-8.24,-8.97,-10.05,-10.28,-7.66,-8.2,-10.4,-14.07,-18.07,-10.12,-8.75,-10.67,-20.84,-16.75,-17.58,-16.22,-14.21,-12.89,-23.69,-15.48,-23.66,-14.93,-10.35,-20.68,-19.74,-16.85,-24.1,-20.36,-18.5,-17.42,-20.97,-17.23,-22.29,-12.38,-13.32,-13.3,-28.95,-24.5,-23.37,-21.7,-8.99,-20.7,-20.94,-20.1,-20.37,-17.75,-7.31,-20.52,-19.04,-19.23,-16.71,-14.99,-11.67,-15.7,-30.88,-17.33,-14.32,-21.15,-9.24,-24.85,-31.27,-25.24,-22.63,-20.2,-10.55,-25.19,-29.14,-24.8,-19.08,-14.48,-21.01,-20.35,-30.6,-24.17,-23.3,-7.54,-15.72,-26.54,-29.71,-27.61,-16.02,-19.89,-18.84,-14.34,-17.57,-15.88,-22.13,-19.79,-11.17,-14.77,-18.42,-21.41,-13.22,-19.71,-13.83,-19.39,-29.39,-27.28,-11.67,-10.43,-9.22,-21.63,-21.69,-21.45,-19.61,-7.11,-11.08,-22.25,-19.69,-17,-12.63,-5.21,-10.67,-12.85,-19.73,-13.69,-14.02,-5.87,-12.98,-15.12,-14.4,-18.69,-10.68,-5.83,-11.14,-9.01,-14.3,-12.66,-7.65,-1.09,-5.86,-8.18,-10.23,-6.99,-4.54,-2.21,-2.19,-7.62,-8.61,-5.57,-0.82,1.95,-2.01,-4.86,-9.28,-3.62,2.62,2.52,1.29,-2.43,-7.01,-2.22,1.43,4.27,1,-5.83,-8.17,-2.52,3.31,6.14</v>
       </c>
     </row>
     <row r="98">
@@ -1474,12 +1474,3774 @@
         <v>[L_05_标记]</v>
       </c>
       <c r="C98" t="str">
-        <v>幅值: 35.4uv 相位: 50°</v>
+        <v>a: 21.9ms -19.6uv b: 48.8ms 174.3uv</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B99" t="str">
+        <v>[R_06_名字]</v>
+      </c>
+      <c r="C99" t="str">
+        <v>FERG(6)_dRod</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B100" t="str">
+        <v>[R_06_放大器]</v>
+      </c>
+      <c r="C100" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B101" t="str">
+        <v>[R_06_闪光]</v>
+      </c>
+      <c r="C101" t="str">
+        <v>b白色光:3.0cd.m-2,4ms</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B102" t="str">
+        <v>[R_06_闪光背景]</v>
+      </c>
+      <c r="C102" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B103" t="str">
+        <v>[R_06_采样]</v>
+      </c>
+      <c r="C103" t="str">
+        <v>刺激间隔:2.0S</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B104" t="str">
+        <v>[R_06_分析时间]</v>
+      </c>
+      <c r="C104" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B105" t="str">
+        <v>[R_06_数据长度]</v>
+      </c>
+      <c r="C105" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B106" t="str">
+        <v>[R_06_详细数据(uv)]</v>
+      </c>
+      <c r="C106" t="str">
+        <v>-8.28,-24.43,-14.17,3.05,-5.92,-22.53,-13.15,4.61,-3.39,-20.45,-12.01,6.21,-0.82,-18.32,-10.87,7.71,1.63,-16.28,-9.88,8.98,3.84,-14.46,-9.16,9.9,5.69,-12.97,-8.81,10.37,7.08,-11.9,-8.9,10.34,7.97,-11.28,-9.45,9.77,8.34,-11.12,-10.47,8.69,8.21,-11.39,-11.91,7.16,7.64,-12.02,-13.68,5.26,6.73,-12.91,-15.67,3.11,5.59,-13.93,-17.76,0.84,4.36,-14.95,-19.8,-1.41,3.16,-15.85,-21.69,-3.53,2.12,-16.51,-23.27,-5.42,1.31,-16.83,-24.6,-6.99,0.76,-16.87,-25.43,-8.38,0.39,-16.58,-26.12,-9.26,0.35,-16.49,-26.98,-10.79,-0.54,-15.76,-28.07,-12.41,-0.1,-15.49,-29.73,-14,-1.2,-17.23,-29.86,-15.31,-4.98,-20.54,-34.29,-18.77,-8.21,-19.05,-33.67,-26.17,-11.07,-20.37,-35.84,-27.26,-17.79,-23.57,-45.77,-27.3,-19.92,-26.19,-42.12,-38.1,-20.82,-32.28,-38.68,-34.07,-16.35,-23.44,-47.77,-26.71,-11.93,-16.79,-36.09,-29.73,-3.69,-7.53,-24.59,-18.3,-1.43,-1.95,-15.2,-7.78,10.51,7.74,-9.1,5.29,22.86,26.55,10.42,10.63,35.93,31.86,18.81,22.48,54.36,44.7,43.69,36.16,58.91,74.07,50.84,59.82,83.41,89.89,68.39,79.27,90.01,100.67,100.31,94.03,109.64,129.23,120,93.69,144.53,132.11,118.49,141.35,149.49,141.97,151.42,128.47,174.88,167.31,169.36,152.74,173.43,190.33,155.54,152.6,182.99,207.36,158.11,161.28,212.87,192.18,198.68,177.33,189.87,198.84,168.69,174.34,178.39,190.06,184.35,187.5,176.15,178.75,170.92,156.66,163.99,165.95,160.85,153.45,175,152.23,155.92,123.29,125.93,151.06,147.84,113.3,118.28,140.06,102.89,105.12,95.28,103.97,89.5,83.9,79.46,102.91,87.48,53.79,73.87,79.01,64.49,42.31,51.3,58.94,47.64,30.34,41.13,54.61,43.69,14.79,22.84,35.53,28.25,11.96,14.46,28.9,22.21,0.48,4.62,24.05,16.71,-4.14,0.11,15.61,11.58,-8.32,-6.3,12.43,8.23,-11.13,-8.73,10.51,8.3,-11.01,-10.42,9.23,7.4,-12,-11.06,8.55,8.49,-10.5,-10.7,9.06,9.98,-8.77,-9.91,9.57,11.68,-6.97,-9.41,9.92,13.02,-5.3,-8.99,10.81,14.82,-3.59,-8.49,11.09,15.09,-2.69,-8.62,10.26,16.82,-2.07,-8.93,10.2,16.81,-1.38,-9.12,7.57,15.66,-1.89,-11.47,6.04,14.26,-1.73,-13.53,4.18,12.08,-4.71,-13.33,0.18,12.08,-6.04,-15.95,-1.78,7.56,-5.57,-18.37,-6.5,5.05,-9.64,-23.38,-7.17,6.3,-9.73,-25.52,-11.45,3.02,-10.48,-26.18,-13.63,-0.32,-10.59,-25.91,-19.56,-3.84,-12.81,-29.01,-15.43,-2.93,-12.84,-29.53,-20.23,-5.47,-15.91,-30.41,-23.03,-5.82,-16.76,-27.59,-17.83,-0.92,-16.52,-31.5,-21.41,-5.77,-7.79,-25.35,-18.43,-7.51,-10.48,-30.26,-21.57,-4.33,-10.58,-29.35,-21.16,-7.18,-8.4,-21.23,-24.02,-0.42,-8.98,-22.02,-18.09,-4.48,-8.95,-26.55,-18.17,-5.59,0.11,-21.97,-30.8,-11.85,-0.56,-28.99,-22.2,-8.32,-4.91,-33.71,-27.35,-15.7,-9.88,-30.55,-38.54,-15.61,-3.04,-31.5,-38.95,-22.35,-10.33,-39.63,-45.28,-26.56,-12.13,-27.05,-47.76,-19.26,-21.15,-35.29,-48.57,-26.42,-13.46,-39.51,-50.22,-26.49,-21.34,-37.99,-38.1,-30.17,-11.7,-36.78,-54.24,-22.88,-17.84,-28.09,-50.2,-22.94,-23.89,-35,-47.17,-23.89,-25.27,-29.25,-44.14,-25.3,-9.83,-25.59,-37.28,-32.53,-9.68,-22.03,-38.88,-28.99,-15.29,-19.56,-33.69,-24.44,-11.14,-13.58,-30.22,-27.82,-12.74,-20.66,-26.04,-14.76,1.55,-13.05,-29.17,-23.39,4.81,-7.57,-26.13,-15.41,-1.73,-3.02,-17.97,-11.54,8.17,0.99,-21.75,-13.06,4.11,3,-24.47,-9.97,6.57,0.71,-21.75,-14.56,9.33,1.47,-20.02,-14.58,6.81,-1.66,-14.32,-15.95,4.26,0.16,-15.29,-16.91,3.5,5.32,-14.22,-15.16,1.37</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B107" t="str">
+        <v>[R_06_标记]</v>
+      </c>
+      <c r="C107" t="str">
+        <v>a: 24.4ms -26.1uv b: 51.9ms 179.4uv</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B108" t="str">
+        <v>[L_06_名字]</v>
+      </c>
+      <c r="C108" t="str">
+        <v>FERG(6)_dRod</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B109" t="str">
+        <v>[L_06_放大器]</v>
+      </c>
+      <c r="C109" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B110" t="str">
+        <v>[L_06_闪光]</v>
+      </c>
+      <c r="C110" t="str">
+        <v>b白色光:3.0cd.m-2,4ms</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B111" t="str">
+        <v>[L_06_闪光背景]</v>
+      </c>
+      <c r="C111" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B112" t="str">
+        <v>[L_06_采样]</v>
+      </c>
+      <c r="C112" t="str">
+        <v>刺激间隔:2.0S</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B113" t="str">
+        <v>[L_06_分析时间]</v>
+      </c>
+      <c r="C113" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B114" t="str">
+        <v>[L_06_数据长度]</v>
+      </c>
+      <c r="C114" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B115" t="str">
+        <v>[L_06_详细数据(uv)]</v>
+      </c>
+      <c r="C115" t="str">
+        <v>-16.59,-20.52,-6.67,1.69,-9.32,-20.46,-12.25,1.78,-1.8,-16.34,-16.46,-1.38,3.75,-9.24,-17.56,-6.4,5.8,-1.18,-14.82,-11.23,4.04,5.49,-8.8,-13.91,-0.6,8.88,-1.2,-13.21,-6.25,8.15,5.73,-9.11,-10.79,3.74,9.83,-2.81,-12.53,-2.74,9.82,3.63,-10.91,-9.11,5.68,7.98,-6.55,-13.39,-1.41,8.63,-1.06,-14.33,-9.28,5.04,3.33,-12.32,-15.97,-2.49,4.59,-8.04,-19.27,-10.88,1.41,-3.89,-19.17,-19.08,-4.97,-2.51,-16.48,-24.7,-14.39,-4.68,-14.16,-28.81,-26.13,-12.14,-10.32,-28.84,-31.41,-21.89,-11.9,-24.99,-36.39,-30.19,-17.38,-19.67,-38.14,-35.61,-23.82,-19.41,-36.75,-47.2,-33.14,-20.64,-30.01,-46.5,-44.34,-26.09,-20.02,-39.52,-48.65,-26.55,-21.35,-27.23,-38.07,-40.84,-17.52,-16.66,-33.29,-29.74,-13.35,0.04,-16.33,-22.33,-13.64,6.34,3.09,-19.15,-15.06,8.94,11.6,6.2,0.36,9.52,31.68,28.91,13.19,26.01,45.08,39.64,34.98,35.8,54.63,63.04,54.07,51.49,70.75,79.81,89.34,82.93,65.2,87.52,88.6,80.36,84.11,107.83,104.71,123.88,93.15,98.67,142.51,144.36,122.88,105.91,128.94,152.01,153.42,145.04,160.82,141.43,142.36,159.14,162.25,166.58,189.77,149.41,174.41,158.32,202.29,191.16,155.72,178.99,189.48,186.22,154.7,148.05,162.14,185.23,202.09,175.67,159.23,168.53,169.06,168.79,155.7,193.25,167.05,161.87,161.22,147.33,162.16,174.86,157.48,158.76,164.35,186,160.55,126.12,133.45,148.49,155.3,146.91,142.67,152.39,137.63,115.19,110.63,138.83,125.19,122.17,97.21,117.88,111.12,106.78,99.9,76.71,90.44,95.02,72.48,68.9,82.53,88.51,71.81,55.67,57.6,62.44,69.17,49.36,45.1,49.64,62.98,47.64,25.91,35.71,43.13,40.34,20.15,16.57,32.87,31.25,17.1,7.81,15.46,26.19,14.93,1.4,1.92,15.38,17.87,1.01,-6.81,3.36,13.52,2.16,-11.35,-6.58,6.73,4.24,-13,-15.26,-2.16,4.31,-9.05,-18.55,-10.22,1.38,-3.71,-17.71,-18.3,-3.68,0.4,-13.98,-21.1,-9.9,1.01,-7.8,-20.54,-15.64,-0.93,-1.84,-16.05,-20.23,-6.83,2.76,-8.96,-20.29,-12.86,2.04,-2.15,-16.16,-16.48,-2.58,2.81,-10.64,-18.34,-9.27,3.26,-4.62,-16.89,-13.39,-0.64,2.5,-14.85,-18.85,-7.31,3.62,-8.79,-20.72,-15.77,0.77,-4.31,-19.42,-21.08,-7.71,-0.88,-14.09,-25.08,-17.14,-1.18,-9.53,-26.35,-22,-6.63,-8.14,-20.65,-31.25,-15.98,-9.53,-16.2,-31.91,-25.13,-10.48,-11.86,-30.99,-30.57,-24.53,-16.43,-23.78,-34.16,-27.83,-18.17,-24.2,-36.86,-35.06,-18.58,-15.47,-32.93,-43.12,-33.88,-21.1,-33.75,-40.05,-37.69,-27.53,-22.35,-37.34,-46.84,-28.39,-26.71,-33.92,-49.65,-33.62,-17.37,-26.06,-35.95,-47.59,-34.16,-21.18,-34.39,-38.69,-32.94,-22.32,-34.25,-48.85,-41.98,-23.02,-22.55,-45.16,-39.38,-27.92,-16.24,-29.74,-50.05,-42.78,-25.31,-24.6,-35.71,-36.33,-29.11,-14.85,-31.28,-52.69,-32.27,-17.05,-25.57,-50.55,-50.38,-26.1,-31.28,-36.87,-51.24,-40.09,-22.7,-39.49,-45.4,-45.45,-33.53,-29.74,-50.51,-56.89,-38.12,-32.97,-47.75,-42.33,-42.95,-28.75,-25.83,-49.08,-50.74,-34.03,-33.55,-45.6,-51.48,-37.55,-32.37,-33.74,-53.01,-46.93,-35.23,-31.49,-46.09,-53.86,-37.49,-29.82,-41.91,-54.1,-48.54,-32.31,-29.75,-41.53,-49.52,-39.84,-25.83,-37.17,-47.73,-36.81,-29.84,-30.07,-41.68,-48.01,-31.69,-25.43,-39.7,-43.52,-25.03,-18.77,-31.67,-42.65,-36.58,-22.95,-21.92,-30.26,-31.84,-18.47,-10.12,-24.79,-38.76,-23,-16.38,-17.27,-29.11,-34.1,-13.11,-11.12,-23.74,-34.81,-19.14,-7.61,-19.91,-27.36,-21.38,-8.49,-5.7,-23.05,-29.42,-15.35,-3.26,-14.89,-24.21,-15.79,-5.1,-11.52,-26.39,-25.25,-7.43,-4.92,-19.55,-29.56,-17.38,-6.08,-14.16,-27.87</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B116" t="str">
+        <v>[L_06_标记]</v>
+      </c>
+      <c r="C116" t="str">
+        <v>a: 24.5ms -29.2uv b: 51.7ms 208.9uv</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B117" t="str">
+        <v>[R_07_名字]</v>
+      </c>
+      <c r="C117" t="str">
+        <v>FERG(7)_dMax</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B118" t="str">
+        <v>[R_07_放大器]</v>
+      </c>
+      <c r="C118" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B119" t="str">
+        <v>[R_07_闪光]</v>
+      </c>
+      <c r="C119" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B120" t="str">
+        <v>[R_07_闪光背景]</v>
+      </c>
+      <c r="C120" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B121" t="str">
+        <v>[R_07_采样]</v>
+      </c>
+      <c r="C121" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B122" t="str">
+        <v>[R_07_分析时间]</v>
+      </c>
+      <c r="C122" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B123" t="str">
+        <v>[R_07_数据长度]</v>
+      </c>
+      <c r="C123" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B124" t="str">
+        <v>[R_07_详细数据(uv)]</v>
+      </c>
+      <c r="C124" t="str">
+        <v>-1.74,11.15,11.61,-1.04,7.85,14.8,1.53,4.28,16.03,5.45,1.41,15.1,9.83,0.01,12.28,13.64,0.47,8.3,15.96,2.69,4.13,16.19,6.09,0.78,14.24,9.76,-1.02,10.5,12.72,-0.91,5.77,14.1,0.93,1.09,13.41,3.9,-2.57,10.64,7.08,-4.51,6.27,9.48,-4.42,1.18,10.25,-2.59,-3.6,9.01,0.24,-7.17,5.71,3.15,-9.18,0.82,4.9,-9.05,-4.56,5.41,-7.28,-10.19,3.41,-5.09,-13.81,-1.56,-4.75,-15.83,-9.68,-2.13,-19.91,-16.5,-4.66,-19.29,-23.41,-11.41,-17.58,-27.79,-15.85,-17.71,-39.38,-28.09,-28.68,-38.87,-43.98,-34.17,-33.42,-54.03,-38.45,-38.95,-47.12,-37.77,-44.42,-58.31,-48.97,-34.71,-57.06,-40.85,-39.36,-37.45,-49.69,-24.89,-42.36,-47.72,-33.79,-32.91,-27.79,-5.97,0.47,-11.08,4.37,-2.71,10.12,18.61,21.94,41.94,35.68,37.35,63.09,47.67,50.48,81.35,80.19,90.77,111.31,108.16,116.93,154.04,127.07,158.49,177.74,194.67,193.39,201.45,208.35,187.63,188.03,217.21,212.25,259.67,281.15,234.03,241.24,285.88,265.52,291,325.24,283.15,268.35,316.09,306.09,290.52,337.76,362.01,336.67,296.67,316.06,370.36,358.06,325.97,366.3,380.32,340.29,324.35,336.97,320.03,361.47,368.52,328.86,355.39,378.63,338.66,350.25,349.18,353.43,295.41,312.7,319.79,288.89,337.31,314.24,282.97,300.61,296.6,303.54,271.62,298.86,270.32,266.92,275.76,262.68,221.93,256.06,219.11,210.27,238.03,219.18,207.8,207.01,214.87,172.4,151.16,168.58,165.91,174.71,150.4,152.51,132.12,136.11,148.13,139.16,136,153.18,126.38,112.27,124.08,119.01,87.99,109.79,105.86,108.77,97.52,98.97,83.11,75.2,96.35,78.1,88.51,95.71,69.67,78.57,75.52,72.53,62.27,62.3,67.12,64.31,65.07,73.78,67.6,40.53,65.17,42.74,28.91,52.75,42.84,27.9,42.34,49.29,25.57,30.53,39.54,31.86,29.1,37.96,33.46,22.94,25.81,32.65,14.97,16.76,24.66,12.19,5.76,23.19,17.43,0.29,10.87,17.58,0.43,8.32,14.82,2.93,-1.02,15.99,4.23,-0.77,8.2,4.48,-6.31,2.3,6.08,-7.88,-3.25,5.59,-6.89,-8.8,4.25,-5.11,-13.42,-2.16,-4.81,-16.92,-7.37,-1.82,-13.69,-11.49,-1.2,-15.27,-16.34,-6.98,-16.38,-21.96,-10.69,-10.07,-25.34,-17.22,-11.02,-27.33,-22.65,-14.09,-26.91,-31,-17.52,-20.63,-35.42,-19.9,-19.24,-29.15,-26.44,-21.09,-33.53,-34.12,-22.57,-32.51,-39.37,-20.86,-32.83,-37.53,-27.41,-23.81,-43.98,-30.95,-19.68,-43.55,-31.61,-25.73,-34.04,-44.03,-29.77,-30.24,-41.15,-33.62,-28.5,-38.27,-39.55,-23.66,-39.41,-39.78,-27.83,-31.98,-48.91,-32.3,-30.61,-48.06,-33.79,-37.43,-36.95,-45.61,-25.69,-44.07,-47.6,-32.54,-33.82,-49.29,-41.42,-28.77,-46.96,-45.22,-36.9,-45.36,-45.62,-33.55,-45.53,-45.66,-31.41,-39.45,-53.47,-42.79,-43.79,-43.9,-34.07,-30.47,-44.28,-40.94,-33.86,-43.06,-43.8,-47.25,-47.51,-54.55,-42.97,-35.76,-47.22,-52.95,-45.45,-53.79,-57.36,-39.76,-53.87,-53.88,-34.71,-50.28,-65.05,-39.2,-36.44,-67.12,-52.36,-45.78,-59.82,-54.08,-43.31,-47.4,-68.85,-37.84,-59.83,-52.54,-45.13,-37.66,-67.75,-45.62,-43.16,-56.8,-50.87,-43.09,-47.95,-51.36,-48.55,-53.53,-62.66,-44.68,-39.96,-49.65,-42.14,-39.17,-49.56,-55.73,-29.66,-42.6,-52.44,-42,-43.01,-56.71,-41.33,-29.18,-47.14,-45.77,-25.18,-41.03,-40.95,-32.06,-35.88,-48.42,-30.49,-27.11,-42.27,-36.21,-34.67,-44.09,-30.93,-31.86,-33.29,-42.12,-27.6,-35.7,-37.86,-26.36,-21.02,-34.07,-27.81,-23.13,-41.84,-30.04,-25.83,-28.89,-31,-24.15,-25.66,-32.82,-24.44,-19.68,-32.77,-33.14,-18.29,-34.25,-32.19,-20.77,-34.34,-34.47,-22.64,-26.98,-34.93,-24.73,-19.88,-35.23,-28.27,-22.55,-31.07,-29.8,-18.96,-26.25,-32.01</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B125" t="str">
+        <v>[R_07_标记]</v>
+      </c>
+      <c r="C125" t="str">
+        <v>a: 26.5ms -65.8uv b: 55.7ms 255.3uv</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B126" t="str">
+        <v>[L_07_名字]</v>
+      </c>
+      <c r="C126" t="str">
+        <v>FERG(7)_dMax</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B127" t="str">
+        <v>[L_07_放大器]</v>
+      </c>
+      <c r="C127" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B128" t="str">
+        <v>[L_07_闪光]</v>
+      </c>
+      <c r="C128" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B129" t="str">
+        <v>[L_07_闪光背景]</v>
+      </c>
+      <c r="C129" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B130" t="str">
+        <v>[L_07_采样]</v>
+      </c>
+      <c r="C130" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B131" t="str">
+        <v>[L_07_分析时间]</v>
+      </c>
+      <c r="C131" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B132" t="str">
+        <v>[L_07_数据长度]</v>
+      </c>
+      <c r="C132" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B133" t="str">
+        <v>[L_07_详细数据(uv)]</v>
+      </c>
+      <c r="C133" t="str">
+        <v>15.46,-3.55,-3.79,16.27,8.57,-7.17,8.4,18.12,-0.9,-1.39,18.62,11,-4.95,10.38,20.13,1.02,0.2,20.07,12.44,-3.78,11.24,20.94,1.69,0.49,20.19,12.5,-4.04,10.65,20.22,0.86,-0.79,18.63,10.95,-6.03,8.25,17.94,-1.55,-3.67,15.4,7.51,-9.5,4.72,13.69,-5.81,-8.64,10.26,2.69,-15.15,-1.81,7.43,-13.79,-14.49,2.82,-3.93,-23.51,-8.83,-2.88,-20.54,-24.9,-6.18,-13.02,-37.05,-18.53,-9.17,-34.58,-39.28,-21.02,-26.87,-47.55,-27.64,-25.4,-49.15,-49.31,-35.18,-36.13,-56.49,-42.06,-27.23,-51.49,-43.84,-26.02,-29.99,-62.05,-38.77,-25.72,-46.33,-55.49,-34.74,-35.15,-43.91,-18.15,-15.81,-18.8,-19.72,17.77,-10.14,-0.24,2.66,21.76,5.2,17.61,45.32,46.22,55.65,69.41,64.34,64.84,74.21,110.52,97.91,83.88,127.85,149.49,131.94,121.45,157.11,187.83,177.92,204.23,190.77,189.91,221.72,253.2,253.85,219.41,217.99,240.12,281.07,258.96,303.86,259.36,246.84,275.59,324.94,325.1,323.56,287.95,337.27,284.76,295.82,350.96,304.99,364.21,370.97,350.55,320.04,365.84,377.93,342.85,319.48,340.18,378.23,306.74,371.23,382.13,368.16,323.74,378.56,320.09,340.79,323.68,367.65,302.35,320.64,321.77,312.05,343.89,278.41,309.09,314.95,304.98,299.53,324.59,246.6,270.16,297.04,242.29,265.63,269.01,236.11,232.44,234.45,238.19,238.59,211.2,226.56,207.67,186.63,209.04,216.65,168.48,162.11,207.66,168.31,161.64,184.04,171.59,142.15,159.15,148.39,159.5,129.28,133.32,142.69,143.78,118.36,117.55,120.36,122.92,118.27,140.2,93.97,107.22,102.37,99.24,86.12,106.5,105.68,66.52,61.52,92.44,74.55,74.8,59.7,93.49,69.16,42.48,80.59,59.39,44.44,51.11,57.88,50.26,43.72,54.45,54.71,27.47,36.76,39.35,20.67,10.74,36.6,41.06,17.62,24.26,35.9,15.69,1.4,20.95,27.31,-2.62,9.19,20.91,8.5,-0.61,14.76,15.85,-3.78,5.94,19.25,4.41,-9.35,10.57,7.36,-12.5,-0.48,14.12,-0.09,-11.34,5.8,4.13,-10.91,-3.77,12.31,-4.26,-15.68,6.36,6.64,-12.43,-2.69,6.8,-7.81,-15.65,3.81,1.27,-16.34,-7.09,8.53,-12.37,-20.67,2,-0.48,-20.31,-11.08,3.56,-16.13,-21.95,-6.38,-6.37,-25.07,-19.28,-4.17,-21.26,-27.63,-8.96,-10.79,-26.18,-18.1,-10.14,-21.47,-32.39,-11.71,-17.03,-30.74,-27.39,-10.53,-27.39,-36.89,-19.8,-25.37,-44.68,-32.52,-22.41,-36.13,-41.48,-18.91,-24.27,-41.26,-42.22,-19.78,-37.11,-53.61,-22.3,-31.73,-42.41,-42.89,-31.66,-35.02,-55.03,-33.58,-31.75,-43.95,-41.34,-31.33,-34.36,-44.67,-32.61,-36.56,-52.42,-45.22,-33,-37.58,-52.67,-31.03,-28.56,-46.92,-44.36,-19.25,-33.87,-51.73,-31.19,-38.56,-54.79,-43.28,-25.33,-39.65,-46.57,-25.49,-23.07,-58.29,-47.84,-20.66,-32.12,-54.36,-29.26,-28.42,-40.09,-51.21,-18.83,-43.19,-44.61,-36.66,-22.65,-57.71,-48.57,-20.08,-38.3,-54.38,-33.32,-39.23,-50.94,-39.69,-27.05,-39.56,-64.94,-29.54,-40.58,-49.49,-57.31,-29.21,-48.98,-65.69,-48.18,-29.05,-66.53,-48.59,-27.71,-48.61,-59.72,-38.37,-40.88,-55.55,-49.36,-39.06,-52.7,-58.06,-42.13,-34.61,-66.76,-43.06,-30.03,-42.54,-50.33,-33.05,-44.46,-50.31,-55.8,-35.24,-48.23,-58.43,-41.34,-39.42,-48.02,-44.49,-34.89,-44.32,-54.66,-38.06,-27.72,-46.37,-37.97,-22.67,-33.51,-52.75,-23.82,-29.91,-42.67,-33,-24.02,-34.18,-45.05,-17.96,-14.1,-37.05,-32.06,-10.65,-24.01,-37.24,-13.11,-13.62,-38,-22.09,-10.11,-26.26,-31.17,-9.46,-15.21,-28.32,-20.41,-4.66,-23.53,-29.36,-8.56,-13.04,-27.97,-22.77,-3.41,-21.29,-27.39,-12.68,-5.09,-28.84,-24.22,-4.17,-15.83,-29.47,-14.79,-8.27,-29.45,-24.78,-5.01,-18.9,-33.87,-14.1,-9.07,-31.57,-26.93,-9.27,-18.43,-32.23</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B134" t="str">
+        <v>[L_07_标记]</v>
+      </c>
+      <c r="C134" t="str">
+        <v>a: 26.5ms -63.9uv b: 55.6ms 223.5uv</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B135" t="str">
+        <v>[R_08_名字]</v>
+      </c>
+      <c r="C135" t="str">
+        <v>FERG(8)_dOps</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B136" t="str">
+        <v>[R_08_放大器]</v>
+      </c>
+      <c r="C136" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B137" t="str">
+        <v>[R_08_闪光]</v>
+      </c>
+      <c r="C137" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B138" t="str">
+        <v>[R_08_闪光背景]</v>
+      </c>
+      <c r="C138" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B139" t="str">
+        <v>[R_08_采样]</v>
+      </c>
+      <c r="C139" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B140" t="str">
+        <v>[R_08_分析时间]</v>
+      </c>
+      <c r="C140" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B141" t="str">
+        <v>[R_08_数据长度]</v>
+      </c>
+      <c r="C141" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B142" t="str">
+        <v>[R_08_详细数据(uv)]</v>
+      </c>
+      <c r="C142" t="str">
+        <v>-1.45,-10.28,-5.19,-3.08,-11.1,-2.56,-5.94,-10.27,-1.77,-9.65,-8.9,-3.38,-12.82,-7.41,-6.75,-14.59,-6.05,-10.77,-13.68,-5.26,-13.16,-10.74,-5.4,-13.93,-6.45,-6.4,-12.13,-3.02,-8.69,-10.13,-2,-10.72,-7.76,-4.43,-14.26,-7.51,-10.3,-17.15,-9.63,-16.72,-19.22,-12.44,-22.72,-18.73,-15.24,-22.92,-13.68,-15.51,-18.52,-7.8,-13.29,-10.2,-2.15,-9.45,-1.58,0.19,-8.02,1.45,-2.81,-8.83,-0.69,-11.72,-12.19,-9.76,-21.5,-18.7,-18.66,-26.83,-19.61,-23.73,-28.82,-16.66,-24.61,-18.87,-10.73,-16.24,-5.02,-2.6,-4.43,7.09,3.68,6.17,13.46,8.14,10.72,9.1,-2.99,1.51,-5.66,-15.95,-13.56,-22.58,-26.42,-22.67,-35.28,-31.89,-26.61,-40.23,-27.43,-23.97,-23.02,-9.1,-9.38,-3.45,10.88,8.06,18.4,15.08,15.7,20.35,10.46,5.95,13.8,-4.56,-6.65,-10.25,-25.54,-24.4,-31.16,-47.59,-34.11,-45.53,-47.58,-34.82,-38.36,-35.52,-23.81,-24.35,-10.33,-5.02,-0.62,10.31,7.71,13.87,22.41,17.43,18.66,11.27,2.13,4.59,-6.48,-18.73,-17.75,-29.01,-38.79,-40.1,-44.36,-48.26,-42.54,-52.64,-33.01,-34.35,-30.22,-16.55,-17.23,-7.23,4.58,3.02,10.87,13.36,12.08,18.06,8.45,5.03,9.16,-4.1,-4.74,-6.17,-21.64,-18.35,-23.41,-33.27,-31.21,-36.13,-36.1,-25.35,-32.8,-25.27,-17.32,-22.55,-9.69,-7.41,-9.09,5.18,-1.13,2.51,7.1,1.06,5.91,2.83,-5.76,0.31,-7.01,-14.56,-9.43,-20.14,-20.63,-18.26,-27.46,-24.63,-20.99,-31.62,-20.7,-21.6,-24.27,-13.28,-19.4,-14.65,-7.52,-15.99,-6.59,-5.87,-12.6,-3.94,-10.44,-12.81,-6.06,-15.74,-14.1,-11.36,-21.73,-15.65,-18.47,-24.78,-16.82,-23.17,-24.4,-15.75,-24.12,-19.18,-15.85,-23.18,-14.15,-15.84,-19.67,-9.8,-16.53,-15.5,-8.72,-17.9,-12.1,-10.68,-18.91,-10.31,-14.3,-18.36,-10.13,-18.19,-16.59,-11.4,-20.46,-13.95,-13.57,-20.42,-11.06,-15.83,-17.74,-9.36,-17.31,-14.02,-9.38,-17.9,-10.42,-11.11,-17.2,-8.07,-13.95,-15.39,-8.01,-16.82,-12.78,-9.69,-18.34,-10.53,-12.82,-18.15,-9.35,-16.24,-16.25,-9.66,-18.72,-13.66,-11.67,-19.77,-11.37,-14.81,-19.01,-10.42,-18.09,-17,-11.31,-20.49,-14.56,-13.89,-21.38,-12.76,-17.35,-20.51,-12.35,-20.65,-18.37,-13.66,-22.72,-15.88,-16.35,-22.98,-14.08,-19.61,-21.46,-13.73,-22.36,-18.81,-15.04,-23.71,-16.04,-17.61,-23.21,-14.18,-20.52,-21.05,-13.89,-22.72,-17.97,-15.24,-23.38,-15.03,-17.68,-22.18,-13.21,-20.26,-19.48,-13.06,-21.95,-16.13,-14.53,-22.03,-13.22,-16.97,-20.36,-11.67,-19.39,-17.4,-11.92,-20.8,-14.11,-13.76,-20.58,-11.56,-16.43,-18.73,-10.59,-18.91,-15.83,-11.47,-20.25,-12.89,-13.86,-19.95,-10.95,-16.91,-18.12,-10.71,-19.54,-15.46,-12.32,-20.87,-12.99,-15.28,-20.52,-11.7,-18.64,-18.73,-12.18,-21.31,-16.27,-14.39,-22.5,-14.2,-17.71,-21.95,-13.41,-21.12,-20.02,-14.37,-23.57,-17.58,-16.9,-24.35,-15.68,-20.27,-23.34,-15.14,-23.41,-21.05,-16.31,-25.32,-18.42,-18.87,-25.44,-16.49,-22,-23.78,-16.02,-24.62,-21,-17.22,-25.83,-18.1,-19.65,-25.19,-16.11,-22.42,-22.88,-15.7,-24.49,-19.68,-16.94,-25.03,-16.64,-19.29,-23.75,-14.76,-21.81,-20.99,-14.58,-23.47,-17.63,-16.06,-23.55,-14.75,-18.54,-21.91,-13.26,-21.01,-19.02,-13.59,-22.5,-15.82,-15.54,-22.38,-13.4,-18.34,-20.65,-12.57,-20.95,-17.89,-13.61,-22.43,-15.1,-16.16,-22.27,-13.32,-19.35,-20.58,-13.24,-22.12,-18.05,-14.99,-23.56,-15.7,-18.06,-23.31,-14.52,-21.5,-21.58,-15.07,-24.23,-19.18,-17.33,-25.44,-17.12,-20.66,-24.87,-16.33,-24.04,-22.9,-17.25,-26.43,-20.4,-19.72,-27.11,-18.4,-22.98,-25.99,-17.76,-25.99,-23.56,-18.8,-27.76,-20.79,-21.23,-27.72,-18.72,-24.2,-25.91,-18.11,-26.67,-22.97,-19.17,-27.74</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B143" t="str">
+        <v>[R_08_标记]</v>
+      </c>
+      <c r="C143" t="str">
+        <v>70.5uv</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B144" t="str">
+        <v>[L_08_名字]</v>
+      </c>
+      <c r="C144" t="str">
+        <v>FERG(8)_dOps</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B145" t="str">
+        <v>[L_08_放大器]</v>
+      </c>
+      <c r="C145" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B146" t="str">
+        <v>[L_08_闪光]</v>
+      </c>
+      <c r="C146" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B147" t="str">
+        <v>[L_08_闪光背景]</v>
+      </c>
+      <c r="C147" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B148" t="str">
+        <v>[L_08_采样]</v>
+      </c>
+      <c r="C148" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B149" t="str">
+        <v>[L_08_分析时间]</v>
+      </c>
+      <c r="C149" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B150" t="str">
+        <v>[L_08_数据长度]</v>
+      </c>
+      <c r="C150" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B151" t="str">
+        <v>[L_08_详细数据(uv)]</v>
+      </c>
+      <c r="C151" t="str">
+        <v>-8.76,-7.95,-21.13,-6.74,-9.26,-20.51,-5.12,-10.86,-19.68,-4.02,-12.64,-18.69,-3.38,-14.6,-17.52,-3.21,-16.5,-16.3,-3.7,-18.53,-15.17,-4.82,-20.58,-14.21,-6.54,-22.48,-13.4,-8.63,-24.14,-12.58,-10.83,-25.1,-11.56,-13.12,-25.33,-10.4,-15.04,-24.78,-9.34,-16.98,-23.97,-8.53,-19.03,-23.25,-8.73,-21.43,-22.74,-9.73,-24.49,-22.63,-11.75,-27.32,-22.19,-14,-30.18,-21.72,-14.52,-30.29,-18.37,-14.78,-28.22,-14,-13,-24.86,-9.1,-11.03,-20.93,-3.65,-10.68,-18.08,-3.13,-12.77,-18.51,-5.27,-18.09,-22.06,-9.61,-24.83,-24.8,-14.52,-27.55,-25.43,-14.8,-27.95,-20.54,-10.98,-23.17,-10.27,-2.39,-14.09,-0.2,6.35,-4.2,9.25,7.92,-4.32,9.74,5.31,-7.48,2.1,-10.02,-21.39,-9.97,-24.93,-32.87,-22.65,-35.32,-37.16,-24.89,-39.88,-32.71,-19.01,-26.62,-16.2,-1.24,-12.32,4.37,15.61,2.35,12.47,17.59,6.64,12.62,14.74,-7.96,2.67,-10.56,-28.23,-21.41,-31.85,-51.51,-39.47,-51.94,-56.93,-41.95,-53.69,-45.72,-31.18,-35.62,-25.99,-6.76,-15.65,-3.5,15.26,7.57,16.38,21.24,1.7,10.12,11.79,-2.64,-0.47,-6.41,-26.31,-18.5,-29.73,-46.95,-29.76,-43.23,-56.61,-32.1,-46.91,-40.64,-22.76,-27.19,-24.95,-3.35,-9.06,-2.3,12.49,1.39,9.42,24.6,9.95,15.8,15,-5.46,1.44,1.51,-17.82,-11.05,-12.74,-32.55,-19.76,-20.21,-33.08,-18.15,-21.93,-32.36,-15,-17.76,-21.31,-1.78,-8.75,-9.29,6.51,-5.27,-4.58,10.28,-4.52,-3.06,8.34,-10.75,-8.03,-1.41,-19.05,-12.58,-9.72,-25.98,-17.06,-15.85,-30.54,-16.82,-16.23,-29.39,-13.7,-15.61,-25.53,-8.72,-14.43,-21.49,-5.46,-13.94,-18.24,-3.07,-16.05,-18.31,-4.06,-18.52,-18.08,-6.71,-22.34,-18.04,-8.81,-24.93,-16.99,-10.07,-25.55,-14.9,-11.08,-25.52,-12.2,-10.98,-23.83,-9.05,-11.05,-21.87,-6.2,-11.37,-20.03,-4.07,-12.25,-18.03,-2.45,-13.57,-16.24,-1.68,-14.71,-14.18,-1.24,-15.68,-11.93,-1.14,-16.38,-9.51,-1.28,-16.69,-7.01,-1.77,-16.7,-4.73,-2.72,-16.56,-2.79,-4.14,-16.27,-1.3,-5.95,-15.85,-0.35,-8.04,-15.29,0.11,-10.31,-14.57,0.06,-12.63,-13.7,-0.48,-14.87,-12.72,-1.47,-16.97,-11.67,-2.88,-18.8,-10.61,-4.67,-20.32,-9.58,-6.75,-21.45,-8.63,-9.02,-22.14,-7.79,-11.39,-22.36,-7.09,-13.74,-22.08,-6.57,-15.97,-21.32,-6.23,-17.99,-20.1,-6.09,-19.68,-18.49,-6.15,-21,-16.53,-6.41,-21.87,-14.33,-6.86,-22.25,-11.96,-7.47,-22.13,-9.54,-8.23,-21.52,-7.17,-9.08,-20.43,-4.95,-10.01,-18.92,-2.98,-10.96,-17.05,-1.33,-11.89,-14.9,-0.09,-12.77,-12.56,0.71,-13.55,-10.13,1.01,-14.2,-7.72,0.81,-14.69,-5.44,0.12,-15.01,-3.37,-1.03,-15.12,-1.61,-2.58,-15.03,-0.23,-4.48,-14.74,0.71,-6.63,-14.25,1.18,-8.93,-13.6,1.15,-11.29,-12.79,0.63,-13.6,-11.87,-0.35,-15.76,-10.87,-1.75,-17.66,-9.82,-3.51,-19.23,-8.78,-5.53,-20.38,-7.78,-7.74,-21.08,-6.86,-10.04,-21.28,-6.06,-12.31,-20.97,-5.42,-14.46,-20.16,-4.94,-16.39,-18.89,-4.66,-18.02,-17.21,-4.59,-19.28,-15.18,-4.72,-20.1,-12.9,-5.04,-20.45,-10.46,-5.55,-20.32,-7.97,-6.22,-19.7,-5.53,-7.02,-18.63,-3.25,-7.91,-17.16,-1.23,-8.86,-15.33,0.45,-9.82,-13.24,1.71,-10.75,-10.97,2.5,-11.62,-8.63,2.78,-12.37,-6.3,2.55,-12.98,-4.09,1.82,-13.43,-2.1,0.62,-13.68,-0.41,-1.01,-13.73,0.91,-2.97,-13.57,1.8,-5.19,-13.21,2.24,-7.57,-12.65,2.19,-10,-11.93,1.68,-12.37,-11.06,0.72,-14.58,-10.08,-0.64,-16.52,-9.04,-2.34,-18.11,-7.96,-4.3,-19.28,-6.9,-6.44,-19.97,-5.9,-8.64,-20.15,-5,-10.83,-19.81,-4.23,-12.9,-18.96,-3.62,-14.75,-17.63,-3.2,-16.31,-15.88</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B152" t="str">
+        <v>[L_08_标记]</v>
+      </c>
+      <c r="C152" t="str">
+        <v>67.7uv</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B153" t="str">
+        <v>[R_09_名字]</v>
+      </c>
+      <c r="C153" t="str">
+        <v>FERG(9)_dMax</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B154" t="str">
+        <v>[R_09_放大器]</v>
+      </c>
+      <c r="C154" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B155" t="str">
+        <v>[R_09_闪光]</v>
+      </c>
+      <c r="C155" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B156" t="str">
+        <v>[R_09_闪光背景]</v>
+      </c>
+      <c r="C156" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B157" t="str">
+        <v>[R_09_采样]</v>
+      </c>
+      <c r="C157" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B158" t="str">
+        <v>[R_09_分析时间]</v>
+      </c>
+      <c r="C158" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B159" t="str">
+        <v>[R_09_数据长度]</v>
+      </c>
+      <c r="C159" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B160" t="str">
+        <v>[R_09_详细数据(uv)]</v>
+      </c>
+      <c r="C160" t="str">
+        <v>27.32,10.66,20.04,19.04,10.41,25.69,6.02,24.58,10.04,16.13,18.6,6.86,24.01,3.97,21.19,9.31,11.96,17.9,3.51,22,2.34,17.71,8.93,8.11,17.31,0.73,20.1,1.3,14.41,9.14,4.72,16.93,-1.08,18.51,1.11,11.23,9.9,1.89,16.41,-2.73,16.79,1.39,7.75,9.66,-1.09,15.13,-3.88,11.98,2.04,3.49,9.26,-3.96,14.04,-5.84,7.34,-1.42,-5.36,3.21,-15.06,6.96,-12.86,-0.22,-7.22,-15.7,0.57,-23,4.19,-20.86,-7.89,-6.01,-24.49,-15.16,-26.63,-5.73,-16.99,-5.91,-20.51,-28.89,0.65,-29.54,-7.25,-11.77,-12.84,-6.52,-14.42,-4.01,-11.01,-9.37,0.53,3.86,10.31,-0.96,26.26,3.25,37.18,36.73,31.88,58.88,23.72,69.66,55.05,78.37,86.17,76.06,107.45,84.57,108.92,107.54,120.74,148.58,145.78,168.36,130.15,201.09,170.28,178.16,192.9,214.75,212.98,224.41,213.53,229.15,243.35,266.22,280.33,266.88,240.19,272.09,322.62,307.61,294.8,279.44,324.24,350.29,371.25,328.01,321.33,330.7,370.75,379.54,377.41,339.57,415.64,380.62,406.31,335.82,435.49,378.59,423.86,428.88,375.99,392.17,342.1,429.26,389.7,424.23,398.67,403.22,385.08,380.75,397.17,376.55,400.73,344.32,316.94,354.14,360.37,358.83,383.11,341.12,358.96,353.11,343.73,321.76,348.64,337.98,306.54,298.36,285.41,288.97,272.98,253.7,296.05,249.37,273.64,246.62,267.93,263.11,252.89,240.05,203.68,209.59,185.48,207.16,206.57,197.98,202.63,191.78,197.93,162.84,175.92,173.06,164.91,171.6,148.07,154.78,123.61,162.22,153.88,122.25,155.26,141.08,132.4,134.74,112.99,121.3,95.3,109.89,95.98,115.38,89.46,108.62,102.56,84.37,93.97,69.97,95.32,83.57,83.56,95.33,79.01,87.8,66.78,81.95,55.39,65.17,75.33,44.46,66.97,48.98,55.97,55.71,50.71,57.43,40.57,51.47,33.1,45.52,48.37,35.61,49.35,29.2,46.06,23.61,30.21,37.66,19.87,43.51,15.88,30.85,24.37,20.64,27.68,11.25,31.57,7.23,22.89,15.49,11.24,22.34,3.16,23.03,2.63,13.13,11.19,2.53,14.17,-3.48,14,-1.43,7.89,3.5,-2.76,8.18,-11.76,7.83,-5.73,0.66,3.03,-11.88,3.55,-12.32,6,-6.2,-6.53,-0.15,-12.45,0.59,-18.14,-1.65,-11.08,-13.13,0.57,-22.41,2.97,-20.03,-2.02,-12.15,-16.86,-2.91,-26.02,-4,-17.98,-4.2,-13.4,-14.84,-6.49,-27.15,-6.78,-21.89,-13.41,-12.5,-15.82,-2.87,-24.81,-6.85,-11.61,-11.24,-11.5,-22.65,-0.41,-16.66,-0.7,-19.52,-21.88,-9.75,-28.39,-7.99,-19.04,-12.48,-16.3,-15.62,-11.47,-18.89,-1.12,-33.98,-22.49,-18.1,-16.23,-12.83,-26.53,-18.96,-28.57,-26.65,-16.04,-36.5,-10.88,-41.58,-17.91,-24.56,-20.63,-19.53,-40.23,-9.06,-45.59,-29.22,-25.23,-31,-30.91,-42.66,-18.71,-45.26,-27.27,-40.89,-31.59,-31.58,-46.93,-31.48,-36.29,-27.91,-32.7,-50.91,-32.25,-47.62,-24.77,-48.12,-28.73,-38.62,-49.94,-18.52,-36.2,-33.71,-47.14,-34.08,-37.95,-47.84,-27.55,-40.89,-35.53,-30,-27.82,-24.88,-48.92,-32.42,-47.29,-20.35,-43.3,-23.57,-14.77,-30.6,-25.82,-32.98,-28.67,-21.75,-23.19,-28.02,-30.72,-22.42,-37.8,-20.27,-30.54,-23.14,-15.13,-36.58,-7.75,-31.3,-24.02,-24.9,-34.42,-4.45,-23.81,-18.68,-27.67,-15.25,-15.85,-22.09,-14,-23.69,-12.82,-19.64,-14.59,-13.84,-30.13,-2.6,-17.58,-13.12,-22.95,-18.61,-10.76,-19.42,-1.27,-20.68,-16.74,-11.01,-25.48,-0.21,-20.86,-3.45,-22.3,-14.66,-8.35,-21.25,-9.67,-20.99,-8.56,-16.82,-13.8,-8.68,-20.78,-4.48,-24.51,-8.85,-19.61,-15.41,-9.69,-16.48,-0.09,-19.76,-5.35,-9.09,-16.2,-4.3,-16.4,4.14,-13.28,-0.94,-4.98,-10.15,1.96,-12.73,3.61,-10.91,-3,-1.46,-6.31,9.77,-8.88,8.56,-4.18,0.98</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B161" t="str">
+        <v>[R_09_标记]</v>
+      </c>
+      <c r="C161" t="str">
+        <v>a: 29.7ms -86.6uv b: 63.0ms 321.6uv</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B162" t="str">
+        <v>[L_09_名字]</v>
+      </c>
+      <c r="C162" t="str">
+        <v>FERG(9)_dMax</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B163" t="str">
+        <v>[L_09_放大器]</v>
+      </c>
+      <c r="C163" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B164" t="str">
+        <v>[L_09_闪光]</v>
+      </c>
+      <c r="C164" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B165" t="str">
+        <v>[L_09_闪光背景]</v>
+      </c>
+      <c r="C165" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B166" t="str">
+        <v>[L_09_采样]</v>
+      </c>
+      <c r="C166" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B167" t="str">
+        <v>[L_09_分析时间]</v>
+      </c>
+      <c r="C167" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B168" t="str">
+        <v>[L_09_数据长度]</v>
+      </c>
+      <c r="C168" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B169" t="str">
+        <v>[L_09_详细数据(uv)]</v>
+      </c>
+      <c r="C169" t="str">
+        <v>-9.86,-15.31,-0.75,-19.71,-3.71,-11.67,-15.31,-2.14,-20.94,-4.11,-13.86,-15.64,-3.96,-22.38,-4.86,-16.27,-16.14,-6.04,-23.85,-5.8,-18.71,-16.63,-8.18,-25.16,-6.73,-20.98,-16.94,-10.2,-26.14,-7.51,-22.91,-16.93,-12.01,-26.69,-8.06,-24.43,-16.57,-13.56,-26.86,-8.41,-25.63,-16.17,-15.06,-26.56,-8.95,-26.8,-15.79,-16.38,-26.66,-9.4,-28.28,-15.61,-18.76,-28.16,-12.39,-30.16,-18.46,-23.9,-30.37,-16.83,-37.08,-20.37,-30.83,-33.95,-19.72,-39.11,-28.09,-36.05,-44.02,-29.02,-54.32,-39.37,-45.54,-54.98,-43.96,-64.23,-45.86,-62.57,-63.64,-53.61,-60.98,-44.23,-64.64,-71.29,-49.18,-77.08,-46.5,-67.36,-51.8,-54.52,-60.65,-45.48,-47.63,-52.94,-29.03,-58.37,-18.36,-37.33,-16.66,-7.34,-19.88,-1.04,-1.34,20.86,7.81,15.93,47.22,26.27,68.2,60.83,66.63,91.88,74.74,94.23,115.23,112.42,122.08,128.09,127.15,169.42,149.91,170.58,185.99,201.65,222.06,229.22,202.31,215.29,260.46,263.35,263.68,281.88,270.57,317.27,313.36,273.55,278.02,268.41,325.89,296.46,293.84,331.8,354.25,380.41,350,338.06,351.68,383.82,405.84,342.51,335.3,330.66,344.15,332.23,375.06,396.29,373.88,348.8,389.14,329.74,356.43,351.32,307.05,346.85,294.99,355.89,306.86,302.99,336.78,275.9,330.17,282.08,300.67,272.4,275.95,259.31,230.15,231.54,260.76,221.52,258.12,229.73,198.96,229.71,196.96,222.95,208.11,154.51,177.1,155.6,179.61,144.9,147.69,156.53,129.5,140.39,143.35,147.53,123.26,108.6,117.78,122.72,106.55,129.71,76.51,126.15,100.48,97.94,110.25,84.34,82.94,66.29,89.51,65.31,77.15,70.09,66.36,57.25,64.36,58.22,62.22,55.7,49.87,62.87,60.87,59.45,42.67,63.8,46.36,40.62,56.25,43.14,54.11,38.98,33.22,52.91,20.93,29.1,36.37,16.26,43.52,26.5,37.84,27.15,14.48,31.6,16.06,23.74,14.42,8.66,20.54,2.07,25,10.45,9.35,19.05,-4.01,15.03,4.25,3.19,8.14,-3.38,13.57,-6.44,-0.44,3.63,-13.04,4.24,-6.7,-8.92,-0.73,-16.96,1.56,-14.1,-8.67,-7.35,-20.92,-2.66,-19.29,-12.67,-10.14,-23.4,-7.02,-22.35,-16.08,-12.71,-28.2,-12.7,-30.52,-18.36,-16.78,-33.63,-14.84,-32.59,-24.39,-25.44,-34.44,-15.97,-35.73,-22.02,-29.97,-38.64,-17.34,-42.13,-23.21,-26.76,-34.26,-21.66,-37.11,-29.22,-29.67,-35.77,-27.66,-46.8,-22.3,-33.35,-37.53,-26.41,-38.07,-22.11,-32.46,-39.84,-30.98,-41.87,-22.41,-39.88,-39.39,-30.14,-38.93,-23.78,-35.15,-31.19,-33.05,-47.33,-21.91,-36.48,-34.65,-24.39,-43.05,-30.03,-39.7,-39.66,-34.85,-48.69,-22.43,-47.14,-38.39,-33.78,-47.11,-26.55,-53.65,-28.25,-34.96,-47.97,-38.98,-45.02,-41.43,-40.92,-46.75,-28.05,-55.25,-45.51,-49.76,-51.49,-32.71,-56.55,-49.05,-49.42,-61.84,-40.71,-55.46,-46.64,-43.32,-44.17,-36.44,-59.27,-49.91,-54.43,-48.3,-37.64,-59.61,-43.26,-61.83,-53.93,-46.46,-67.43,-44.34,-65.35,-50.31,-45.98,-61.61,-44.29,-66.57,-55.1,-44.35,-71.36,-47.3,-56.09,-43.7,-40.28,-55.14,-52.09,-65.05,-44.57,-43.81,-63.14,-49.12,-62.67,-50.92,-40.23,-54.65,-40.02,-49.83,-52.03,-35.77,-51.47,-35.91,-48.5,-43.5,-49.39,-52.84,-31.86,-44.29,-34.16,-38.02,-40.03,-30.52,-51.47,-32.61,-31.25,-41.87,-28.97,-43.85,-31.55,-39.52,-34.5,-25.07,-51.36,-24.46,-29.74,-37.75,-28.13,-45.64,-19.08,-34.98,-37.93,-20.9,-37.66,-25.01,-36.45,-38.31,-19.33,-46.69,-14.92,-31.22,-24.98,-27.29,-34.93,-19.56,-35.41,-27.87,-24.04,-37.79,-20.08,-39.77,-26.56,-24.77,-38.27,-23.4,-36.23,-24.35,-29.65,-38.67,-21.51,-36.58,-27.59,-28.34,-36.38,-19.09,-36.66,-18.71,-25.64,-31.91,-15.27,-36.84,-17.23,-21.4,-27.86,-15.59,-31.86,-15.89,-23.64,-24.44,-9.81,-28.7,-14.35,-19.65,-22.52,-7.87,-28.59</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B170" t="str">
+        <v>[L_09_标记]</v>
+      </c>
+      <c r="C170" t="str">
+        <v>a: 29.7ms -84.3uv b: 63.2ms 348.7uv</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B171" t="str">
+        <v>[R_10_名字]</v>
+      </c>
+      <c r="C171" t="str">
+        <v>FERG(10)_dOps</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B172" t="str">
+        <v>[R_10_放大器]</v>
+      </c>
+      <c r="C172" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B173" t="str">
+        <v>[R_10_闪光]</v>
+      </c>
+      <c r="C173" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B174" t="str">
+        <v>[R_10_闪光背景]</v>
+      </c>
+      <c r="C174" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B175" t="str">
+        <v>[R_10_采样]</v>
+      </c>
+      <c r="C175" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B176" t="str">
+        <v>[R_10_分析时间]</v>
+      </c>
+      <c r="C176" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B177" t="str">
+        <v>[R_10_数据长度]</v>
+      </c>
+      <c r="C177" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B178" t="str">
+        <v>[R_10_详细数据(uv)]</v>
+      </c>
+      <c r="C178" t="str">
+        <v>-15.62,-13.71,-16.85,-13.03,-17.97,-12.31,-18.98,-11.79,-19.88,-11.37,-20.46,-11.12,-20.88,-10.96,-20.83,-10.94,-20.64,-11.09,-20.29,-11.55,-19.69,-12.35,-19.09,-13.26,-18.45,-14.39,-17.58,-15.56,-16.6,-16.45,-15.58,-17.37,-14.2,-17.77,-12.56,-17.84,-10.81,-17.58,-8.97,-16.81,-7.09,-15.99,-5.95,-15.63,-5.84,-15.01,-5.51,-15.57,-6.67,-15.92,-8.39,-16.33,-10.05,-17.5,-12.19,-16.37,-13.9,-16.26,-13.95,-13.55,-13.69,-10.95,-12.45,-6.95,-10.1,-3.86,-8.71,-1.11,-7.97,1.55,-6.41,2.45,-8.71,-1.25,-12.71,-4.8,-16.69,-10.33,-21.62,-16.57,-24.31,-17.03,-27.69,-21.52,-25.29,-18.28,-20.77,-16.61,-14.48,-10.8,-5.74,-4.58,1.75,0.81,5.46,4.49,7.72,1.2,6.88,-3.55,-1.09,-14.02,-9.71,-25.9,-19.8,-35.87,-26.42,-42.68,-35.63,-42.76,-34.57,-38.38,-23.93,-28.47,-15.4,-13.71,-3.19,-1.87,7.45,8.63,18.24,20.14,13.74,16.51,6.67,13.1,-2.46,1.02,-15,-14.99,-27.87,-27.18,-40.56,-34.83,-44.3,-40.27,-48.36,-33.03,-34.68,-21.51,-22.39,-5.45,-4.82,10.41,11.86,20.23,24.39,19.83,21.13,18.35,19.72,16.42,11.51,-1.49,-2.84,-16.87,-16.67,-32.58,-25.4,-34.24,-35.87,-43.26,-33.47,-34.15,-25.19,-26.04,-12.53,-15.15,0.88,-2.53,13.46,4.42,14.52,16.61,14.54,10.72,16.74,8.64,2.01,-2.8,-7.84,-10.81,-19.8,-19.39,-25.73,-24.08,-29.24,-28.62,-34.68,-21.69,-26.14,-15.9,-22.15,-7.53,-13.94,-0.59,-7.15,3.11,-1.18,5.11,-0.92,5.21,-2.42,3.58,-6.3,-3.44,-8.88,-8.97,-13.2,-14.76,-14.98,-17.88,-16.58,-19.85,-12.73,-18.47,-11.38,-15.02,-6.58,-12.96,-2.28,-9.79,1.06,-7.93,3.93,-6.27,3.49,-5.56,2.51,-6.83,1.18,-7.1,-0.82,-7.84,-3.07,-8.18,-5.13,-7.75,-6.27,-6.59,-6.82,-5.72,-7.85,-3.62,-7.6,-1.92,-7.65,-0.41,-7.78,0.67,-8.09,1.41,-8.13,1.18,-8.63,1.04,-9.09,0.15,-9.54,-0.95,-9.7,-2.18,-9.52,-3.38,-9.14,-4.51,-8.41,-5.72,-7.5,-6.78,-6.46,-7.82,-5.47,-8.85,-4.56,-9.77,-3.78,-10.67,-3.15,-11.39,-2.66,-11.91,-2.42,-12.2,-2.31,-12.24,-2.39,-12.01,-2.61,-11.51,-2.98,-10.74,-3.45,-9.74,-4.01,-8.59,-4.64,-7.29,-5.31,-5.92,-6,-4.53,-6.64,-3.16,-7.23,-1.88,-7.7,-0.7,-8.04,0.31,-8.22,1.12,-8.2,1.73,-7.99,2.1,-7.58,2.24,-6.99,2.14,-6.22,1.81,-5.31,1.29,-4.29,0.59,-3.2,-0.25,-2.08,-1.18,-0.98,-2.17,0.07,-3.17,1.01,-4.13,1.8,-5,2.42,-5.77,2.83,-6.38,3.02,-6.82,2.97,-7.06,2.68,-7.12,2.16,-6.97,1.43,-6.65,0.52,-6.15,-0.54,-5.52,-1.71,-4.78,-2.94,-3.97,-4.18,-3.13,-5.38,-2.29,-6.48,-1.5,-7.46,-0.79,-8.25,-0.19,-8.84,0.26,-9.19,0.56,-9.28,0.69,-9.12,0.65,-8.69,0.44,-8.02,0.08,-7.13,-0.4,-6.06,-0.99,-4.83,-1.64,-3.5,-2.33,-2.11,-3,-0.72,-3.62,0.63,-4.16,1.88,-4.58,2.99,-4.86,3.93,-4.96,4.66,-4.88,5.16,-4.6,5.42,-4.14,5.44,-3.5,5.22,-2.71,4.78,-1.79,4.14,-0.78,3.34,0.29,2.42,1.37,1.42,2.42,0.38,3.39,-0.64,4.24,-1.6,4.94,-2.47,5.45,-3.2,5.75,-3.77,5.82,-4.16,5.65,-4.34,5.26,-4.33,4.65,-4.11,3.84,-3.72,2.87,-3.16,1.77,-2.47,0.59,-1.68,-0.63,-0.83,-1.84,0.05,-2.98,0.9,-4,1.69,-4.88,2.4,-5.56,2.98,-6.02,3.41,-6.23,3.68,-6.18,3.78,-5.87,3.71,-5.31,3.48,-4.52,3.1,-3.52,2.6,-2.35,2,-1.06,1.35,0.32,0.68,1.73,0.04,3.12,-0.56,4.43,-1.05,5.63,-1.42,6.67,-1.64,7.52,-1.69,8.14,-1.55,8.52,-1.23,8.66,-0.73,8.55</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B179" t="str">
+        <v>[R_10_标记]</v>
+      </c>
+      <c r="C179" t="str">
+        <v>67.4uv</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B180" t="str">
+        <v>[L_10_名字]</v>
+      </c>
+      <c r="C180" t="str">
+        <v>FERG(10)_dOps</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B181" t="str">
+        <v>[L_10_放大器]</v>
+      </c>
+      <c r="C181" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B182" t="str">
+        <v>[L_10_闪光]</v>
+      </c>
+      <c r="C182" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B183" t="str">
+        <v>[L_10_闪光背景]</v>
+      </c>
+      <c r="C183" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B184" t="str">
+        <v>[L_10_采样]</v>
+      </c>
+      <c r="C184" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B185" t="str">
+        <v>[L_10_分析时间]</v>
+      </c>
+      <c r="C185" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B186" t="str">
+        <v>[L_10_数据长度]</v>
+      </c>
+      <c r="C186" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B187" t="str">
+        <v>[L_10_详细数据(uv)]</v>
+      </c>
+      <c r="C187" t="str">
+        <v>-18.02,-28.54,-19.16,-27.49,-21.44,-25.8,-24.41,-23.87,-27.46,-22.19,-29.92,-20.95,-31.38,-20.72,-31.3,-21.62,-29.9,-23.14,-27.47,-24.97,-24.42,-26.76,-21.45,-27.99,-19.49,-28.76,-18.16,-29.1,-19.04,-28.31,-21.39,-26.97,-24.74,-25.49,-28.39,-24.76,-31.01,-22.75,-33.24,-22.52,-32.85,-22.16,-29.98,-21.76,-26,-21.21,-20.91,-20.32,-14.85,-20.59,-11.94,-20.14,-9.37,-21.14,-10.35,-19.77,-14.49,-21.73,-20.01,-23.88,-26.72,-24.81,-31.75,-26.95,-37.15,-24.38,-37.94,-24.68,-32.41,-21.34,-24.76,-17.32,-15.29,-13.69,-7.92,-9.64,-2.15,-8.23,1.49,-11.31,-1.1,-14.75,-7.88,-18.95,-18.93,-27.33,-32.11,-31.86,-40.66,-39.5,-46.41,-35.83,-50.03,-32.86,-41.52,-27.78,-31.51,-20.3,-17.72,-12.02,-1.11,-4.51,6.64,-0.64,9.4,1.26,8.9,-5.07,-2.17,-18.37,-19.37,-31.01,-38.11,-38.47,-48.6,-49.84,-56.36,-49.23,-61.19,-44.52,-50.4,-32.64,-35,-22.25,-17.49,-9.66,-2.81,-2.45,10.43,5.64,21.21,8.95,12.94,-0.14,3.81,-14.16,-14.15,-26.09,-31.16,-37.93,-43.45,-43.18,-56.36,-48.61,-57.28,-39.73,-44.13,-29.08,-32.67,-17.77,-16.76,-6.16,-0.08,2.06,5.26,4.55,13.88,-0.2,13.41,-3.48,1.11,-10.97,-9.13,-21,-21.74,-28.21,-33.09,-33.26,-40.46,-29.94,-40.73,-28.86,-37.56,-25.23,-30.8,-17.91,-19.98,-12.74,-11.57,-9.14,-6.12,-7.08,-3,-13.06,-1.94,-13.87,-6.21,-18.06,-13.41,-22.65,-20.95,-25.63,-26.75,-26.28,-30.65,-23.34,-33.86,-23.24,-31.84,-20.55,-27.89,-18.3,-23.43,-17.16,-18.54,-16.63,-13.31,-18.37,-11.63,-19.34,-10.83,-21.64,-11.62,-21.78,-13.76,-21.85,-17.37,-20.54,-20.79,-18.59,-23.75,-16.53,-24.48,-14.33,-24.6,-13.09,-22.83,-12.84,-19.91,-13.62,-16.51,-15.29,-13.38,-16.96,-10.49,-18.28,-9.14,-19.2,-8.87,-19.22,-9.84,-17.96,-11.94,-15.95,-14.48,-13.63,-17.1,-11.34,-18.87,-9.66,-19.91,-9.19,-19.58,-9.9,-18.21,-11.63,-16.07,-14.06,-13.68,-16.7,-11.51,-18.97,-10.21,-20.38,-9.96,-20.64,-10.96,-19.8,-12.97,-18.06,-15.65,-15.86,-18.44,-13.79,-20.79,-12.31,-22.24,-11.85,-22.51,-12.53,-21.58,-14.25,-19.7,-16.66,-17.32,-19.24,-14.97,-21.43,-13.18,-22.76,-12.35,-22.92,-12.65,-21.85,-14,-19.78,-16.07,-17.13,-18.36,-14.45,-20.32,-12.28,-21.46,-11.04,-21.47,-10.94,-20.27,-11.94,-18.06,-13.73,-15.25,-15.85,-12.38,-17.73,-10.01,-18.88,-8.58,-18.97,-8.32,-17.88,-9.22,-15.8,-11.01,-13.1,-13.21,-10.33,-15.28,-8.03,-16.7,-6.67,-17.11,-6.51,-16.39,-7.54,-14.66,-9.52,-12.29,-11.99,-9.8,-14.41,-7.73,-16.23,-6.56,-17.07,-6.56,-16.77,-7.77,-15.43,-9.94,-13.37,-12.65,-11.11,-15.32,-9.18,-17.43,-8.08,-18.56,-8.09,-18.51,-9.28,-17.35,-11.43,-15.39,-14.12,-13.11,-16.8,-11.08,-18.93,-9.78,-20.06,-9.53,-19.99,-10.43,-18.75,-12.29,-16.64,-14.71,-14.13,-17.16,-11.77,-19.09,-10.08,-20.05,-9.41,-19.81,-9.88,-18.38,-11.34,-16.04,-13.42,-13.25,-15.61,-10.56,-17.35,-8.52,-18.19,-7.5,-17.86,-7.64,-16.37,-8.84,-13.95,-10.75,-11.07,-12.86,-8.29,-14.63,-6.13,-15.58,-5,-15.43,-5.08,-14.14,-6.28,-11.93,-8.28,-9.24,-10.58,-6.61,-12.63,-4.59,-13.93,-3.6,-14.17,-3.82,-13.29,-5.21,-11.46,-7.45,-9.11,-10.05,-6.75,-12.46,-4.95,-14.16,-4.11,-14.81,-4.48,-14.3,-6,-12.8,-8.39,-10.68,-11.17,-8.48,-13.78,-6.72,-15.69,-5.86,-16.54,-6.14,-16.18,-7.56,-14.76,-9.84,-12.63,-12.53,-10.31,-15.06,-8.34,-16.91,-7.19,-17.69,-7.13,-17.24,-8.19,-15.66,-10.13,-13.31,-12.51,-10.68,-14.79,-8.35,-16.43,-6.78,-17.03,-6.29,-16.41,-6.94,-14.65,-8.52,-12.08,-10.61,-9.21,-12.69,-6.59,-14.21,-4.72,-14.76,-3.95,-14.13,-4.36,-12.39,-5.78,-9.83,-7.8,-6.95,-9.92,-4.3,-11.57</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B188" t="str">
+        <v>[L_10_标记]</v>
+      </c>
+      <c r="C188" t="str">
+        <v>67.5uv</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B189" t="str">
+        <v>[R_11_名字]</v>
+      </c>
+      <c r="C189" t="str">
+        <v>FERG(11)_dMax</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B190" t="str">
+        <v>[R_11_放大器]</v>
+      </c>
+      <c r="C190" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B191" t="str">
+        <v>[R_11_闪光]</v>
+      </c>
+      <c r="C191" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B192" t="str">
+        <v>[R_11_闪光背景]</v>
+      </c>
+      <c r="C192" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B193" t="str">
+        <v>[R_11_采样]</v>
+      </c>
+      <c r="C193" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B194" t="str">
+        <v>[R_11_分析时间]</v>
+      </c>
+      <c r="C194" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B195" t="str">
+        <v>[R_11_数据长度]</v>
+      </c>
+      <c r="C195" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B196" t="str">
+        <v>[R_11_详细数据(uv)]</v>
+      </c>
+      <c r="C196" t="str">
+        <v>-9.38,3.4,-11.36,3.95,-11.16,2.44,-8.89,-0.75,-5.18,-4.75,-1.06,-8.46,2.34,-10.83,4.12,-11.18,3.84,-9.33,1.62,-5.77,-1.84,-1.38,-5.54,2.71,-8.32,5.46,-9.46,6.12,-8.38,4.67,-5.31,1.65,-1.4,-2.2,2.93,-5.55,5.98,-8.01,7.05,-8.33,6.16,-6.38,3.19,-3.63,-1.09,-0.02,-6.08,2.56,-10.09,3.19,-11.81,1.41,-13.82,-0.8,-13.87,-8.99,-11.05,-15.03,-7.12,-19.32,-11.29,-24.68,-13.48,-28.85,-20.14,-25.42,-24.14,-30.01,-31.97,-32.99,-42.43,-29.36,-43.17,-35.16,-44.62,-32.7,-50.48,-25.89,-40.75,-47.07,-51.42,-40.61,-37.2,-38.46,-40.43,-32.9,-23.86,-48.75,-36.63,-35.22,-20.63,-18.02,-36.17,-8.71,-25.68,1.47,-12.52,2.07,16.16,21.56,0.27,24.77,27.99,47.69,49.09,61.79,64.86,52.59,81.77,82.74,130.33,127.45,129.57,122.89,135.11,132.57,167.21,175.68,195.99,197.95,205.76,228.43,201.81,247.3,202.37,242.79,231.34,255.78,247.34,248.96,286.16,312.26,332.8,266.11,297.06,318.59,340.84,350.22,350.85,334.7,334.5,336.96,362.38,370.58,387.57,349.2,363.47,370.88,392.47,399.76,383.06,376.93,421.58,387.95,391.76,354.12,404.54,377.98,392.01,352.21,408.22,404.35,339.93,372.07,374.15,360.7,348.49,384.16,302.94,346.06,299.63,311.92,305.1,351.31,303.91,327.99,327.55,300.74,270.44,255.88,281.69,247.82,293.89,284.14,261.39,224,240.01,237.28,219.61,230.25,201.9,199.35,198.69,219.16,200.05,180.2,189.6,201.02,184.95,188.9,188.4,180.28,151.87,171.83,177.53,136.94,150.86,151,153.56,124.03,134.59,139.19,132.64,117.4,100.72,106.76,95.43,118.93,95.34,112.37,80.16,94.61,98.77,71.43,88.51,90.89,86.72,60.9,90.74,65.85,75.12,45.21,62.44,56.94,67.22,60.66,45.4,56.13,29.06,54.15,35.24,55.51,27.95,30.57,34.23,27.08,24.16,15.66,35.49,6.13,20.85,3.36,22.76,5.51,12.22,6.95,6.38,9.15,3.02,3.06,-4,3.28,-10.6,5.53,-14.84,2.99,-13.27,-4.84,-11.98,-10.76,-11.05,-15.59,-10.57,-22.58,-7.3,-23.33,-7.91,-24.68,-12.4,-21.53,-15.11,-18.79,-20.65,-14.46,-26.44,-13.93,-30.44,-15.82,-30.27,-17.07,-26.14,-18.29,-26.49,-22.9,-18.18,-28.09,-14.56,-33.12,-14.44,-30.34,-20.01,-29.01,-22.26,-26.51,-22.88,-21.73,-24.79,-22.58,-29.71,-15.3,-38.23,-18.41,-38.14,-19.4,-34.4,-21.44,-31.62,-29.84,-28.33,-34.74,-24.5,-45.48,-20.4,-36.56,-32.96,-45.25,-30.07,-38.59,-41.39,-32.68,-39.8,-39.66,-41.21,-35.11,-40.92,-32.15,-47.88,-40.09,-40.48,-45.42,-45.36,-54.73,-35.26,-50.49,-32.87,-56.27,-37.96,-54.33,-35.23,-49,-45.33,-59.61,-58.61,-45.11,-60.85,-49.78,-69.52,-46.97,-67.2,-45.58,-52.11,-59.76,-58.2,-49.89,-49.94,-57.46,-61.21,-71.83,-53.67,-64.7,-49.93,-63.04,-49.35,-63.19,-49.51,-52.94,-68.66,-58.71,-56.98,-61.26,-59.22,-55.12,-69.13,-54.67,-71.91,-59.15,-67.89,-64.42,-60.19,-54.44,-59.12,-57.87,-48.94,-52.25,-57.75,-58.66,-59.75,-52.74,-50.96,-46.07,-61.04,-48.75,-60.71,-41.69,-63.42,-52.28,-63.27,-50.01,-55.16,-50.81,-60.01,-62.86,-58.52,-53.19,-51.22,-64.81,-55.41,-70.71,-39.46,-52.61,-46.26,-56.87,-54.33,-52.75,-49.52,-57.62,-53.38,-51.27,-63.81,-46.41,-66.31,-40.1,-62.39,-50.63,-60.14,-45.78,-42.59,-62.19,-40.79,-56.91,-46.8,-54.54,-36.28,-49.24,-45.35,-45.56,-48.13,-45.6,-55.51,-36.77,-59.31,-34.41,-57.94,-40.29,-46.85,-44.82,-53.28,-46.14,-38.71,-49.71,-44.1,-43.22,-30.83,-52.55,-37.62,-47.96,-29.43,-39.53,-31.81,-41.75,-40.91,-35.5,-34.91,-32.45,-44.58,-30.44,-40.68,-22.82,-42.61,-29.82,-31.32,-24.87,-31.42,-30.66,-21.9,-33.05,-22.43,-33.75,-22.59,-37.08,-21.86,-34.69,-23.5,-27.82,-23.55,-21.22,-30.43,-17.62,-33.95,-19.79</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B197" t="str">
+        <v>[R_11_标记]</v>
+      </c>
+      <c r="C197" t="str">
+        <v>a: 32.7ms -82.3uv b: 69.8ms 376.0uv</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B198" t="str">
+        <v>[L_11_名字]</v>
+      </c>
+      <c r="C198" t="str">
+        <v>FERG(11)_dMax</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B199" t="str">
+        <v>[L_11_放大器]</v>
+      </c>
+      <c r="C199" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B200" t="str">
+        <v>[L_11_闪光]</v>
+      </c>
+      <c r="C200" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B201" t="str">
+        <v>[L_11_闪光背景]</v>
+      </c>
+      <c r="C201" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B202" t="str">
+        <v>[L_11_采样]</v>
+      </c>
+      <c r="C202" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B203" t="str">
+        <v>[L_11_分析时间]</v>
+      </c>
+      <c r="C203" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B204" t="str">
+        <v>[L_11_数据长度]</v>
+      </c>
+      <c r="C204" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B205" t="str">
+        <v>[L_11_详细数据(uv)]</v>
+      </c>
+      <c r="C205" t="str">
+        <v>-30.4,-17.5,-29.18,-19.39,-27.52,-21.51,-25.55,-23.75,-23.4,-25.94,-21.23,-27.93,-19.2,-29.59,-17.44,-30.78,-16.03,-31.43,-15.09,-31.41,-14.68,-30.82,-14.83,-29.65,-15.43,-27.96,-16.61,-25.95,-17.97,-23.32,-19.92,-20.73,-21.74,-18.25,-23.24,-15.91,-25.63,-14.54,-26.8,-13.71,-27.86,-13.03,-29.05,-12.15,-29.02,-13.25,-30.44,-16.15,-30.43,-20.2,-31.36,-22.4,-29.56,-27.26,-32.2,-30.39,-31.68,-31.91,-32.08,-37.87,-32.14,-43.9,-37.65,-48.44,-37.03,-57.35,-32.76,-55.12,-37.44,-60.36,-37.21,-52.36,-47.06,-56.68,-56.55,-54.73,-59.2,-53.07,-57.23,-61.15,-59.57,-50.08,-51.46,-30.24,-38.03,-40.49,-51.14,-16.73,-47.41,-17.81,-50.15,-24.74,-26.84,-3.03,1.8,7.29,11.44,17.4,17.04,47.66,29.35,43.4,37.18,46.74,74.81,80.8,102.89,111.34,111.75,90.39,147.79,123.24,156.99,142.46,158.56,191.79,169.77,212.21,187.67,215.14,246.57,256.57,276.44,236.6,291.62,273.3,270.4,281.73,314.55,322.02,329.82,299.99,290.3,367.14,334.43,339.56,304.23,343.88,343.78,356.87,319.37,387.83,381.76,387.23,371,393.61,374.22,342.45,390.2,368.09,358.64,345.18,328.54,324.49,347.64,330.06,407.08,389.84,337.16,368.01,322.04,362.53,335.04,362.36,342.93,300.41,363.12,345.68,304.03,303.99,285.77,302.49,295.57,273.51,293.93,302.27,243.59,260.96,246.39,265.8,240.65,220.08,226.82,231.04,229.54,237.76,219.93,203.42,201.51,199.22,203.93,215.59,188.86,192.03,182.24,169.05,165.89,180.54,151.18,149.35,159.43,125.47,146.99,116.89,135.42,123.42,154.22,121.62,121.21,127.46,136.45,97.45,115.22,86.9,102.83,85.94,104.1,94.38,100.62,81.18,96.81,85.25,64.29,88.89,78.33,85.16,60.99,57.28,58.79,63.11,53.24,59.04,42.68,52.4,47.55,48.85,33.89,47.17,26.36,40.42,28.25,28.14,18.82,18.19,18.45,23.86,18.12,16.1,14.36,13.55,16.06,8.03,16.51,-4.26,12.02,-8.28,6.39,-10.73,4.15,-10.69,3.7,-9.5,-0.2,-13.42,-3.13,-12.75,-6.25,-15.89,-10.43,-16.28,-17.81,-10.61,-22.04,-14.53,-23.64,-14.55,-25.59,-10.24,-30.18,-12.08,-30.71,-13.79,-31.15,-11.32,-30.07,-18.04,-31.23,-17.28,-26.92,-21.35,-26.49,-25.71,-24.8,-27.55,-24.51,-28.11,-20.32,-26.97,-17.55,-30.72,-18.49,-32.22,-17.06,-34.68,-16.06,-30.09,-15.08,-31.87,-23.25,-33.36,-22.88,-27.07,-23.41,-26.16,-25.24,-29.26,-25.23,-31.25,-26.9,-28.18,-35.76,-20.04,-35.42,-27.84,-35.87,-17.11,-38.93,-21.69,-38.82,-26.84,-37.26,-25.58,-45.47,-34.32,-38.16,-24.73,-42.42,-28.82,-33.45,-33.1,-42.02,-38.92,-32.91,-49.78,-29.82,-52.19,-43.54,-53.86,-31.83,-46.28,-29.42,-49.22,-41.17,-57.19,-47.73,-58.17,-37.82,-61.31,-37.93,-62.5,-38.62,-55.3,-43.14,-42.88,-43.83,-44.27,-60.08,-47.72,-58.97,-42.47,-66.99,-51.15,-50.12,-36.92,-66.02,-36.36,-55.32,-39.52,-55.96,-32.21,-50.66,-37.7,-54.14,-44.87,-45.14,-49.46,-44.93,-58.18,-55.2,-55.29,-42.91,-59.53,-50.62,-53.49,-41,-51.26,-29.84,-42.34,-34.27,-54.77,-25.24,-42.17,-35.64,-50.08,-39.71,-51.72,-44.65,-42.1,-35,-33.74,-32.74,-41.52,-40.2,-45.59,-45.34,-30.36,-42.05,-33.28,-45.57,-27.42,-44.82,-34.18,-54.64,-37.89,-48.48,-24.51,-52.27,-28.42,-43.67,-29.59,-48.67,-25.21,-39.74,-26.96,-35.41,-39.66,-27.37,-39.27,-35.39,-41.99,-29.61,-45.63,-30.61,-43.28,-24.31,-41.11,-19.95,-35.77,-31.47,-38.18,-27.42,-42.72,-22.49,-34.4,-23.49,-39.77,-29.21,-34.8,-25.62,-32.79,-33.33,-20.38,-34.27,-22.41,-32.44,-21.43,-29.66,-17.29,-32.75,-15.65,-26.19,-14.01,-26.92,-9.54,-29.72,-15.05,-22.52,-9.58,-19.33,-13.73,-19.71,-13.2,-13.33,-11.5,-7.06,-16.64,-6.58,-17.74,-1.26,-17.09,-3.46,-18.09,-1.28,-17.78,1.03,-17.54,3.44,-12.18,-0.33,-11.41</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B206" t="str">
+        <v>[L_11_标记]</v>
+      </c>
+      <c r="C206" t="str">
+        <v>a: 32.7ms -87.3uv b: 69.8ms 426.0uv</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B207" t="str">
+        <v>[R_12_名字]</v>
+      </c>
+      <c r="C207" t="str">
+        <v>FERG(12)_dOps</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B208" t="str">
+        <v>[R_12_放大器]</v>
+      </c>
+      <c r="C208" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B209" t="str">
+        <v>[R_12_闪光]</v>
+      </c>
+      <c r="C209" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B210" t="str">
+        <v>[R_12_闪光背景]</v>
+      </c>
+      <c r="C210" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B211" t="str">
+        <v>[R_12_采样]</v>
+      </c>
+      <c r="C211" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B212" t="str">
+        <v>[R_12_分析时间]</v>
+      </c>
+      <c r="C212" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B213" t="str">
+        <v>[R_12_数据长度]</v>
+      </c>
+      <c r="C213" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B214" t="str">
+        <v>[R_12_详细数据(uv)]</v>
+      </c>
+      <c r="C214" t="str">
+        <v>-3.5,5.17,-3.97,2.56,1.71,-2.92,5.94,-3.1,3.2,2.72,-2.17,6.83,-2.11,3.97,3.87,-1.26,7.89,-0.95,4.87,5.07,-0.38,8.8,0.04,5.49,5.92,0.09,9.29,0.53,5.53,6.29,0.1,9.32,0.64,5.45,6.63,0.33,9.78,1.32,5.97,7.57,1.05,10.54,2.56,6.89,8.44,1.66,11.19,2.55,6.11,8.04,0.49,9.32,0.62,3.45,5.34,-2.69,6.52,-2.68,0.71,2.96,-4.47,4.96,-2.14,1.23,5.16,-1.63,8.98,2.45,5.99,10.6,2.43,12.91,6.12,7.57,10.34,1.49,9.6,0.42,0.5,2.76,-7.39,0.72,-7.77,-8.4,-5.34,-13.16,-3.22,-9.99,-6.91,1.43,-4.28,8.02,5.92,9.32,17.45,11.35,25.3,19.25,19.33,24.15,11.29,22.36,12.46,7.93,8.24,-4.91,-0.87,-11.18,-12.66,-9.31,-22.08,-17.03,-15.85,-14.06,-6.65,-8.94,5.07,6.08,10.86,24.28,24.03,38.31,32.42,38.54,42.41,31.82,38.79,27.89,19.93,20.48,3.41,4.82,-8.92,-13.82,-13.06,-28.18,-27.29,-27.38,-23.46,-19.51,-19.02,-5.98,-4.76,1.92,17.16,13.83,28.99,34.2,37.38,44.56,37.12,41.62,28.28,24.08,27.64,11.01,9.74,1.09,-8.37,-8.12,-25.46,-16.81,-24.39,-28.28,-16.17,-23.48,-15.23,-12.35,-9.53,6.62,3.2,14.94,16.82,18.08,32.63,24.4,26.79,29.01,18.69,27.35,11.01,13.6,10.05,0.15,4.96,-6.27,-4.16,-8.3,-15.14,-4.76,-12.11,-3.63,-1.35,-4.1,7.05,1.76,10.33,13.52,10.17,21.33,14.86,19.26,20.69,13.41,21.29,12.42,16.12,14.89,7.09,14.59,4.52,7.24,8.16,0.48,8.79,0.65,5.21,7.41,1.13,11.85,4.57,9.27,12.18,5.87,16.12,8.04,12.3,14.73,6.68,16.67,7.73,10.68,12.99,4.91,13.72,5.36,7.82,10.33,2.16,11.31,3.83,6.23,9.5,1.38,10.97,3.87,6.24,9.96,1.96,11.48,4.49,6.5,10.42,2.18,11.53,4.75,6.29,10.53,2.02,11.33,4.72,6.05,10.57,2.06,11.39,5.12,6.23,11.15,2.6,11.92,6.01,6.83,12.11,3.47,12.79,7.14,7.63,13.19,4.44,13.66,8.27,8.4,14.23,5.36,14.44,9.31,9.08,15.16,6.17,15.11,10.24,9.64,15.95,6.84,15.61,10.99,10.01,16.53,7.3,15.88,11.5,10.13,16.83,7.49,15.86,11.73,9.97,16.85,7.41,15.56,11.68,9.54,16.6,7.08,15.02,11.42,8.9,16.15,6.58,14.3,11,8.14,15.58,5.99,13.51,10.53,7.34,14.99,5.41,12.73,10.09,6.61,14.46,4.93,12.07,9.79,6.02,14.1,4.63,11.59,9.69,5.67,13.96,4.59,11.37,9.86,5.59,14.09,4.83,11.42,10.31,5.78,14.49,5.35,11.74,11.01,6.24,15.13,6.11,12.28,11.93,6.91,15.95,7.04,12.98,12.99,7.7,16.87,8.07,13.73,14.08,8.52,17.78,9.08,14.45,15.13,9.27,18.6,9.99,15.04,16.02,9.87,19.23,10.72,15.42,16.69,10.24,19.61,11.19,15.55,17.09,10.34,19.71,11.39,15.39,17.21,10.18,19.53,11.33,14.96,17.07,9.76,19.11,11.04,14.32,16.73,9.17,18.5,10.6,13.53,16.25,8.48,17.8,10.09,12.7,15.74,7.78,17.1,9.62,11.92,15.3,7.17,16.51,9.27,11.27,15.01,6.75,16.09,9.13,10.85,14.94,6.57,15.92,9.25,10.69,15.14,6.67,16.02,9.65,10.81,15.61,7.06,16.39,10.32,11.19,16.33,7.69,16.98,11.22,11.78,17.24,8.51,17.74,12.26,12.5,18.25,9.42,18.55,13.36,13.26,19.28,10.34,19.34,14.41,13.95,20.21,11.16,20.01,15.33,14.49,20.97,11.81,20.47,16.04,14.81,21.49,12.21,20.67,16.49,14.87,21.73,12.34,20.58,16.66,14.65,21.68,12.21,20.23,16.56,14.18,21.39,11.85,19.64,16.26,13.51,20.9,11.33,18.9,15.83,12.74</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B215" t="str">
+        <v>[R_12_标记]</v>
+      </c>
+      <c r="C215" t="str">
+        <v>72.9uv</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B216" t="str">
+        <v>[L_12_名字]</v>
+      </c>
+      <c r="C216" t="str">
+        <v>FERG(12)_dOps</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B217" t="str">
+        <v>[L_12_放大器]</v>
+      </c>
+      <c r="C217" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B218" t="str">
+        <v>[L_12_闪光]</v>
+      </c>
+      <c r="C218" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B219" t="str">
+        <v>[L_12_闪光背景]</v>
+      </c>
+      <c r="C219" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B220" t="str">
+        <v>[L_12_采样]</v>
+      </c>
+      <c r="C220" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B221" t="str">
+        <v>[L_12_分析时间]</v>
+      </c>
+      <c r="C221" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B222" t="str">
+        <v>[L_12_数据长度]</v>
+      </c>
+      <c r="C222" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B223" t="str">
+        <v>[L_12_详细数据(uv)]</v>
+      </c>
+      <c r="C223" t="str">
+        <v>11.5,-10.55,6.54,-1.56,-4.91,8.33,-12.38,9.75,-8.86,1.47,2.4,-8.71,10.49,-10.92,9.75,-2.44,1.19,10.81,-5.52,17.7,-2.83,13.44,9.98,3.8,20.91,-1.27,20.95,4.12,11.38,13.64,-0.74,18.75,-4.96,13.43,1.46,0.86,11.7,-7.88,13.29,-6.16,8.79,7.69,0.52,20.02,-0.37,22.93,8.87,18.11,25.04,8.61,29.48,8.81,23.15,13.54,9.01,19.96,-3.56,15.8,-7.14,0.13,-2.98,-17.58,0.76,-21.99,-3.37,-16.05,-10.33,1.53,-14.09,12.67,-5.02,13.9,13.32,9.64,25.52,9,28.43,17.7,18.97,18.59,2.73,19.76,-7.91,4.72,-10.27,-14.81,-10.48,-34.88,-17.58,-32.44,-20.49,-26.15,-26.04,-5.66,-19.56,7.12,-1.45,10.52,22.5,15.56,35.38,19.79,39.37,30.8,24.17,41.62,12.09,29.19,3.04,7.57,-1.34,-15.01,-7.58,-30.79,-9.15,-28.51,-22.43,-19.51,-26.94,0.59,-15.69,7.63,10.65,15.11,38.53,23.93,46.39,30.67,40.73,43.21,28.65,45.28,20.96,34.28,14.05,8.21,11,-17.1,-0.11,-28.31,-15.33,-20.35,-23.55,-5.13,-33.27,-6.48,-12.97,-1.35,10.98,3.83,28.25,10.16,33.24,33.46,27.12,38.91,20.77,38.51,14.3,20.46,12.66,-2.76,9.74,-18.44,-4.82,-20.89,-16.62,-11.2,-32.25,-6.99,-28.85,-10.35,-12.27,-10.96,8.28,-7.47,19.19,3.29,15.29,18.64,8.21,32.84,7.47,26.13,9.37,7.86,17.21,-5.11,13.71,-10.24,2.45,-2,-10.53,3.73,-15.47,3.49,-8.18,-1.74,6.82,-5.56,18.13,-1.23,19.08,12.63,11.4,25.39,5.87,29.55,9.01,21.45,19.92,8.69,25.65,1.69,20.97,5.3,7.93,14.57,-2.5,19.26,-3.6,13.91,6.33,3.28,18.16,-1.6,21.14,3.75,13.97,15.55,4.27,23.78,0.8,20.37,7.9,9.34,17.99,-1.33,20.11,-1.49,12,6.95,-0.84,14.85,-7.32,13.79,-2.97,3.84,7.79,-6.44,14.52,-7.82,10.42,0.8,-0.47,11.48,-8.04,14.31,-5.48,6.77,5.1,-4.37,13.49,-8.83,12.02,-2.42,1.94,8.72,-7.47,14.38,-7.35,9.48,2.49,-1.19,13.31,-7.18,15.53,-2.44,7.8,9.33,-2.04,17.92,-4.14,16.1,4.2,6.32,15.97,-1.63,20.96,0.27,15.21,10.94,4.67,21.07,-0.3,21.83,5.41,13,17,3.23,24.14,1.94,20.53,10.65,9.8,21.49,2.08,24.55,4.59,17.02,15.01,5.83,23.55,1.17,22.09,7.14,11.68,17.83,1.6,22.93,0.73,17.21,9.37,5.44,18.93,-2.06,19.95,1.04,10.85,11.24,-0.58,18.42,-4.39,15.29,2.33,4.13,12.74,-5.3,16.61,-4.8,9.85,4.68,-1.74,13.92,-7.79,14.02,-3,4.62,7.97,-5.74,14.82,-7.53,11.17,0.92,0.46,11.89,-7.22,15.4,-4.5,8.5,6.44,-2.04,15.86,-6,15.53,0.83,6.3,12.69,-2.66,19.21,-2.4,15.02,7.53,4.68,18.6,-1.52,21.25,2.86,13.7,14.42,3.62,23.1,0.97,21.44,8.78,11.52,20.32,3.02,25.34,4.23,19.54,14.34,8.58,24.21,2.81,24.84,7.67,15.68,18.66,5.18,25.48,2.93,21.63,10.79,10.39,21.14,1.83,24,3.45,16.24,13.25,4.54,21.59,-0.84,20.14,4.49,9.62,14.94,-0.86,20.18,-2.23,14.71,6.15,2.96,15.89,-4.76,17.38,-1.85,8.71,8.48,-2.55,16.22,-6.37,13.83,0.47,3.24,11.39,-5.93,16.11,-5.27,10.2,4.59,-0.82,14.59,-6.6,15.65,-1.56,7.05,9.95,-2.88,17.65,-4.5,14.87,4.21,4.73,15.73,-2.77,20,-0.04,13.72,11.06,3.39,20.93,-0.71,21.11,5.91,12.13,17.79,2.97,24.57,2.76,20.57,12.29,10.06,23.24,3.28,25.92,6.94,18.23,17.99,7.6,26.44,4.1,24.62,11.08,14.28,22.1,4.99,26.87,5.24,20.8,14.58,9.26,24.06,2.61,24.51,6.61,15.06,17.06,3.96</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B224" t="str">
+        <v>[L_12_标记]</v>
+      </c>
+      <c r="C224" t="str">
+        <v>75.5uv</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B225" t="str">
+        <v>[R_13_名字]</v>
+      </c>
+      <c r="C225" t="str">
+        <v>FERG(13)_dMax</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B226" t="str">
+        <v>[R_13_放大器]</v>
+      </c>
+      <c r="C226" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B227" t="str">
+        <v>[R_13_闪光]</v>
+      </c>
+      <c r="C227" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B228" t="str">
+        <v>[R_13_闪光背景]</v>
+      </c>
+      <c r="C228" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B229" t="str">
+        <v>[R_13_采样]</v>
+      </c>
+      <c r="C229" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B230" t="str">
+        <v>[R_13_分析时间]</v>
+      </c>
+      <c r="C230" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B231" t="str">
+        <v>[R_13_数据长度]</v>
+      </c>
+      <c r="C231" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B232" t="str">
+        <v>[R_13_详细数据(uv)]</v>
+      </c>
+      <c r="C232" t="str">
+        <v>-14.4,-24.13,-11.17,-14.55,-23.13,-9.81,-14.76,-22.06,-8.6,-15.06,-20.98,-7.59,-15.46,-19.9,-6.8,-15.96,-18.86,-6.25,-16.58,-17.89,-5.98,-17.3,-17.01,-5.99,-18.13,-16.25,-6.29,-19.05,-15.63,-6.88,-20.12,-15.16,-7.76,-21.29,-14.82,-9.02,-22.49,-14.78,-10.47,-23.99,-15.38,-12.6,-25.73,-15.64,-15.44,-27.53,-17.49,-18.67,-30.57,-18.15,-22.61,-32.03,-22.86,-26.5,-38.26,-25.2,-32.09,-43.98,-30.77,-38.59,-46.8,-35.27,-50.03,-55.03,-40.87,-56.31,-61.67,-45.42,-56.2,-61.58,-58.4,-76.89,-74.16,-56.68,-82.31,-67.96,-71.34,-85.54,-77.52,-72.34,-87.93,-81.75,-71.5,-72.72,-77.41,-62.27,-64.64,-57.44,-55.58,-59.14,-46.29,-38.83,-53.17,-33.55,-23.58,-34.39,-16.1,-3.18,-6.51,1.93,23.03,27.2,34.78,36.18,50.01,66.37,83.08,64.16,112.2,86.64,92.33,119.12,132.5,128.92,154.75,156.35,148.29,199.49,182.18,202.55,220.71,203.51,224.2,219.71,204.36,222.38,275.59,269.42,258.41,265.01,266.62,257.72,323.92,324.57,281.76,296.32,283.27,306.31,293.42,343.52,335.52,319.74,328.52,368.43,344.82,329.51,336.43,309.59,297.6,342.18,325.37,313.72,363.46,351.39,340.22,352.84,330.49,324.92,287.82,289.19,310.99,290.55,253.36,264.05,266.55,273.44,250.29,268.53,218.37,199.67,221.04,232.93,183.56,196.03,185.79,171.86,192.3,173.35,172.27,149.38,166.81,144.81,158.98,126.82,126.65,145.83,131.23,131.01,124.4,119.23,111.8,110.35,92.56,113.63,112.18,82.88,89.31,85.63,73.37,94.99,76.5,88.42,75.08,81.87,71.91,87.07,57.67,51.12,83,57.8,45.1,81.19,50.65,58.23,63.65,51.58,55.21,68.43,57.67,42.84,54,48.52,24.78,50.45,30.3,31.6,51.63,20.63,38.26,45.5,30,22,30.32,7.92,14.92,20.83,11.25,17.77,11.24,9.61,5.49,7.25,-4.72,4.68,6.96,-7.58,-1.08,4.52,-7.91,4.55,-0.88,-13.22,0.72,-3.5,-15.31,-1.93,-9.13,-15.29,-1.07,-8.7,-18.47,-5.33,-12.65,-18.67,-8.21,-14.8,-20.63,-7.73,-19.7,-21.83,-6.81,-18.29,-19.87,-12.03,-22,-19.66,-10.29,-24.45,-18.88,-13.48,-24.95,-18.58,-14.06,-27.72,-23.53,-17.24,-29.58,-22.79,-18.48,-26.9,-23.32,-20.91,-33.23,-24.39,-18.8,-29.29,-22.58,-18.54,-35.21,-19.6,-25.44,-37.59,-25.21,-25.32,-35.12,-25.89,-33.79,-37.02,-30.23,-35.5,-42.57,-23.4,-34.73,-36.07,-27.44,-40.07,-47.44,-32.8,-46.55,-46.98,-26.9,-49.3,-49.82,-30.72,-44.79,-41,-35.4,-53.47,-44.01,-37.68,-50.24,-44.75,-36.48,-44.62,-43.56,-42.85,-51.65,-49.43,-44.44,-57.72,-50.33,-43.16,-57.97,-52.84,-45.97,-53.56,-48.37,-50.21,-57.61,-46.44,-49.12,-60.18,-42.22,-41.35,-48.6,-47.69,-54.92,-55.99,-47.04,-41.75,-52.7,-34.25,-51.47,-56.66,-42.21,-56.37,-62.94,-40.7,-56.1,-43.89,-47.46,-45.47,-48.47,-41.78,-45.85,-58.43,-45.85,-49.89,-44.12,-31.72,-47.15,-41.68,-40.27,-64.81,-56.26,-33.83,-56.97,-51.72,-35.61,-64.36,-52.11,-38.82,-57.76,-51.87,-53.86,-55.47,-40.95,-55.34,-67.19,-46.46,-56.14,-66.94,-48.12,-54.79,-65.57,-46.14,-51.88,-61.38,-49.83,-44.57,-55.38,-39.35,-52.79,-55.13,-37.47,-47.42,-57,-33.99,-54.41,-61.81,-33.35,-57.7,-52.86,-37.3,-59.61,-43.02,-32.7,-44.67,-54.43,-36.39,-47.45,-41.84,-35.39,-43.05,-39.61,-33.42,-44.55,-45.61,-30.8,-41.5,-34.93,-32.98,-47.03,-37.95,-29.07,-44.49,-33.8,-31.69,-42.27,-27.93,-27.78,-37.99,-30.4,-26.41,-37.58,-23.1,-25.48,-38.75,-25.3,-26.93,-38.37,-17.78,-25.17,-30.06,-20.99,-26.69,-33.71,-15.17,-28.31,-27.75,-13.24,-25.95,-24.74,-15.75,-23.94,-22.84,-12.85,-26.05,-27.45,-17.06,-26.49,-20.75,-13.05,-24.84,-22.92,-13.94,-26.99,-22.9,-12.49,-28.29,-20.8,-15.22,-28.66,-19.5,-15.39,-29.87,-16.54,-19.33,-29.17,-18.26</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B233" t="str">
+        <v>[R_13_标记]</v>
+      </c>
+      <c r="C233" t="str">
+        <v>a: 36.8ms -98.3uv b: 77.7ms 467.7uv</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B234" t="str">
+        <v>[L_13_名字]</v>
+      </c>
+      <c r="C234" t="str">
+        <v>FERG(13)_dMax</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B235" t="str">
+        <v>[L_13_放大器]</v>
+      </c>
+      <c r="C235" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B236" t="str">
+        <v>[L_13_闪光]</v>
+      </c>
+      <c r="C236" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B237" t="str">
+        <v>[L_13_闪光背景]</v>
+      </c>
+      <c r="C237" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B238" t="str">
+        <v>[L_13_采样]</v>
+      </c>
+      <c r="C238" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B239" t="str">
+        <v>[L_13_分析时间]</v>
+      </c>
+      <c r="C239" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B240" t="str">
+        <v>[L_13_数据长度]</v>
+      </c>
+      <c r="C240" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B241" t="str">
+        <v>[L_13_详细数据(uv)]</v>
+      </c>
+      <c r="C241" t="str">
+        <v>13.07,12.42,5.76,15.5,10.16,7.82,16.7,8.15,10.79,16.46,7.04,13.99,14.95,7.22,16.64,12.68,8.75,18.13,10.33,11.28,18.13,8.61,14.21,16.69,8.03,16.78,14.24,8.76,18.31,11.44,10.62,18.39,9.02,13.07,16.97,7.59,15.41,14.33,7.47,16.92,11.16,8.6,17.05,8.11,10.46,15.66,5.86,12.5,12.98,4.89,14.05,9.47,5.16,14.11,5.53,6.19,12.76,2.42,8.04,9.74,0.33,8.93,5.21,-0.93,8.16,-0.03,-1.71,6.03,-4.81,-1.84,-0.26,-10.57,-2.25,-6.46,-16.6,-9.28,-12.96,-17.61,-12.66,-24.12,-18.31,-18.07,-27.92,-22.73,-19.55,-30,-32.32,-33.05,-29.95,-32.52,-40.78,-43.24,-28.69,-43.39,-33.82,-42.86,-35.23,-37.84,-29.73,-39.83,-24.09,-32.13,-27.39,-7.78,-30.25,-18.89,3.03,-8.92,0.97,5.08,0.38,19.65,27.94,16.99,46.04,42.95,60.51,51.78,45.66,62.16,82.39,79.32,109.51,120.19,117.79,130.69,118.2,133.45,143.24,142.39,154.18,195.03,186.77,188.67,224.75,215.07,209.86,206.13,257.76,262.38,242.24,253.37,311.7,268.09,318.73,309.28,283.99,310.88,346.89,342.23,311.64,297.93,335.66,373.51,358.25,382.77,329.29,362.49,365.76,398.24,367.96,327.63,392.09,381.41,354.7,361.11,364.86,358.35,384.68,374.7,314.31,382.41,383.18,307,315.18,356.82,352.67,289.97,315.33,344.42,347.12,325.35,321.83,308.72,275.78,284.8,268.35,260.18,283.32,246.86,262.02,275.79,238.8,203.6,222.01,249.54,223.08,189.92,189.98,203.7,204.05,195.81,189.16,190.82,151.5,177.7,169.44,151.91,166.22,145.52,140.75,146.69,137.91,151.84,147.21,119.42,139.29,117.72,125.3,115.22,102.92,121.63,100.54,119.59,101.37,101.98,85.85,102.29,101.23,73.76,84.9,95.39,68.47,90.54,65.04,78.79,67.72,81.29,81.27,70.35,71.74,67.55,55.25,62.63,65.4,45.55,61.72,55.15,44,55.4,52.05,43.7,49.51,36.54,30.91,40.57,42.85,25.7,36.09,22.31,25.89,36.44,22.3,33.27,30.78,15.68,25.82,24.53,17.35,24.58,13.69,15.63,22.71,10.5,15.33,17.69,12.54,18.69,11.66,8.34,18.9,6.83,5.8,13.93,4.36,8.14,13.32,0.43,13.11,9.95,2.71,8.71,1.63,3.58,9.7,-2.26,1.44,9.31,-5.14,3.04,0.91,-7.03,5.31,-4.08,-4.29,6.27,-4.1,-0.82,2.32,-7.5,0.21,-1.57,-9.99,-0.99,-4.92,-9.57,-4.74,-7.76,-6.79,-3.19,-12.79,-11.74,-7.86,-18.32,-5.61,-11.36,-14.18,-6.13,-20.46,-20.19,-8.98,-22.3,-18.64,-7.46,-17.26,-15.62,-19.31,-21.54,-19,-15.44,-25.61,-18.36,-19.93,-25.08,-17.42,-24.19,-16.85,-18.33,-19.58,-18.61,-18.04,-31.78,-18.63,-25.73,-26.87,-19.92,-31.7,-23.17,-23.36,-22.01,-15.52,-18.99,-22.1,-18.8,-33.43,-23.17,-23.12,-28.39,-27.57,-13.11,-35.33,-30.98,-28.05,-38.68,-16.24,-33.47,-24.42,-14.4,-36.8,-30.3,-16.89,-26.25,-25.46,-19.21,-40.41,-17.45,-31.98,-30.95,-32.08,-34.18,-28.1,-26.96,-26.53,-30.57,-23.94,-43.61,-32.6,-35.99,-42.86,-33.71,-35.24,-33.2,-27.58,-26.43,-25.32,-26.05,-28.43,-30.21,-38.05,-45.84,-28.67,-35.88,-34.06,-18.18,-33.82,-41.83,-35.85,-43.41,-28.57,-32.37,-45.07,-24.23,-34.53,-36.02,-21.14,-27.22,-40.83,-23.84,-34.05,-21.9,-26.15,-34.62,-23.28,-22.88,-38.45,-24.66,-34,-34.96,-23.06,-26.61,-22.24,-15.02,-35.81,-20.74,-15.4,-25.63,-11.27,-23.14,-23.53,-15.07,-24.9,-20.69,-22.19,-24.41,-21.12,-15.4,-18.62,-8.66,-18.78,-16.25,-7.32,-14.45,-14.84,-14.87,-20.32,-18.14,-7.84,-13.36,-5.36,-8.93,-13.54,-2.79,-10.67,-15.36,-1.63,-19.27,-8.25,-3.93,-19.4,-8.36,-7.76,-16.7,-4.8,-7.9,-7.56,-0.12,-8.66,-5.8,-2.13,-11.25,-6.48,-7.62,-10.9,-5.08,-9.18,-13.04,-4.51,-11.71,-5.47,-1.89</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B242" t="str">
+        <v>[L_13_标记]</v>
+      </c>
+      <c r="C242" t="str">
+        <v>a: 37.0ms -98.5uv b: 77.9ms 498.4uv</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B243" t="str">
+        <v>[R_14_名字]</v>
+      </c>
+      <c r="C243" t="str">
+        <v>FERG(14)_dOps</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B244" t="str">
+        <v>[R_14_放大器]</v>
+      </c>
+      <c r="C244" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B245" t="str">
+        <v>[R_14_闪光]</v>
+      </c>
+      <c r="C245" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B246" t="str">
+        <v>[R_14_闪光背景]</v>
+      </c>
+      <c r="C246" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B247" t="str">
+        <v>[R_14_采样]</v>
+      </c>
+      <c r="C247" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B248" t="str">
+        <v>[R_14_分析时间]</v>
+      </c>
+      <c r="C248" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B249" t="str">
+        <v>[R_14_数据长度]</v>
+      </c>
+      <c r="C249" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B250" t="str">
+        <v>[R_14_详细数据(uv)]</v>
+      </c>
+      <c r="C250" t="str">
+        <v>-20.72,-11.36,-17.36,-24.43,-15.78,-12.19,-22.36,-22.27,-12.32,-16.65,-24.95,-17.6,-12.12,-21.62,-23.33,-12.9,-14.92,-24.19,-18.14,-11.09,-19.44,-23.24,-13.31,-13.66,-23.87,-20.3,-12.3,-20.04,-26.38,-17.66,-16.45,-27.34,-26.22,-17.07,-23.51,-31.75,-23.7,-19.67,-29.25,-29.32,-18.38,-21.27,-28.98,-21.08,-13.74,-21.86,-24.39,-13.47,-13.49,-24.71,-18.94,-12.14,-21.13,-26.93,-18.04,-19.56,-32,-30.54,-22.69,-31.51,-37.07,-31.13,-25.96,-36.09,-34.98,-24.17,-26.07,-31.41,-19.51,-12,-17.55,-14.44,-2.02,-4.93,-13.28,-2.55,4.17,-8.62,-13.77,-5.45,-10.9,-25.32,-23.66,-19.92,-34.35,-39.89,-36.26,-33.61,-48.81,-41.07,-31.58,-33.44,-35.17,-21.26,-12.62,-16.47,-9.13,7.21,7.94,0.84,9.12,10.88,6.45,-1.86,8.36,0.94,-16.86,-16.42,-17.89,-31.91,-40.12,-40.2,-43.08,-54.4,-48.83,-45.14,-46.23,-46.85,-32.05,-26.88,-29.62,-18.91,-3.54,0.15,-1.62,9.34,18.85,7.94,4.32,13.71,3.84,-12.46,-9.56,-13.27,-30.08,-37.92,-35.38,-46.08,-52.48,-54.33,-44.68,-55.25,-50.09,-42.62,-37.73,-38.38,-28.3,-14.33,-16.04,-13.95,-3.66,4.66,-8.22,-2.18,8.2,0.5,-10,-5.96,-8.06,-21.9,-25.91,-20.01,-28.21,-41.41,-34.55,-32.01,-38.15,-39.76,-29.91,-32.1,-35.17,-25.09,-15.07,-20.12,-20.37,-5.62,-5.82,-11.18,-8.09,0.41,-4.63,-13.25,-3.01,-4.31,-16.79,-17.99,-10.86,-19.14,-27.49,-20.73,-18.89,-30.63,-30.69,-20.35,-23.93,-30.15,-22.15,-15.27,-23.85,-24.14,-12.57,-13.9,-22.65,-16.78,-8.73,-17.86,-21.54,-12.7,-13.71,-23.83,-20.97,-13.44,-21.93,-28.52,-19.74,-18.6,-29.05,-27.56,-18.09,-23.82,-31.52,-22.4,-18.34,-28.01,-28.01,-17.48,-21.02,-29.33,-22.08,-15.97,-25.31,-27.51,-17.13,-19,-28.64,-23.21,-15.8,-24.22,-28.44,-18.42,-18.17,-28.27,-24.43,-15.62,-22.55,-28.29,-18.65,-16,-26,-24.11,-14.2,-19.29,-26.56,-17.97,-13.38,-23.18,-23.38,-13.03,-16.32,-25.01,-17.9,-11.63,-20.82,-23.22,-12.84,-14.21,-23.83,-18.51,-10.78,-18.94,-23.37,-13.38,-12.74,-22.91,-19.58,-10.69,-17.51,-23.83,-14.67,-12.06,-22.42,-21.23,-11.59,-16.81,-24.74,-16.79,-12.32,-22.4,-23.38,-13.36,-16.73,-25.92,-19.47,-13.27,-22.62,-25.69,-15.66,-16.99,-27.01,-22.28,-14.58,-22.77,-27.75,-18.08,-17.27,-27.67,-24.83,-15.9,-22.55,-29.21,-20.25,-17.32,-27.63,-26.75,-16.94,-21.75,-29.78,-21.9,-16.94,-26.72,-27.83,-17.53,-20.29,-29.36,-22.88,-16.09,-24.94,-28,-17.64,-18.26,-28,-23.21,-14.9,-22.48,-27.39,-17.44,-15.91,-25.96,-23.09,-13.64,-19.67,-26.27,-17.17,-13.6,-23.59,-22.8,-12.64,-16.92,-24.97,-17.15,-11.73,-21.27,-22.64,-12.24,-14.61,-23.82,-17.64,-10.62,-19.36,-22.85,-12.66,-13.06,-23.07,-18.79,-10.48,-18.06,-23.54,-13.98,-12.4,-22.78,-20.58,-11.33,-17.43,-24.65,-16.11,-12.59,-22.9,-22.85,-13,-17.33,-25.97,-18.77,-13.42,-23.2,-25.26,-15.18,-17.53,-27.19,-21.58,-14.58,-23.38,-27.42,-17.5,-17.73,-27.96,-24.14,-15.74,-23.15,-28.97,-19.57,-17.63,-27.99,-26.08,-16.6,-22.29,-29.63,-21.12,-17.08,-27.12,-27.18,-17.01,-20.74,-29.29,-22.02,-16.05,-25.36,-27.41,-16.97,-18.61,-28.03,-22.33,-14.69,-22.91,-26.89,-16.65,-16.15,-26.09,-22.23,-13.28,-20.1,-25.89,-16.32,-13.75,-23.82,-22.01,-12.17,-17.35,-24.75,-16.28,-11.78,-21.63,-21.97,-11.68,-15.05,-23.78,-16.8,-10.59,-19.83,-22.33,-12.04,-13.48,-23.2,-18.02,-10.37,-18.62,-23.2,-13.33,-12.79,-23.09,-19.9,-11.13,-18.04,-24.48,-15.44,-12.91,-23.35,-22.27,-12.7,-17.96,-25.97,-18.09,-13.63,-23.74,-24.78,-14.77,-18.12,-27.32,-20.89,-14.66,-23.97,-27.03,-16.96,-18.22,-28.19,-23.43,-15.64,-23.74,-28.67,-18.91,-17.99,-28.29,-25.37,-16.32,-22.84,-29.41,-20.35,-17.27,-27.46,-26.49,-16.55</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B251" t="str">
+        <v>[R_14_标记]</v>
+      </c>
+      <c r="C251" t="str">
+        <v>65.2uv</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B252" t="str">
+        <v>[L_14_名字]</v>
+      </c>
+      <c r="C252" t="str">
+        <v>FERG(14)_dOps</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B253" t="str">
+        <v>[L_14_放大器]</v>
+      </c>
+      <c r="C253" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B254" t="str">
+        <v>[L_14_闪光]</v>
+      </c>
+      <c r="C254" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B255" t="str">
+        <v>[L_14_闪光背景]</v>
+      </c>
+      <c r="C255" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B256" t="str">
+        <v>[L_14_采样]</v>
+      </c>
+      <c r="C256" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B257" t="str">
+        <v>[L_14_分析时间]</v>
+      </c>
+      <c r="C257" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B258" t="str">
+        <v>[L_14_数据长度]</v>
+      </c>
+      <c r="C258" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B259" t="str">
+        <v>[L_14_详细数据(uv)]</v>
+      </c>
+      <c r="C259" t="str">
+        <v>-4.81,-7.46,10.59,2.31,-9.73,6.85,8.72,-8.71,0.97,12.31,-4.61,-5.05,12.02,1.27,-9.08,7.95,6.98,-9.83,1.68,10.84,-6.9,-4.77,11.41,-1.24,-9.4,8.53,4.88,-10.75,2.66,9.59,-8.74,-4.66,9.87,-4.76,-11.25,5.99,-0.8,-15.84,-1.88,2.11,-16.48,-10.02,2.18,-13.97,-17.05,0.24,-7.67,-19.83,-2.66,0.02,-16.5,-6.03,6.3,-10.22,-8.95,8.35,-1.69,-12.54,3.91,2.89,-15.9,-5.26,2.37,-17.36,-16.27,-2.45,-17.56,-24.39,-8.15,-10.8,-28.74,-11.9,-4.64,-19.17,-12.08,6.22,-4.78,-6.84,13.88,10.95,2,18.8,24.15,2.45,12.31,22.32,3.81,-3.41,10.93,-1.93,-18.25,-4.57,-5.47,-27.09,-24.63,-13.98,-29.19,-28.15,-7.83,-11.34,-15.91,6.32,11.45,0.73,18.39,30.68,17.62,18.42,43.87,25.21,17.95,26.27,20.64,-1.94,5.57,5.16,-20.67,-21.63,-14.66,-28.36,-39.68,-26.21,-34.94,-41.91,-22.08,-15.72,-26.28,-11.66,9.07,0.5,2.59,27.07,22.13,10.19,33.81,26.14,12.88,18.55,24.47,-3.12,-9.03,1.16,-16.67,-32.88,-20.71,-28.81,-48.94,-33.87,-24.73,-39.4,-36.66,-15.06,-21.9,-23.45,1.1,3.64,-5.45,10.24,26.12,7.47,15.92,26.02,10.42,2,16.43,8.64,-9.09,0.66,2.31,-21.17,-17.9,-5.83,-18.51,-24.63,-4.31,-11.32,-25.53,-5.28,0.13,-12.53,-0.91,14.72,0.78,1.98,20.95,13.45,1.72,18.32,17.96,-0.67,9.6,15.97,-2.33,-3.59,11.01,-2.22,-12.43,3.62,1,-16.79,-3.78,5.21,-11.97,-8.35,7.74,-5.06,-10.98,7.66,3.38,-11.51,3.41,8.7,-9.05,-3.13,9.96,-6.28,-10.96,6.15,-2.26,-16.27,-1.15,0.9,-17.21,-9.07,2.64,-14.36,-15.87,1.54,-8.24,-19.27,-2.15,-1.71,-18.71,-7.72,2.62,-14.61,-13.45,3.49,-8.32,-17.14,0.47,-1.72,-17.79,-4.89,3.2,-14.5,-10.73,5.05,-8.34,-14.84,3.46,-1.04,-15.59,-0.76,5.13,-12.48,-6.03,8.45,-6.31,-10.27,8.04,1.14,-11.78,4.36,7.71,-9.79,-1.09,11.5,-4.66,-6.24,11.49,2.12,-9.12,7.88,8.48,-8.64,2.02,12.41,-4.87,-4.09,12.64,0.97,-8.41,9.09,6.88,-9.55,2.84,10.79,-7.26,-4.16,11.26,-2.48,-9.76,7.9,2.98,-12.34,1.6,7.04,-11.32,-5.83,8.06,-7.32,-12.22,5.39,-1.99,-15.74,-0.37,2.61,-15.52,-7.6,4.65,-11.9,-14.15,3.22,-6.31,-18.06,-1.42,-0.83,-18.21,-7.88,2.61,-14.65,-14.1,2.77,-8.63,-18.05,-0.41,-2.14,-18.37,-5.81,2.73,-14.87,-11.52,4.5,-8.55,-15.47,2.77,-1.31,-16.12,-1.65,4.68,-12.98,-7.01,7.72,-6.83,-11.24,7.09,0.61,-12.62,3.31,7.15,-10.38,-2.07,10.92,-5,-6.98,10.91,2,-9.54,7.37,8.49,-8.7,1.64,12.47,-4.61,-4.23,12.73,1.46,-8.24,9.21,7.51,-9.05,3.06,11.47,-6.46,-3.76,11.92,-1.47,-9.13,8.53,4.09,-11.46,2.23,8.12,-10.22,-5.15,9.02,-6.1,-11.44,6.2,-0.77,-14.84,0.28,3.69,-14.53,-7.05,5.49,-10.89,-13.64,3.77,-5.41,-17.56,-1.14,-0.15,-17.71,-7.82,2.98,-14.2,-14.18,2.79,-8.31,-18.18,-0.71,-2.05,-18.53,-6.36,2.53,-15.05,-12.21,3.98,-8.8,-16.19,1.97,-1.7,-16.78,-2.64,4.11,-13.57,-8.06,6.94,-7.36,-12.22,6.14,0.09,-13.43,2.28,6.59,-10.98,-3.06,10.28,-5.39,-7.79,10.23,1.76,-10.07,6.7,8.34,-8.92,1.1,12.36,-4.52,-4.54,12.63,1.79,-8.24,9.16,7.98,-8.7,3.13,12,-5.79,-3.49,12.45,-0.56,-8.59,9.07,5.11,-10.64,2.79,9.14,-9.15,-4.51,9.96,-4.88,-10.66,7,0.46,-13.9,0.97,4.81,-13.47,-6.43,6.41,-9.8,-13.04,4.43,-4.4,-16.93,-0.74,0.67,-17.06,-7.62,3.49,-13.6,-14.09,2.96,-7.84,-18.15,-0.86,-1.81</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B260" t="str">
+        <v>[L_14_标记]</v>
+      </c>
+      <c r="C260" t="str">
+        <v>66.2uv</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B261" t="str">
+        <v>[R_15_名字]</v>
+      </c>
+      <c r="C261" t="str">
+        <v>FERG(15)_dMax</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B262" t="str">
+        <v>[R_15_放大器]</v>
+      </c>
+      <c r="C262" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B263" t="str">
+        <v>[R_15_闪光]</v>
+      </c>
+      <c r="C263" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B264" t="str">
+        <v>[R_15_闪光背景]</v>
+      </c>
+      <c r="C264" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B265" t="str">
+        <v>[R_15_采样]</v>
+      </c>
+      <c r="C265" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B266" t="str">
+        <v>[R_15_分析时间]</v>
+      </c>
+      <c r="C266" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B267" t="str">
+        <v>[R_15_数据长度]</v>
+      </c>
+      <c r="C267" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B268" t="str">
+        <v>[R_15_详细数据(uv)]</v>
+      </c>
+      <c r="C268" t="str">
+        <v>15.44,22.37,11.95,1.07,7.34,20.02,17.73,3.82,0.8,13.16,19.97,9.44,-1.57,4.57,17.16,14.82,0.84,-2.25,10.08,16.89,6.37,-4.65,1.5,14.14,11.87,-2.03,-5.06,7.35,14.29,3.91,-6.99,-0.71,12.08,10.01,-3.72,-6.59,6,13.15,2.98,-7.75,-1.29,11.72,9.87,-3.7,-6.38,6.33,13.7,3.64,-6.94,-0.36,12.68,10.87,-2.66,-5.21,7.29,14.75,4.82,-6.06,0.23,13.06,10.24,-3.62,-5.93,5.89,12.47,1.71,-9.21,-4.34,5.86,4.98,-11.76,-12.88,-2.22,1.04,-13.32,-20.26,-23.67,-11.78,-15.59,-29.02,-38.7,-30.95,-23.84,-33.16,-45.14,-47.58,-30.35,-44.96,-52.95,-59.12,-52.94,-34.55,-47.39,-70.91,-50.78,-37.31,-54.61,-72.09,-68.37,-40.06,-30.64,-42.25,-39.82,-42.87,-18.52,-21.82,-21.72,-34.13,3.35,0.39,3.62,-3.77,9.62,35.53,28.5,40.42,43.77,71.83,85.15,71.4,70.95,108.32,116.92,121.53,111.56,139.47,161.42,176.44,158.54,176.81,189.9,237.26,220.24,246.77,221.79,275.91,257.04,249.29,264.22,296.36,290.14,287.64,299.36,304.38,338.53,378.07,326.01,310.27,370.38,414.19,381.44,386.16,398.01,428.51,445.4,437.29,384.16,389.79,395.12,372.92,375.76,388.49,404.87,396.4,386.58,392.62,406.17,382.39,368.72,352.72,402.39,335.57,377.32,354.47,321.52,324.62,342.4,327.48,292.89,289.55,301.25,330.36,310.73,292.85,248.44,284,244.49,225.18,235.74,233.66,260.19,204.11,205.83,188.46,181.49,216.51,174.9,177.95,171.1,158.56,154.28,144.48,155.69,160.86,136.61,120.33,108.01,127.29,127.69,119.6,95.48,100.9,122.08,124.37,97.49,98.87,91.92,127,110.15,98.94,84.22,86.91,94.19,65.02,80.1,78.97,94.71,93.05,77.09,90.39,91.29,66.44,74.75,52.56,78.41,65.06,71.49,54.31,68.18,69.43,66.3,65.94,36.91,68.72,55.52,44.64,41.37,36.88,48.8,55.27,31.48,29.66,38.29,57.8,35.85,33.71,34.72,50.27,37.96,19.46,25.68,27.28,34.65,24.18,10.43,21.11,29.16,24.63,10.96,9.34,21.26,27.72,11.87,-0.81,7.04,16.19,12.77,-0.9,-0.53,7.64,14.46,4.82,-8.85,-4.12,7.41,6.93,-10.11,-15.56,-1.16,5.39,-4.96,-18.61,-13.19,2.9,-3.37,-15.4,-20.93,-6.06,-0.88,-12.31,-20.15,-15.22,-6.69,-8.67,-17.5,-21.42,-10.7,-5.48,-17.82,-24.2,-21.14,-9.75,-5.52,-26.31,-23.16,-19.21,-10.27,-15.76,-26.32,-24.8,-10.52,-6.76,-24.52,-22.82,-20.69,-13.09,-18.27,-26.86,-19.69,-8.07,-9.25,-29.73,-26.33,-22.45,-15.63,-25.1,-35.1,-31.74,-9.99,-16.56,-29.29,-37.06,-15.07,-14.1,-17.97,-35.38,-35.17,-11.2,-16.72,-24.45,-32.9,-30.41,-17.61,-24.17,-32.47,-36.19,-11.44,-27.69,-36.76,-41.55,-35.83,-25.92,-30.18,-43.89,-44.62,-26.55,-19.76,-37.27,-49.24,-32.47,-18.19,-26.85,-39.94,-40.33,-35.53,-29.84,-40.77,-59.67,-44.25,-28.83,-34.83,-56.6,-43.97,-42.89,-29.04,-44.72,-62.94,-50.13,-43.29,-34.55,-55.24,-40.27,-43.08,-31.46,-56.31,-65.67,-49.74,-40.14,-55.39,-52.24,-43.12,-25.41,-39.36,-52.76,-56.69,-49.9,-23.11,-51.94,-55.61,-36.18,-23.02,-26.3,-42.61,-58.14,-33.85,-34.94,-48.07,-52.75,-50.85,-26.38,-25.06,-44.93,-41.71,-38.03,-15.1,-36.87,-39.35,-31.94,-23.95,-33.64,-37.93,-35.99,-31.37,-26.7,-37.08,-32.33,-32.03,-12,-14.76,-34.02,-43.26,-19.09,-23.2,-34.02,-36.58,-26.45,-14.01,-17.26,-33.95,-40.23,-30.39,-10.06,-22.43,-35.63,-33.83,-18.18,-22.2,-26.14,-40.98,-29.28,-18.56,-25.45,-32.2,-27.11,-11.09,-16.67,-30.84,-32.8,-17.64,-13,-26.6,-34.46,-29.97,-13.58,-11.79,-23.74,-32.29,-15.23,-9.21,-18.61,-27.57,-27.53,-10.85,-10.78,-22.13,-30.37,-18.85,-10.47,-19.34,-27.9,-24.48,-6.2,-9.98,-21.03,-20.65,-11.16,0.86,-8.25,-20.67,-14</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B269" t="str">
+        <v>[R_15_标记]</v>
+      </c>
+      <c r="C269" t="str">
+        <v>a: 39.6ms -111.8uv b: 83.5ms 524.3uv</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B270" t="str">
+        <v>[L_15_名字]</v>
+      </c>
+      <c r="C270" t="str">
+        <v>FERG(15)_dMax</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B271" t="str">
+        <v>[L_15_放大器]</v>
+      </c>
+      <c r="C271" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B272" t="str">
+        <v>[L_15_闪光]</v>
+      </c>
+      <c r="C272" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B273" t="str">
+        <v>[L_15_闪光背景]</v>
+      </c>
+      <c r="C273" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B274" t="str">
+        <v>[L_15_采样]</v>
+      </c>
+      <c r="C274" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B275" t="str">
+        <v>[L_15_分析时间]</v>
+      </c>
+      <c r="C275" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B276" t="str">
+        <v>[L_15_数据长度]</v>
+      </c>
+      <c r="C276" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B277" t="str">
+        <v>[L_15_详细数据(uv)]</v>
+      </c>
+      <c r="C277" t="str">
+        <v>20.88,16.97,4.96,7.74,19.79,17.79,5.32,5.99,18.19,18.18,5.59,4.15,16.18,18.16,5.8,2.29,13.83,17.75,5.99,0.52,11.25,17.03,6.18,-1.1,8.52,15.99,6.41,-2.5,5.83,14.79,6.56,-3.71,3.01,13.15,6.54,-4.81,0.15,11.29,6.36,-5.71,-3.61,7.99,5.86,-6.86,-6.92,4.71,3.62,-9.42,-13.3,0.03,-1.77,-15.7,-17.45,-7.44,-9.08,-20.83,-24.94,-15.96,-12.67,-26.42,-34.51,-29.48,-22.57,-39.86,-51.72,-37.73,-33.74,-45.77,-62.22,-51.5,-40.8,-50.23,-64.37,-59.47,-51.19,-56.42,-63.75,-64.83,-41.95,-36.14,-59.07,-43.82,-41.56,-36.81,-44.01,-32.77,-20.19,-4.65,-18.3,-23.71,11.14,6.25,12.63,12.87,45.21,41.99,43.44,43.85,72.24,90.7,80.1,94.36,117.43,110.86,117.85,137.07,131.3,159.54,168,167.52,163.95,214.02,187.78,197.53,217.78,268.09,243.34,245.21,265.14,309.47,255.27,297.26,314.82,293.04,308.4,282.43,320.28,357.13,352.66,375.21,346,364.88,416.94,359.89,413.2,384.79,402.53,374.58,344.75,406.44,416.23,423.09,422.6,409.28,359.45,352.07,357.02,350.71,371.78,387.45,362.66,362.53,345.73,351.33,352.24,322.73,347.43,324.32,298.58,315.76,298.11,288.3,260.59,249.76,297.25,273.5,269.86,240.61,247.19,233,232.1,193.68,214.66,222.7,213.02,179.32,174.5,172.07,182.42,161.38,167.79,175.39,160.95,145.53,133.34,159.46,143.65,119.02,132.1,127.65,114.2,114.03,102.65,122.4,131.89,98.9,97.04,126.84,108.42,85.16,91.51,116.04,106.37,83.58,75.19,77.06,88.55,74.32,62.9,68.96,75.47,75.5,67.61,82.79,87.95,53.62,43.71,71.77,77.08,70.7,54.52,65.71,52.55,57.36,49.99,45.97,51.53,60.5,33.64,34.17,57.15,36.25,34.07,38,48.27,44.42,21.74,31.69,38.21,40.88,28.19,17.18,28.94,28.56,19.27,15.44,24.2,28.62,15.63,11.64,18.37,26.42,18.47,7.23,15.02,20.64,12.62,0.1,12.68,19.8,11.6,2.47,3.39,16.82,9.13,-3.65,0.75,14.57,7,-6.72,-3.13,6.76,5.85,-3.84,-6.93,5.94,8.25,-4.88,-13.5,2.93,5.1,-7.19,-14.9,-5.4,0.06,-13.12,-17.36,-6.36,-4.03,-15.06,-24.07,-13.46,-6.7,-10.22,-24.81,-16.16,-6.89,-17.51,-30.07,-24.31,-9.99,-13.19,-29.76,-20.11,-9.46,-16.74,-29.06,-21.79,-12.19,-18.63,-33.44,-35.01,-19.86,-19.35,-30.5,-30.72,-16.21,-15.18,-28.15,-30.69,-19.43,-22.38,-31.53,-42.07,-30.35,-22.79,-23.47,-41.67,-28.82,-24.77,-30.94,-31.96,-25.59,-12.41,-24.57,-37.45,-32.05,-24.66,-33.88,-38.23,-39.59,-25.79,-15.14,-43.31,-29.99,-17.16,-23.78,-36,-34.34,-25.11,-18.36,-34.76,-36.66,-34.4,-18.15,-31.71,-36.17,-31.89,-31.38,-38.4,-37.24,-28.09,-34.76,-39.12,-34.3,-42.59,-22.86,-41.44,-55.89,-26.99,-22.83,-36.46,-52.83,-45.77,-34.67,-38.11,-40.93,-34.04,-33.56,-28.68,-53.93,-56.02,-29.04,-29.79,-44.92,-40.08,-38.05,-30.19,-54.97,-48.75,-41.48,-37.82,-51.51,-54.93,-39.12,-31.34,-38.8,-41.76,-39.44,-29.93,-44.8,-51.76,-40.74,-24.37,-45.38,-54.97,-30.48,-37.35,-28.44,-41.76,-33.44,-28.27,-40.55,-41.5,-34.66,-31.22,-21.04,-46.72,-39.81,-15.06,-20.27,-28.89,-29.75,-27.06,-24.72,-31.44,-36.04,-28.33,-23.42,-37.63,-25.34,-20.34,-15.44,-23.49,-33.06,-15.35,-7.95,-24.13,-27.73,-20.63,-8.33,-14.77,-28.46,-16.16,-15.25,-10.75,-31.37,-17.6,-2.82,-9.58,-27.36,-20.13,-8.42,-9.18,-27.9,-17.94,-4.96,-12.23,-17.62,-23.64,-6.31,-12.76,-22.32,-21.64,-8.99,-3.82,-15.61,-18.87,-7.1,-2.66,-16.15,-21.19,-10.31,-7.12,-13.37,-24.97,-13.32,-2.11,-14.69,-24.04,-12.99,-3.2,-11.32,-20.17,-11.78,-3.44,-6.4,-17.7,-10.36,0.77,-7.01,-19.28,-13.76,-2.34,-5.96,-16.15,-12.37,-1.77,-2.44,-16.1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B278" t="str">
+        <v>[L_15_标记]</v>
+      </c>
+      <c r="C278" t="str">
+        <v>a: 39.7ms -115.1uv b: 83.6ms 519.4uv</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B279" t="str">
+        <v>[R_16_名字]</v>
+      </c>
+      <c r="C279" t="str">
+        <v>FERG(16)_dOps</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B280" t="str">
+        <v>[R_16_放大器]</v>
+      </c>
+      <c r="C280" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B281" t="str">
+        <v>[R_16_闪光]</v>
+      </c>
+      <c r="C281" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B282" t="str">
+        <v>[R_16_闪光背景]</v>
+      </c>
+      <c r="C282" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B283" t="str">
+        <v>[R_16_采样]</v>
+      </c>
+      <c r="C283" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B284" t="str">
+        <v>[R_16_分析时间]</v>
+      </c>
+      <c r="C284" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B285" t="str">
+        <v>[R_16_数据长度]</v>
+      </c>
+      <c r="C285" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B286" t="str">
+        <v>[R_16_详细数据(uv)]</v>
+      </c>
+      <c r="C286" t="str">
+        <v>-15.86,-26.14,-28.74,-21.2,-11.38,-8.76,-16.18,-27.08,-31.08,-24.73,-14.74,-11.01,-17.65,-28.83,-34.15,-28.69,-18.62,-13.25,-18.59,-29.57,-35.48,-30.7,-19.95,-13.12,-16.49,-26.35,-32.94,-28.93,-18.17,-9.95,-12.36,-22.33,-29.79,-28.16,-18.73,-10.63,-12.1,-22.38,-31.92,-32.22,-23.32,-14.94,-15.12,-23.81,-34.3,-33.79,-24.49,-13.68,-10.44,-17.54,-25.42,-25.39,-15.55,-2.85,0.91,-4.91,-15.31,-15.96,-10.17,0.89,4.09,-5.18,-17.1,-24.49,-21.73,-13.64,-10.96,-18.1,-29.95,-37.75,-36.35,-24.42,-16.64,-19.79,-25.83,-30.08,-23.5,-9.53,1.11,2.9,-4.88,-11.07,-2.46,1.86,10.52,12.49,-2.77,-17.9,-19.1,-15.59,-13.19,-18.63,-35.35,-49.74,-54.66,-41.87,-33.93,-34.69,-45.26,-47.95,-47.76,-34.23,-19.46,-9.43,-9.48,-16.89,-14.51,-2.86,10.73,12.1,12.03,2.28,-6.27,-11.85,-6.6,-8.27,-20.47,-39.13,-52.58,-52.6,-47.4,-46.14,-54.54,-56.6,-65.33,-58.76,-40.18,-26.24,-20.73,-21.78,-20.3,-10.43,3.23,22.5,19,17.01,-0.69,4.49,5.62,12.17,5.49,-8.19,-25.96,-33.54,-29.22,-27.15,-35.56,-39.1,-49.33,-50.78,-40.04,-34.26,-26.6,-27.65,-29.3,-25.66,-10.99,5.95,13.48,11.78,-0.16,-4.03,2.04,15.27,16.87,4.62,-6.84,-19.31,-20.98,-15.4,-13.11,-25.45,-36.09,-46.67,-46.5,-36.65,-26.87,-25.13,-33.56,-38.2,-34.21,-19.99,-8.51,-7.59,-14.08,-20.71,-16.09,-6.57,-0.27,-1,-10.87,-24.57,-26.95,-21.13,-13.51,-15.3,-26.55,-37.69,-41.09,-33.88,-23.94,-22.55,-30.28,-37.99,-39.96,-31.03,-19.61,-14.17,-18.98,-27.56,-30.31,-23,-11.43,-7.47,-11.93,-22.29,-28.07,-24.44,-13.64,-8.6,-13.15,-24.25,-31.29,-27.95,-17.67,-10.32,-13.06,-22.94,-30.11,-27.53,-16.53,-7.83,-8.95,-18.03,-25.85,-24.24,-14.09,-4.78,-4.62,-13.88,-22.89,-23.33,-14.6,-5.16,-4.28,-13.02,-23.03,-24.96,-17.12,-7.28,-5.22,-13.05,-23.53,-26.75,-19.67,-9.55,-6.1,-12.9,-23.62,-28,-22.09,-11.74,-7.16,-13.05,-23.99,-29.73,-25.1,-14.86,-9.21,-13.96,-24.92,-31.83,-28.42,-18.33,-11.61,-15.08,-25.67,-33.49,-31.27,-21.39,-13.6,-15.61,-25.68,-34.24,-33.19,-23.66,-14.92,-15.46,-24.81,-33.99,-34.16,-25.13,-15.57,-14.63,-23.14,-32.79,-34.16,-25.79,-15.58,-13.19,-20.71,-30.69,-33.26,-25.7,-15.02,-11.23,-17.7,-27.88,-31.66,-25.07,-14.15,-9.08,-14.43,-24.71,-29.69,-24.25,-13.31,-7.11,-11.32,-21.59,-27.74,-23.59,-12.87,-5.68,-8.73,-18.87,-26.15,-23.39,-13.1,-5.08,-6.95,-16.84,-25.15,-23.85,-14.18,-5.48,-6.16,-15.64,-24.86,-25.05,-16.15,-6.89,-6.37,-15.27,-25.24,-26.89,-18.88,-9.19,-7.43,-15.58,-26.09,-29.14,-22.1,-12.09,-9.08,-16.3,-27.14,-31.48,-25.48,-15.24,-10.97,-17.09,-28.03,-33.53,-28.6,-18.26,-12.75,-17.61,-28.41,-34.95,-31.13,-20.8,-14.09,-17.59,-28.05,-35.48,-32.79,-22.62,-14.79,-16.85,-26.78,-34.98,-33.46,-23.61,-14.79,-15.37,-24.63,-33.47,-33.17,-23.81,-14.17,-13.3,-21.77,-31.15,-32.1,-23.42,-13.16,-10.89,-18.48,-28.3,-30.55,-22.74,-12.07,-8.5,-15.15,-25.29,-28.86,-22.11,-11.26,-6.5,-12.15,-22.52,-27.39,-21.85,-11.05,-5.22,-9.82,-20.29,-26.42,-22.23,-11.67,-4.89,-8.39,-18.81,-26.13,-23.35,-13.22,-5.6,-7.95,-18.15,-26.52,-25.19,-15.64,-7.28,-8.42,-18.2,-27.48,-27.58,-18.71,-9.72,-9.58,-18.75,-28.72,-30.22,-22.13,-12.59,-11.13,-19.48,-29.93,-32.73,-25.5,-15.51,-12.69,-20.04,-30.75,-34.76,-28.44,-18.12,-13.93,-20.12,-30.88,-35.99,-30.65,-20.12,-14.61,-19.5,-30.11,-36.22,-31.94,-21.35,-14.6,-18.11,-28.4,-35.42,-32.26,-21.8,-13.93,-16.03,-25.85,-33.69,-31.74,-21.61,-12.78,-13.46,-22.7,-31.28,-30.61,-21.02,-11.42,-10.74,-19.3,-28.53,-29.22,-20.38,-10.23,-8.24,-16.04,-25.84,-27.92,-20.03</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B287" t="str">
+        <v>[R_16_标记]</v>
+      </c>
+      <c r="C287" t="str">
+        <v>72uv</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B288" t="str">
+        <v>[L_16_名字]</v>
+      </c>
+      <c r="C288" t="str">
+        <v>FERG(16)_dOps</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B289" t="str">
+        <v>[L_16_放大器]</v>
+      </c>
+      <c r="C289" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B290" t="str">
+        <v>[L_16_闪光]</v>
+      </c>
+      <c r="C290" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B291" t="str">
+        <v>[L_16_闪光背景]</v>
+      </c>
+      <c r="C291" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B292" t="str">
+        <v>[L_16_采样]</v>
+      </c>
+      <c r="C292" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B293" t="str">
+        <v>[L_16_分析时间]</v>
+      </c>
+      <c r="C293" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B294" t="str">
+        <v>[L_16_数据长度]</v>
+      </c>
+      <c r="C294" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B295" t="str">
+        <v>[L_16_详细数据(uv)]</v>
+      </c>
+      <c r="C295" t="str">
+        <v>-21.95,-11.98,-11.39,-21.27,-30.25,-27.99,-17.71,-12.28,-18.71,-29.69,-32.82,-24.43,-15.28,-16.58,-27.08,-34.3,-29.8,-18.92,-14.75,-22.21,-32.17,-32.79,-23.03,-14.15,-17.66,-27.88,-33.61,-27.77,-17.33,-15.75,-25.05,-34.88,-34.06,-24.18,-17.75,-22.7,-33.68,-38.53,-30.58,-19.64,-18.77,-27.3,-34.89,-29.99,-17.74,-11.11,-16.27,-25.16,-24.57,-15.93,-5.28,-5.76,-18.33,-25.25,-20.14,-10.35,-8.29,-18.1,-29.35,-30.65,-23.43,-17.48,-23.41,-32.96,-37.8,-29.18,-17.51,-14.64,-21.04,-27.56,-22.21,-8.21,1.16,-0.81,-11.17,-11.86,-0.7,9.64,6.33,-2.89,-15.61,-15.33,-7.36,-7.85,-19.87,-36.76,-41.86,-33.29,-33.34,-32.42,-48.13,-52.85,-43.31,-27.38,-23.55,-25.01,-29.15,-22.59,-4.32,5.6,7.9,0.76,-2.39,5.97,14.82,11.75,-6.05,-18.89,-22.2,-18.45,-21.2,-35.26,-52.88,-62,-51.66,-44.08,-47.7,-62.94,-63.12,-50.4,-34.89,-25.39,-24.12,-26.05,-20.62,-2.34,8.15,9.43,1.51,6.31,4.81,10.43,9.57,-4.94,-20.53,-25.64,-22.47,-23.56,-31.82,-49.36,-52.68,-45.57,-45.53,-35.5,-45.19,-51.4,-40.26,-20.84,-10.06,-10.58,-12.77,-9.75,1.12,16.46,16.6,2.32,-1.64,2.93,6.81,6.75,-5.62,-19.68,-24.83,-19.12,-15.39,-22.65,-39.84,-40.3,-34.06,-28.97,-22.94,-29.01,-35.82,-28.51,-15.03,-5.75,-8.79,-15.72,-17.96,-6.35,4.65,2.41,-7.51,-16.38,-15.14,-7.46,-4.77,-15.56,-28.16,-31.21,-23.72,-18.51,-21.46,-33.37,-39.58,-32.69,-22.42,-19.35,-25.58,-34.25,-31.5,-19.99,-11.52,-15.07,-24.52,-28.86,-20.33,-10.93,-9.53,-20.05,-28.45,-25.72,-16.17,-11.23,-18.22,-29.44,-31.9,-23.31,-13.92,-15.27,-25.38,-32.27,-26.39,-15.11,-10.74,-17.98,-27.31,-26.57,-15.95,-7.41,-10.41,-20.57,-25.24,-18.22,-7.41,-5.66,-14.73,-23.58,-21.62,-10.97,-4.38,-9.7,-20.39,-23.64,-15.31,-5.53,-5.64,-15.63,-23.34,-19.28,-8.39,-3.52,-10.51,-20.85,-22.16,-12.86,-4.15,-6.61,-17.35,-23.69,-18.2,-7.7,-5.04,-13.7,-23.62,-23.2,-13.3,-6.14,-10.68,-21.82,-26.58,-19.59,-9.63,-8.99,-18.81,-27.65,-25.23,-14.81,-9.2,-15.46,-26.38,-29.15,-20.73,-11.49,-12.76,-23.26,-30.6,-26.16,-15.45,-11.46,-19.11,-29.31,-29.9,-20.21,-11.89,-14.92,-25.62,-31.1,-24.69,-13.97,-11.66,-20.37,-29.45,-27.79,-17.15,-10.03,-14.7,-25.26,-28.72,-20.6,-10.29,-9.82,-19.37,-27.11,-23.36,-12.24,-6.68,-12.97,-23.16,-24.62,-15.22,-5.85,-7.37,-17.6,-23.9,-18.36,-7.31,-3.68,-11.54,-21.17,-20.77,-10.57,-2.61,-6.24,-16.95,-21.74,-14.75,-4.27,-2.83,-12.1,-20.96,-18.79,-8.24,-2.04,-7.73,-18.6,-21.75,-13.58,-4.07,-4.86,-15.23,-22.99,-19.1,-8.52,-4.24,-11.72,-22.31,-23.64,-14.46,-6.13,-9.01,-19.99,-26.26,-20.65,-10.25,-7.88,-16.74,-26.51,-25.81,-15.77,-8.74,-13.44,-24.48,-28.87,-21.55,-11.52,-10.99,-20.75,-29.23,-26.36,-15.66,-10.04,-16.27,-26.87,-29.11,-20.24,-10.84,-12.07,-22.34,-29.17,-24.18,-13.16,-9.11,-16.64,-26.44,-26.47,-16.38,-7.96,-10.97,-21.45,-26.46,-19.61,-8.75,-6.51,-15.19,-23.98,-21.93,-11.11,-4.1,-8.94,-19.43,-22.61,-14.3,-4.12,-3.95,-13.67,-21.31,-17.42,-6.4,-1.22,-7.88,-18.18,-19.58,-10.25,-1.26,-3.29,-13.83,-20.19,-14.71,-3.97,-0.89,-9.22,-19.05,-18.69,-8.71,-1.24,-5.43,-16.45,-21.31,-14.41,-4.3,-3.39,-13.07,-22.03,-19.84,-9.46,-3.69,-9.8,-20.81,-23.87,-15.66,-6.4,-7.54,-18.08,-25.71,-21.61,-11.03,-6.98,-14.62,-25.07,-26.06,-16.66,-8.38,-11.37,-22.24,-28.11,-22.08,-11.51,-9.18,-17.95,-27.34,-26.11,-15.71,-8.6,-13.24,-23.97,-27.81,-20,-9.75,-9.17,-18.74,-26.74,-23.31,-12.29,-6.6,-12.76,-23.04,-24.76,-15.5,-6,-7.28,-17.43,-23.86,-18.48,-7.33,-3.41,-11.01,-20.64,-20.34,-10.11</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B296" t="str">
+        <v>[L_16_标记]</v>
+      </c>
+      <c r="C296" t="str">
+        <v>71.1uv</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B297" t="str">
+        <v>[R_17_名字]</v>
+      </c>
+      <c r="C297" t="str">
+        <v>FERG(17)_dMax</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B298" t="str">
+        <v>[R_17_放大器]</v>
+      </c>
+      <c r="C298" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B299" t="str">
+        <v>[R_17_闪光]</v>
+      </c>
+      <c r="C299" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B300" t="str">
+        <v>[R_17_闪光背景]</v>
+      </c>
+      <c r="C300" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B301" t="str">
+        <v>[R_17_采样]</v>
+      </c>
+      <c r="C301" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B302" t="str">
+        <v>[R_17_分析时间]</v>
+      </c>
+      <c r="C302" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B303" t="str">
+        <v>[R_17_数据长度]</v>
+      </c>
+      <c r="C303" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B304" t="str">
+        <v>[R_17_详细数据(uv)]</v>
+      </c>
+      <c r="C304" t="str">
+        <v>1.76,5.94,6.52,3.16,-2.79,-8.94,-12.78,-12.77,-8.95,-2.93,2.77,5.77,4.83,0.34,-5.82,-11.05,-13.17,-11.24,-6.01,0.39,5.39,6.96,4.55,-0.77,-6.69,-10.67,-10.94,-7.3,-1.15,5.07,8.88,8.82,5.03,-0.81,-6.17,-8.69,-7.23,-2.29,4.19,9.62,11.82,10,4.97,-1.1,-5.62,-6.66,-3.72,1.97,8.12,12.23,12.52,8.74,2.73,-3.33,-6.96,-6.55,-2.41,3.38,8.61,10.18,8.67,2.46,-4.38,-9.56,-12.09,-10.88,-7.09,-2.13,0.06,-1.01,-4.89,-10.39,-18.31,-25.46,-27.01,-23.88,-19.53,-20.56,-21.95,-22.14,-31.41,-39.98,-41.25,-45.35,-49.64,-45.97,-40.59,-46.75,-37.43,-51.33,-52.53,-67.01,-65.72,-80.73,-78.34,-74.43,-62.43,-58.57,-62.03,-66.82,-67.16,-69.18,-70.43,-67.86,-60.62,-35.75,-34.03,-24.89,-33.64,-13.04,-22.54,-17.74,-14.22,-2.79,2.84,23.97,31.82,34,52.43,55.58,52.35,56.89,75.71,82.9,104.9,109.35,127.94,125.19,133.54,152.4,172.37,173.5,174.87,194.69,233.1,230.73,244.94,261.58,273.46,270.01,241.98,285.63,249.79,296.64,305.31,287.62,333.44,313.8,311.2,338.19,356.18,384.76,326.76,370.45,400.79,412.54,356.28,401.41,352.03,336.88,391.17,386.37,411.82,430.91,378.27,402.58,354.96,408.86,354.24,337.49,384.6,329.81,352.2,371.6,333.75,313.16,347.9,346.01,288.26,284.03,311.37,282.06,290.65,312.75,296.12,308.25,268.45,269.65,218.4,205.09,233.85,232.98,225.43,212.71,217.23,193.49,180.61,192.46,176.77,162.33,178.46,178.18,169.02,163.51,158.18,149.11,145.19,131.08,128.44,137.89,112.01,142.45,129.76,140,106.22,116.72,103.97,108.78,83.28,96.43,98.72,116.06,119.92,108.48,99.74,92.27,66.88,68.45,91.12,65,95.65,78.34,91.79,66.37,83.41,67.13,56.66,43.57,49.35,50.5,54.87,72.03,69.76,54.24,43.23,40.62,37.26,30.46,42.28,32.65,54.73,51.18,41.09,38.63,17.54,20.13,13.86,19.66,25.29,31.4,26.44,29.15,15.79,7.69,4.03,0.92,-4.13,-0.74,3.62,10.99,7.18,5.66,-4.08,-7.64,-16.32,-16.88,-15.34,-7.53,-4.13,-1.98,-3.11,-5.5,-11.33,-17.93,-23.55,-24.55,-17.89,-10.19,-5.11,-5.15,-7.67,-11.97,-20.41,-26.69,-27.53,-24.42,-21.26,-13.27,-11.53,-11.19,-13.2,-21.25,-23.87,-28.49,-29.39,-23.69,-15.81,-12.57,-12.03,-12.55,-20.12,-25.79,-32.49,-28,-28.4,-21.26,-19.04,-15.61,-12.43,-14.16,-27.03,-26.53,-30,-35.38,-30.26,-26.04,-23.38,-20.01,-17.69,-23.56,-32.21,-39.17,-35.02,-45.46,-36.85,-30.72,-29.13,-22.09,-25.87,-38.5,-35.96,-49.83,-46.16,-49.16,-44.78,-32.55,-32.18,-34.07,-33.98,-46.04,-55.4,-58.48,-49.02,-44.47,-41.01,-43.62,-30.12,-40.01,-45.9,-54.06,-52.48,-59.56,-63.06,-49.61,-43.13,-44.61,-52.05,-55.65,-51.99,-64.47,-69.52,-63.58,-50.61,-55.22,-42.42,-34.48,-46.82,-53.71,-67.29,-63.58,-54.76,-69.27,-47.27,-43.54,-45.26,-44.6,-46.52,-43.83,-57.78,-67.92,-57.05,-66.18,-43.9,-44.72,-48.34,-43.56,-39.24,-52.72,-60.28,-70.12,-65.62,-46.14,-47.87,-52.99,-48.68,-49.05,-40.21,-60.18,-56.81,-66.51,-63.9,-41,-43.26,-38.1,-40.17,-54.54,-56.33,-47.24,-56.91,-49.97,-49.07,-57.52,-51.47,-32.73,-43.66,-49.75,-61.08,-68.78,-71.68,-58.21,-56.56,-55.34,-35.76,-51.13,-42.8,-60.59,-50.81,-55.78,-61.49,-62.63,-54.73,-45.57,-47.85,-48.45,-44.31,-58.6,-59.46,-63.24,-51.61,-45.29,-48.86,-42.44,-36.46,-41.75,-44.99,-50.44,-61.85,-61.6,-49.41,-41.22,-39.31,-33.68,-41.98,-39.71,-50.78,-46.79,-50.38,-49.06,-49.75,-40.38,-35.82,-23.15,-36.11,-31.18,-42.49,-47.06,-47.79,-43.94,-31.75,-30.17,-24.62,-24.1,-29.09,-27.07,-36.66,-40.23,-41.6,-33.31,-28.3,-17.45,-17.73,-19.55,-25.55,-25.67,-34.16,-36.78,-35.24,-28.61,-16.4,-14.34</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B305" t="str">
+        <v>[R_17_标记]</v>
+      </c>
+      <c r="C305" t="str">
+        <v>a: 44.1ms -118.3uv b: 91.8ms 514.8uv</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B306" t="str">
+        <v>[L_17_名字]</v>
+      </c>
+      <c r="C306" t="str">
+        <v>FERG(17)_dMax</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B307" t="str">
+        <v>[L_17_放大器]</v>
+      </c>
+      <c r="C307" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B308" t="str">
+        <v>[L_17_闪光]</v>
+      </c>
+      <c r="C308" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B309" t="str">
+        <v>[L_17_闪光背景]</v>
+      </c>
+      <c r="C309" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B310" t="str">
+        <v>[L_17_采样]</v>
+      </c>
+      <c r="C310" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B311" t="str">
+        <v>[L_17_分析时间]</v>
+      </c>
+      <c r="C311" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B312" t="str">
+        <v>[L_17_数据长度]</v>
+      </c>
+      <c r="C312" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B313" t="str">
+        <v>[L_17_详细数据(uv)]</v>
+      </c>
+      <c r="C313" t="str">
+        <v>2.54,12.21,16.88,13.6,4.1,-6.18,-11.32,-8.45,0.61,10.37,14.96,11.57,2.14,-7.82,-12.45,-9.03,0.41,10.3,14.84,11.39,2.06,-7.54,-11.64,-7.7,2.1,12.11,16.56,13.01,3.74,-5.58,-9.22,-4.83,5.23,15.21,19.49,15.7,6.37,-2.81,-6.13,-1.49,8.68,18.46,22.39,18.11,8.41,-0.75,-3.78,0.68,10.91,20.14,23.53,18.15,8.35,-1.27,-4.52,-1.11,8.97,17.04,18.93,12.45,2.96,-9.25,-11.79,-10.09,0.32,3.94,8.94,2.47,-9.89,-27.66,-28.17,-25.4,-16.52,-16.03,-15.95,-20.4,-32.89,-43.7,-56.21,-53.5,-35.13,-32.05,-30.71,-45.86,-53.82,-57.61,-71.84,-52.16,-62.82,-47.04,-31.6,-41.89,-47.04,-50.95,-58.75,-50.82,-37.45,-35.76,-20.66,-18.93,-23.86,-23.8,-21.89,5.2,10.46,16.84,31.78,31.72,35.25,35.33,32.84,66.73,72.87,99.4,93.69,102.69,112.52,127.4,136.59,137.85,142.99,161.86,208.16,171.41,211.86,217.99,184.24,226.49,222.77,254.19,291.35,291.06,270.64,293.67,277.77,301.41,317.29,311.91,371.77,317.59,325.81,361.63,360.08,390.59,408.1,357.66,399.64,423.79,349.79,333.21,385.86,380.22,363.69,366.53,398.43,392.58,377.41,378.75,381.01,416.77,424.59,367.09,407.68,387.6,329.04,364.39,352.99,367.24,366.77,352.33,332.91,287.87,312.44,290.86,262.1,294.11,283.61,295.63,261.64,241.57,255.04,232.98,226.02,219.29,213.42,239.47,226.55,200.11,175.04,180.52,184.5,172.49,167.45,186.35,170.29,165.33,150.47,126.85,132.67,145.31,150.18,141.93,124.81,127.66,108.03,108.87,104.44,129.62,131.81,115.93,103.94,98.98,84.26,81.65,81.49,112.68,88.6,110.62,106.27,105.27,70.07,74.28,64.52,85.37,91.67,87.63,87.2,85.95,75.95,73.28,69.61,65.46,79.92,76.33,70.44,60.43,54.17,40.72,46.59,60.33,74.36,75.46,56.73,42.37,34.52,27.44,34.71,34.74,41.34,44.81,41.17,26.21,16.93,16.89,23.73,30.47,33.47,31,29.96,18.86,6.01,5.3,3.71,11.95,20.09,23.43,14.69,4.77,-7.32,-9.49,-4.31,5.56,10.17,13.13,3.33,-1.59,-13.47,-15.12,-11.24,-2.36,3.62,7.11,-1.3,-12.71,-19.38,-21.65,-16.52,-6.91,-0.49,1.92,-1.44,-13.94,-21.77,-24.06,-14.36,-9.89,3.49,3.58,-6.82,-13.81,-20.3,-20.06,-13.85,-6.02,4.14,1.45,-3.34,-9.98,-24.44,-25.56,-19.06,-7.24,4.66,2.58,-7.47,-19.55,-22.6,-22.85,-21.97,-4.81,-5.03,3.14,-4.87,-12.29,-31.41,-25.96,-25.86,-16.06,1.3,-8.67,-7.96,-21.09,-30.81,-28.34,-30.79,-9.09,-1.41,-3.78,-10.25,-24.56,-42.35,-40.59,-29.97,-17.12,-16.09,-14.91,-22.4,-30.64,-34.42,-41.27,-32.86,-30.63,-12.59,-30.2,-25.44,-50.4,-54.4,-44.86,-45.21,-37.49,-17.31,-28.18,-34.73,-54.37,-46.62,-61.29,-52.24,-31.83,-27.49,-20.7,-40.83,-48.08,-55.92,-47.01,-42.28,-37.84,-22.37,-40.03,-37.51,-45.59,-49.63,-58.52,-39.19,-44.06,-24.83,-37.32,-36.54,-53.93,-46.7,-54.57,-34.51,-22.73,-23.27,-17.13,-43.72,-47.17,-51.17,-45.59,-30.99,-24.63,-30.23,-23.16,-36.71,-33.45,-50.85,-52.32,-37.51,-24.77,-13.51,-27.06,-36.11,-36.04,-40.4,-44.03,-37.16,-14.86,-19.01,-23.8,-20.06,-39.09,-43.54,-31.38,-39.19,-13.44,-24.18,-28.48,-28.59,-39.29,-37.7,-47.5,-37.32,-27.8,-10.91,-16.84,-38.61,-32.51,-41.5,-44.05,-38.25,-28.83,-9.78,-13.95,-32.23,-40.13,-40.25,-36.13,-24.6,-15.96,-18.28,-21.15,-34.54,-43.62,-40.87,-33.96,-34.37,-22.59,-14.11,-14.42,-30.06,-39.57,-42.61,-29.36,-22,-9.44,-6.71,-14.69,-25.96,-30.8,-30.27,-26.76,-19.95,-9.8,-8.74,-12.08,-21.34,-23.76,-32.31,-25.37,-10.44,1.59,-2.41,-6.2,-14.26,-23.67,-21.48,-13.25,-6.01,6.48,9.5,3.99,-10.46,-14.12,-16.28,-10.69,2.06,9.54,9,4.01,-5.22,-13.02</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B314" t="str">
+        <v>[L_17_标记]</v>
+      </c>
+      <c r="C314" t="str">
+        <v>a: 44.2ms -119.9uv b: 91.8ms 473.4uv</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B315" t="str">
+        <v>[R_18_名字]</v>
+      </c>
+      <c r="C315" t="str">
+        <v>FERG(18)_dOps</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B316" t="str">
+        <v>[R_18_放大器]</v>
+      </c>
+      <c r="C316" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B317" t="str">
+        <v>[R_18_闪光]</v>
+      </c>
+      <c r="C317" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B318" t="str">
+        <v>[R_18_闪光背景]</v>
+      </c>
+      <c r="C318" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B319" t="str">
+        <v>[R_18_采样]</v>
+      </c>
+      <c r="C319" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B320" t="str">
+        <v>[R_18_分析时间]</v>
+      </c>
+      <c r="C320" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B321" t="str">
+        <v>[R_18_数据长度]</v>
+      </c>
+      <c r="C321" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B322" t="str">
+        <v>[R_18_详细数据(uv)]</v>
+      </c>
+      <c r="C322" t="str">
+        <v>-10.93,-11.67,-11.83,-11.06,-9.65,-7.71,-5.31,-2.84,-0.15,2.28,4.31,5.79,6.61,6.77,6.18,4.93,3.43,1.09,-1.17,-3.42,-5.48,-6.89,-7.89,-8.38,-7.95,-6.67,-4.77,-2.4,0.32,3.63,6.89,9.17,11.34,13.56,14.26,13.96,12.63,10.99,8.57,5.49,2.32,-1.12,-4.38,-6.67,-8.4,-10.06,-11.62,-9.7,-8.11,-5.93,-2.67,0.27,4.09,7.63,11.47,13.03,15.94,16.71,16.1,13.59,11.91,8.04,5.58,0.07,-4.09,-8.55,-13.16,-17.06,-17.66,-21.29,-19.38,-18.36,-17.98,-18.11,-12.78,-8.31,-4.27,-0.2,3.78,7.56,9.95,13.19,12.14,16.1,10.79,10.61,10.11,6.49,2.38,-3.1,-7.84,-11.78,-15.78,-17.78,-20.23,-23.38,-23.84,-21.07,-18.37,-17.34,-18.18,-12.74,-8.26,-3.22,1.1,5.58,8.96,13.1,19.37,15.63,17.44,21.3,22.86,15.46,12.21,14.76,6.59,3.54,-0.83,-6.62,-10.86,-12.14,-17.43,-15.86,-20.41,-25.29,-23.27,-21.54,-14.2,-10.55,-6.94,-0.93,3.33,13.62,16.78,26.72,26.64,32.41,26.15,28.39,28.24,22.85,18.99,13.44,5.87,-0.08,-11.98,-16.03,-22.78,-23.04,-31.6,-35.68,-34.9,-36.19,-31.5,-24.49,-17.74,-10.2,-3.94,5.31,11.71,19.63,20.66,21,23.87,29.27,24.58,16.66,12.22,5.84,-1.91,-9.82,-16.7,-24.29,-27.95,-33.24,-35.71,-36.22,-33.4,-27.11,-22.44,-16.98,-11.92,-4.95,1.24,7.77,11.32,16.41,19.77,21.71,16.83,15.02,11.41,8.65,3.61,-1.45,-6.28,-10.3,-13.97,-16.56,-19.34,-17.53,-16.02,-13.16,-9.91,-6.69,-3.47,1.65,5.19,8.02,10.5,12.17,13.49,12.05,10.96,9.63,7.01,4.9,1.56,-1.25,-4.25,-5.81,-7.04,-7.37,-7.3,-6.11,-4.52,-3.16,-0.27,0.76,2.59,4.43,4.77,5.59,5.06,3.91,2.32,0.36,-1.82,-4.04,-6.41,-8.23,-9.84,-10.77,-11.21,-11.02,-9.95,-8.78,-7.06,-5.13,-3.26,-1.45,-0.05,0.76,1.32,0.94,0.12,-1.32,-3.37,-5.38,-7.76,-9.98,-11.97,-13.56,-14.57,-15,-14.61,-13.64,-12.17,-10.04,-7.69,-5.16,-2.65,-0.43,1.45,2.76,3.45,3.48,2.82,1.58,-0.14,-2.13,-4.28,-6.39,-8.24,-9.68,-10.54,-10.76,-10.3,-9.18,-7.45,-5.26,-2.75,-0.12,2.43,4.74,6.6,7.88,8.49,8.38,7.58,6.16,4.24,1.98,-0.45,-2.82,-4.97,-6.71,-7.9,-8.46,-8.34,-7.56,-6.2,-4.37,-2.24,0.02,2.19,4.09,5.56,6.45,6.67,6.18,5.02,3.25,0.99,-1.6,-4.31,-6.96,-9.35,-11.31,-12.71,-13.44,-13.47,-12.82,-11.56,-9.81,-7.74,-5.53,-3.38,-1.47,0.01,0.94,1.23,0.85,-0.19,-1.82,-3.89,-6.26,-8.74,-11.12,-13.22,-14.86,-15.92,-16.29,-15.96,-14.93,-13.29,-11.16,-8.7,-6.11,-3.58,-1.3,0.55,1.84,2.47,2.43,1.72,0.42,-1.34,-3.4,-5.57,-7.66,-9.48,-10.86,-11.67,-11.82,-11.28,-10.07,-8.29,-6.04,-3.5,-0.86,1.68,3.94,5.73,6.94,7.46,7.28,6.41,4.93,2.97,0.68,-1.72,-4.07,-6.15,-7.8,-8.9,-9.35,-9.12,-8.25,-6.8,-4.91,-2.74,-0.48,1.67,3.53,4.93,5.73,5.85,5.28,4.02,2.17,-0.14,-2.75,-5.46,-8.09,-10.43,-12.31,-13.61,-14.25,-14.18,-13.44,-12.11,-10.31,-8.21,-6.01,-3.89,-2.05,-0.64,0.19,0.37,-0.12,-1.26,-2.97,-5.11,-7.53,-10.01,-12.38,-14.43,-16.01,-16.98,-17.27,-16.84,-15.73,-14.02,-11.84,-9.36,-6.78,-4.28,-2.07,-0.3,0.89,1.43,1.28,0.47,-0.9,-2.72,-4.81,-6.99,-9.05,-10.82,-12.12,-12.84,-12.88,-12.24,-10.94,-9.07,-6.77,-4.2,-1.55,0.97,3.18,4.91,6.03,6.46,6.18,5.23,3.68,1.67,-0.63,-3.02,-5.33,-7.34,-8.91,-9.91,-10.25,-9.91,-8.94,-7.41,-5.45,-3.25,-0.98,1.15,2.96,4.28,5,5.03,4.36,3.02,1.1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B323" t="str">
+        <v>[R_18_标记]</v>
+      </c>
+      <c r="C323" t="str">
+        <v>73.3uv</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B324" t="str">
+        <v>[L_18_名字]</v>
+      </c>
+      <c r="C324" t="str">
+        <v>FERG(18)_dOps</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B325" t="str">
+        <v>[L_18_放大器]</v>
+      </c>
+      <c r="C325" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B326" t="str">
+        <v>[L_18_闪光]</v>
+      </c>
+      <c r="C326" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B327" t="str">
+        <v>[L_18_闪光背景]</v>
+      </c>
+      <c r="C327" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B328" t="str">
+        <v>[L_18_采样]</v>
+      </c>
+      <c r="C328" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B329" t="str">
+        <v>[L_18_分析时间]</v>
+      </c>
+      <c r="C329" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B330" t="str">
+        <v>[L_18_数据长度]</v>
+      </c>
+      <c r="C330" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B331" t="str">
+        <v>[L_18_详细数据(uv)]</v>
+      </c>
+      <c r="C331" t="str">
+        <v>-17.78,-20.41,-21.07,-19.8,-16.63,-12.27,-7.38,-2.77,0.73,2.52,2.44,0.48,-2.95,-7.24,-11.61,-15.14,-17.1,-17.54,-15.61,-12.4,-7.71,-2.82,1.73,5.11,6.71,6.25,4.1,0.31,-4.83,-9.49,-13.39,-15.42,-15.82,-13.84,-10.25,-5.14,0.47,5.72,9.79,12.17,12.56,10.71,7.98,3.13,-1.47,-5.72,-8.56,-9.74,-9.03,-7.09,-4.36,-1.38,1.58,3.24,3.73,2.41,-1.52,-7.25,-10,-16.49,-19.23,-19.27,-18.93,-15.07,-10.1,-3.59,4.82,11.59,12.35,19.16,15.41,14.66,9.79,1.47,-7.51,-14.28,-21.52,-26.08,-28.24,-28.63,-30.46,-27.97,-26.29,-24.4,-20.48,-22.59,-18.72,-20.16,-18.19,-18.42,-15.8,-13.8,-10.38,-3.71,1.7,13.43,20.09,17.67,24.85,20.85,11.57,6.39,-5.41,-16.75,-29.31,-35.31,-41.28,-52.1,-51.69,-42.81,-36.99,-33.65,-23.92,-12.42,-7.24,0.97,5.28,9.94,14.44,10.27,11.69,16.74,10.63,19.11,16.86,12.88,14.16,13.71,9.42,3.1,-5.81,-10.57,-18.74,-31.61,-35,-38.99,-40.16,-42.04,-38.7,-28.45,-16.13,-7.12,3.74,11.37,19.99,20.56,20.18,21.61,13.1,8.31,4.06,-4.7,-5.39,-10.16,-12.49,-13.5,-12.86,-14.49,-15.71,-17.02,-15.6,-23.27,-27.58,-30.42,-31.74,-34.51,-31.93,-29.71,-24.64,-18.36,-11.21,-4.91,2.13,6.12,5.1,3.61,2.23,-5.6,-11.41,-16.99,-23.29,-27.66,-29.94,-29.48,-26.58,-23.06,-18.27,-15.11,-11.43,-9.53,-8.59,-9.57,-12.48,-16.14,-19.44,-21.92,-23.2,-21.94,-19.87,-15.75,-11.45,-6.42,-1.41,1,2.12,1.45,-1.45,-5.79,-10.67,-15.42,-19.08,-21.52,-21.58,-19.79,-16.17,-11.32,-6.35,-1.63,1.63,3.12,2.54,0.07,-3.88,-8.54,-13.13,-16.96,-19.28,-19.72,-18.2,-15.03,-10.8,-6.43,-2.54,0.08,0.89,-0.3,-3.34,-7.77,-12.93,-17.94,-21.99,-24.52,-25.06,-23.67,-20.61,-16.49,-12.09,-8.24,-5.66,-4.87,-6.07,-9.09,-13.51,-18.6,-23.53,-27.5,-29.89,-30.33,-28.78,-25.55,-21.25,-16.65,-12.58,-9.77,-8.73,-9.66,-12.4,-16.5,-21.24,-25.8,-29.4,-31.38,-31.41,-29.45,-25.82,-21.13,-16.16,-11.73,-8.59,-7.23,-7.85,-10.29,-14.09,-18.55,-22.83,-26.14,-27.87,-27.65,-25.46,-21.65,-16.8,-11.7,-7.19,-4,-2.61,-3.24,-5.71,-9.56,-14.07,-18.43,-21.83,-23.66,-23.57,-21.55,-17.91,-13.28,-8.44,-4.21,-1.32,-0.26,-1.23,-4.05,-8.26,-13.12,-17.83,-21.58,-23.76,-24.01,-22.34,-19.06,-14.78,-10.31,-6.45,-3.93,-3.24,-4.57,-7.73,-12.24,-17.39,-22.36,-26.34,-28.71,-29.14,-27.61,-24.47,-20.32,-15.95,-12.19,-9.75,-9.12,-10.47,-13.63,-18.11,-23.19,-28.04,-31.87,-34.07,-34.29,-32.54,-29.16,-24.76,-20.13,-16.1,-13.39,-12.47,-13.53,-16.37,-20.51,-25.24,-29.72,-33.16,-34.96,-34.78,-32.63,-28.86,-24.09,-19.11,-14.74,-11.7,-10.49,-11.25,-13.81,-17.69,-22.14,-26.36,-29.56,-31.12,-30.73,-28.4,-24.47,-19.57,-14.51,-10.09,-7.05,-5.85,-6.66,-9.29,-13.24,-17.8,-22.13,-25.46,-27.17,-26.94,-24.8,-21.09,-16.44,-11.65,-7.54,-4.83,-3.98,-5.15,-8.15,-12.48,-17.4,-22.09,-25.76,-27.82,-27.94,-26.14,-22.78,-18.49,-14.06,-10.31,-7.95,-7.45,-8.96,-12.27,-16.88,-22.06,-26.97,-30.84,-33.06,-33.32,-31.64,-28.38,-24.18,-19.82,-16.12,-13.81,-13.32,-14.82,-18.09,-22.62,-27.69,-32.45,-36.14,-38.14,-38.16,-36.23,-32.7,-28.21,-23.57,-19.59,-16.97,-16.18,-17.36,-20.3,-24.49,-29.19,-33.57,-36.87,-38.47,-38.09,-35.76,-31.85,-27,-22.02,-17.71,-14.8,-13.73,-14.64,-17.32,-21.26,-25.72,-29.88,-32.96,-34.37,-33.81,-31.33,-27.3,-22.37,-17.34,-13.03,-10.14,-9.13,-10.12,-12.91,-16.98,-21.57,-25.88,-29.12,-30.71,-30.35,-28.09,-24.31,-19.65,-14.93,-10.95,-8.41,-7.77,-9.14,-12.31,-16.76,-21.72,-26.39,-29.98,-31.92,-31.9,-29.98,-26.54</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B332" t="str">
+        <v>[L_18_标记]</v>
+      </c>
+      <c r="C332" t="str">
+        <v>70.6uv</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B333" t="str">
+        <v>[R_19_名字]</v>
+      </c>
+      <c r="C333" t="str">
+        <v>FERG(19)_lCone</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B334" t="str">
+        <v>[R_19_放大器]</v>
+      </c>
+      <c r="C334" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B335" t="str">
+        <v>[R_19_闪光]</v>
+      </c>
+      <c r="C335" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B336" t="str">
+        <v>[R_19_闪光背景]</v>
+      </c>
+      <c r="C336" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B337" t="str">
+        <v>[R_19_采样]</v>
+      </c>
+      <c r="C337" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B338" t="str">
+        <v>[R_19_分析时间]</v>
+      </c>
+      <c r="C338" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B339" t="str">
+        <v>[R_19_数据长度]</v>
+      </c>
+      <c r="C339" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B340" t="str">
+        <v>[R_19_详细数据(uv)]</v>
+      </c>
+      <c r="C340" t="str">
+        <v>3.05,2.62,2.22,1.83,1.48,1.15,0.85,0.59,0.37,0.18,0.03,-0.08,-0.15,-0.17,-0.15,-0.09,0.01,0.15,0.33,0.56,0.81,1.11,1.44,1.8,2.18,2.59,3.03,3.48,3.95,4.43,4.91,5.4,5.9,6.38,6.86,7.33,7.78,8.21,8.61,8.99,9.34,9.66,9.94,10.18,10.37,10.52,10.63,10.69,10.7,10.66,10.56,10.42,10.21,9.95,9.66,9.31,8.88,8.46,7.95,7.4,6.82,6.12,5.44,4.75,4.15,3.14,2.44,1.47,0.76,-0.18,-1.35,-1.66,-2.78,-3.76,-4.42,-4.92,-6.42,-6.83,-8.65,-8.67,-10.59,-11.38,-11.19,-13.23,-13.75,-16.01,-13.36,-17.14,-17.2,-17.4,-15.16,-17.58,-21,-17.27,-18.76,-20.57,-21.32,-21.14,-22.84,-21.96,-17.1,-22.2,-21.02,-13.74,-15.06,-15.38,-18.58,-21.07,-10.8,-10.42,-15.94,-17.07,-8.83,-11.11,-11.6,0.14,-2.17,-5.97,-4.46,-1.88,5.48,13.59,9.61,12.35,10.19,17.87,10.8,17.88,23.49,27.71,33.24,24.36,29.13,36.08,33.09,41.79,42.5,50.2,53.62,42.2,42.9,51.13,45.44,50.46,52.4,55.66,68.94,56.51,68.9,79.59,63.89,77.85,66.05,77.19,84.97,70.33,89.94,71.4,87.01,84.38,87.72,80.53,80.21,86.34,88.27,113.71,101.78,117.32,116.32,105.61,108.8,117.47,123.67,124.32,102.72,130.18,106.6,121.72,134.28,126.43,121.39,109.08,115.31,115.69,132.03,139.37,129.88,143.15,137.75,114.24,135.23,135.68,110.47,138.79,132.77,132.06,108.27,108.1,122.82,105.36,131.04,122.32,122.16,120.5,115.2,109.01,109.8,97.66,90.02,97.88,93.93,81.05,99.15,77.85,87.2,80.6,66.68,72.57,75.43,65.85,56.2,64.51,49.53,59.49,46.19,45.55,46.91,41,41.43,40.56,29.25,26.32,25.87,20.27,25.57,21.18,17.73,16.42,16.1,8.2,11.4,10.55,9.21,4.22,5.71,1.02,3.82,2.28,2.22,0.84,-0.91,-0.47,-2.67,-0.61,-1.92,-2.02,-1.75,-1.62,-2.64,-2.26,-2.17,0,-0.81,-0.27,-0.11,-0.62,0.84,1.06,0.72,1.73,2.1,2.03,2.08,2.21,2.88,2.67,3.43,2.84,2.83,3.22,2.74,2.14,1.12,2.33,0.32,-0.43,-0.85,-1.12,-2.18,-3.56,-3.19,-4.8,-6.17,-5.23,-5.39,-8.28,-9.46,-11.18,-10.88,-10.92,-13.03,-13.47,-16.33,-15.6,-17.41,-19.09,-16.94,-19.22,-19.37,-20.65,-24.21,-22.67,-24.78,-25.15,-23.77,-23.51,-25.99,-27.69,-25.61,-26.93,-26.64,-28.28,-27.91,-30.79,-24.96,-29.08,-24.99,-26.93,-25.2,-27.73,-29.99,-25.1,-30.1,-28.3,-27.75,-25.11,-26.22,-23.06,-20.47,-21.31,-25.88,-19.87,-24.59,-25.22,-17.7,-22.63,-21.61,-22.78,-21.73,-22.84,-20.29,-15.7,-23.05,-18.25,-20.65,-18.14,-25.68,-20.45,-22.13,-18.71,-26.1,-23.32,-25.9,-19.27,-21.22,-18.81,-23.34,-29.19,-23.73,-20.97,-22.62,-23.96,-25.54,-27.69,-29.58,-29.9,-31.2,-27.51,-28.54,-28.46,-38.61,-38.94,-36.46,-30.77,-37.78,-33.72,-39.41,-40.36,-41.71,-34.58,-33.41,-40.47,-31.96,-32.8,-35.87,-43.3,-40.84,-41.53,-42.15,-33.55,-31.74,-42.06,-41.01,-38.12,-38.29,-37.11,-35.17,-29.73,-35.67,-35.46,-27.95,-35.21,-26.21,-32.91,-34.25,-28.92,-30.88,-31.65,-32.54,-29.31,-23.01,-27.62,-27.11,-25.53,-29.34,-24.29,-25.45,-24.34,-28.37,-27.26,-26.55,-26.26,-27.1,-21.27,-19.38,-21.08,-23.23,-26.4,-26.42,-25.35,-20.1,-27.12,-23.07,-21.83,-22.46,-26.24,-23.22,-25.82,-26.94,-27.99,-26.99,-25.73,-27.02,-24.33,-25.94,-27.48,-27.96,-28.09,-24.47,-28.81,-28.92,-26.98,-28.69,-27.59,-25.38,-27.84,-27.42,-26.12,-26.87,-23.65,-23.47,-25.53,-24.49,-21.68,-22.86,-23.48,-21.94,-21.74,-20.33,-20.88,-20.05,-18.73,-19.11,-18.98,-16.3,-17.53,-15.61,-14.99,-14.55,-15.71,-15.25,-14.39,-14.35,-13.57,-12.48,-12.47,-13.29,-11.55,-12.41,-12.05</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B341" t="str">
+        <v>[R_19_标记]</v>
+      </c>
+      <c r="C341" t="str">
+        <v>a: 47.2ms -35.0uv b: 99.7ms 56.8uv</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B342" t="str">
+        <v>[L_19_名字]</v>
+      </c>
+      <c r="C342" t="str">
+        <v>FERG(19)_lCone</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B343" t="str">
+        <v>[L_19_放大器]</v>
+      </c>
+      <c r="C343" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B344" t="str">
+        <v>[L_19_闪光]</v>
+      </c>
+      <c r="C344" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B345" t="str">
+        <v>[L_19_闪光背景]</v>
+      </c>
+      <c r="C345" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B346" t="str">
+        <v>[L_19_采样]</v>
+      </c>
+      <c r="C346" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B347" t="str">
+        <v>[L_19_分析时间]</v>
+      </c>
+      <c r="C347" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B348" t="str">
+        <v>[L_19_数据长度]</v>
+      </c>
+      <c r="C348" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B349" t="str">
+        <v>[L_19_详细数据(uv)]</v>
+      </c>
+      <c r="C349" t="str">
+        <v>-6.49,-6.45,-6.39,-6.33,-6.24,-6.15,-6.05,-5.93,-5.81,-5.67,-5.53,-5.37,-5.21,-5.04,-4.87,-4.68,-4.5,-4.31,-4.11,-3.91,-3.71,-3.5,-3.29,-3.08,-2.88,-2.67,-2.46,-2.25,-2.05,-1.84,-1.64,-1.45,-1.25,-1.06,-0.87,-0.69,-0.51,-0.34,-0.17,-0.01,0.15,0.31,0.45,0.6,0.73,0.87,0.99,1.12,1.23,1.35,1.45,1.56,1.65,1.75,1.84,1.92,2.01,2.08,2.15,2.23,2.29,2.36,2.4,2.45,2.49,2.52,2.59,2.59,2.62,2.58,2.61,2.59,2.53,2.34,2.2,2.21,2.26,1.91,1.91,1.62,1.33,0.22,0.69,0.13,-1.14,-2.22,-1.79,-3.42,-2.9,-6.15,-5.56,-6.84,-6.09,-10.45,-12.61,-12.62,-14.92,-12.58,-17.14,-13.85,-15.94,-22.15,-17.34,-19.53,-17.35,-18.99,-23.89,-22.65,-21.94,-23.91,-25.14,-24.03,-20.92,-26.88,-25.23,-21.45,-20.71,-19.57,-13.23,-13.59,-10.48,-15.95,-7.02,-5.46,-8.02,-5.77,-2.92,1.07,-1.28,3.94,3.95,11.43,13.37,12.29,14.99,20.59,22.13,19.77,25.68,28.1,34.13,29.33,37.75,40.2,40.71,39.24,42.02,57.72,52.32,57.18,59.93,69.18,73.33,74.62,70.83,68.38,70.07,82.91,74.48,91.13,80.33,91.34,105.46,108.56,106.41,121.5,128.99,123.89,105.48,124.01,109.03,129.84,138.1,140.89,127.29,127.64,134.36,141.53,120.05,147.41,121.13,147.88,127.32,125.25,133.43,148.55,145.07,123.66,145.55,139.97,141.27,137.22,142.67,118.77,113.83,135.5,107.54,114.61,114.77,94.82,116.13,94.96,92.68,84.17,99.16,94.89,91.96,87.28,79.34,85.32,75.46,64.43,70.1,59.39,57.06,58.77,61.13,53.56,44.23,51.43,46.19,40.99,42.75,39.25,35.04,31.29,28.53,26.89,24.79,24.4,24.81,21.55,19.56,20.62,16.51,16.53,14.4,13.51,12.07,12.68,11.67,11.02,8.89,7.75,7.64,6.91,6.87,6.09,5.17,5.11,4.78,4.45,3.73,2.91,3.41,2.73,2.61,2.73,2.49,1.71,1.48,1.93,2.27,1.43,1.17,2.28,1.05,1.56,2.04,2.46,2.04,2.32,2.59,1.4,1.47,2.84,1.8,3.4,2.51,3.37,2.17,2.14,3.54,4.21,3.86,4.88,4.79,3.81,5.31,3.08,3.11,4.2,5.43,4.19,3.97,3.57,4.97,3.5,6.17,5.89,4.22,6.29,4.17,5.27,3.79,4.66,2.5,6.04,5.16,4.81,5.97,6.28,2.28,5.99,1.17,4.24,3.47,0.72,5.36,0.44,2.76,0.83,-0.26,0.07,-1.73,2.78,-2.21,3.86,2.64,-2.81,1.02,1.84,-0.14,1.73,2.81,-1.83,-2.9,-2.19,-5.23,-5.86,-5.95,-1.12,-3.2,-3.61,-8.18,-0.68,-8.6,-2.98,-4.66,-1.93,-3.17,-3.41,-4.77,-5.57,-3.87,-4.74,-11.35,-11.89,-11.75,-5.41,-8.84,-13.34,-12.24,-8.5,-10.66,-3.5,-8.06,-7.79,-12.2,-14.38,-4.4,-7.19,-10.37,-7.57,-9.36,-5.1,-6.91,-15.48,-11.39,-8.4,-16.39,-4.66,-12.81,-8.62,-5.73,-8.27,-7.84,-15.02,-14.54,-11.37,-8.35,-15.92,-11.87,-13.24,-7.15,-16.02,-7.21,-11.36,-13.33,-8.13,-8.7,-4.82,-7.03,-15.57,-8.45,-15.1,-13.43,-8.15,-4.43,-11.67,-3.79,-14.13,-12.67,-10.3,-6.02,-6.77,-7.77,-2.29,-3.42,-9.51,-3.77,-7.28,-4.73,-3.47,-3.8,-0.71,-0.23,1.16,-2.59,-0.72,-0.41,-1.46,0.67,3.42,-3.32,3.28,4.09,0.44,0.82,5.64,-0.12,3.86,0.79,4.47,7.93,5.69,5.55,8.58,5.64,10.72,6,8.95,10.04,8.9,13.14,10.41,13.68,13,14.68,13.13,11.21,15.34,15.34,12.28,15.73,13.93,15.01,16.47,13.04,15.56,13.58,16.05,14.11,17.1,15.55,17.56,16.05,16.63,15.85,14.62,15.89,15.52,17.11,15.77,14.52,16.74,16.67,15.44,14.42,14.27,15.32,14.49,14.92,15.28,13.95,14.27,13.63,14.2,14.32,13.53</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B350" t="str">
+        <v>[L_19_标记]</v>
+      </c>
+      <c r="C350" t="str">
+        <v>a: 47.1ms -34.9uv b: 99.5ms 74.6uv</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B351" t="str">
+        <v>[R_20_名字]</v>
+      </c>
+      <c r="C351" t="str">
+        <v>FERG(20)_lFlicker</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B352" t="str">
+        <v>[R_20_放大器]</v>
+      </c>
+      <c r="C352" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B353" t="str">
+        <v>[R_20_闪光]</v>
+      </c>
+      <c r="C353" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B354" t="str">
+        <v>[R_20_闪光背景]</v>
+      </c>
+      <c r="C354" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B355" t="str">
+        <v>[R_20_采样]</v>
+      </c>
+      <c r="C355" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B356" t="str">
+        <v>[R_20_分析时间]</v>
+      </c>
+      <c r="C356" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B357" t="str">
+        <v>[R_20_数据长度]</v>
+      </c>
+      <c r="C357" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B358" t="str">
+        <v>[R_20_详细数据(uv)]</v>
+      </c>
+      <c r="C358" t="str">
+        <v>31.89,29.28,22.51,15.61,13.73,13.29,14.62,14.68,21.48,25.14,34.28,40.46,41.71,39.95,40.11,32.02,23.7,17.25,15.03,11.17,14.2,13.05,18.02,25.76,30.86,31.25,29.77,31.3,28,19.77,15.29,5.27,6.62,1.5,-1.08,4.75,9.9,11.71,20.73,21.17,23.76,19.09,17.96,11.49,2.96,-1.77,-6.02,-10.04,-8.36,-5.19,-1.33,4.43,10.22,12.03,11.8,12.36,5.21,-0.77,-7.82,-12.91,-18.66,-20.24,-20.96,-15.44,-13.77,-10.09,-2.12,-2.65,-3.63,-2.82,-10.17,-15.8,-24.9,-33.48,-37.17,-38.48,-36.02,-29.49,-29.8,-24.66,-14.5,-13.31,-12.77,-19.49,-22.03,-33.45,-36.97,-37.36,-45.53,-43,-42.47,-33.21,-28.25,-21.33,-14.2,-15.48,-8.5,-14.93,-15.99,-17.72,-21.17,-26.2,-25.94,-28.22,-21.4,-15.69,-6.33,0.03,6.82,10.12,13.1,11.54,7.65,3.81,-1.08,-3.16,-4.46,-1.71,3.09,8.36,15.41,21.74,29.92,31.25,29.78,29.9,21.27,19.26,14.34,9.09,5.51,10.55,12.01,17.16,20.95,30.8,35.07,34.51,28.8,25.61,23.4,16.06,8.38,5.6,0.26,3.05,7.02,10.78,20.37,22.29,28.89,28.33,26.96,21.63,17.02,7.21,6.16,0.9,3.19,0.45,5.2,12.23,17.66,24.53,25.34,27.7,25.27,21.63,16.26,10.63,4.41,1.6,3.77,4.74,9.26,13.74,18.87,24.97,26.5,27.83,24.32,17.48,12.6,3.67,-1.54,-4.55,-3.96,-3.42,2.27,5.04,9.05,14.24,12.48,9.94,6.71,-3.34,-9.88,-18.65,-20.58,-25.26,-28.26,-26.16,-22.36,-20.14,-16.1,-14.61,-9.04,-9.35,-21.12,-25.64,-30.15,-42.64,-46.42,-40.97,-44.03,-38.95,-36.29,-31.16,-20.2,-20.47,-19.03,-18.08,-20.45,-23.85,-32.54,-32.16,-34.34,-35.73,-34.12,-25.65,-19.62,-12.48,-5.27,1.34,3.62,3.55,1.67,-0.45,-5.11,-8.75,-9.24,-7.84,-3.84,2.42,11.46,18.04,22.65,29.59,31,31.77,28.17,23.99,19.86,14.37,11.85,13.53,16.77,21.63,26.71,34.26,43.42,47.16,43.72,45.54,39.83,30.08,29.02,17.79,17.69,21.32,18.19,26.48,30.89,35.74,36.54,44.53,40.52,42.78,31.22,25.41,18.7,13.45,9.46,14.85,14.66,19.11,25.96,29.55,33.69,38.8,34.08,32.69,26.91,18.8,13.28,7.76,3.77,4.73,6.29,10.89,16.4,21.43,24.8,25.39,20.91,18.91,10.66,4.79,-3.42,-7.97,-10.25,-12.02,-8.95,-6.17,-3.19,0.42,3.07,6.22,-0.1,-6.64,-11.92,-16.57,-24.67,-34.58,-34.09,-30.9,-34.02,-28.45,-24.31,-19.04,-15.17,-15.95,-16.44,-20.28,-24.17,-34.76,-37.79,-39.79,-41.74,-40.55,-35.3,-27.48,-20.84,-14.67,-9.3,-10.57,-12,-11.85,-15.38,-21.63,-22.65,-27.02,-21.92,-18.52,-13.55,-4.41,3.2,11.5,16.39,19.31,17.91,15.09,12.32,8.66,6.96,3.82,7.35,13.16,20.28,26.84,32.93,38.12,42.18,42.84,41.84,37.39,32.02,26.13,23.1,20.1,20.16,25.94,26.81,33.06,42.89,45.03,48.96,45.13,40.03,34.94,31.23,18.5,17.99,16.09,16.21,14.74,20.87,31.08,31.96,38.65,35.52,33.37,29.45,21.93,17.11,12.26,10.05,6.3,6.95,11.7,16.15,20.39,25.88,29.61,30.76,26.32,24.84,18.48,11.17,5.8,4.24,3.54,3.66,9.95,15.3,20.51,25.06,26.48,27.86,26.44,20.28,15.27,7.08,4.06,-2.98,-5.32,0.01,2.29,7.8,13.21,16.24,17.14,19.12,12.8,10.03,0.64,-8.96,-13.18,-16.07,-20.48,-17.02,-14.2,-7.59,-2.67,-3.68,3.12,-3.09,-2.87,-11.86,-19.07,-22.07,-29.72,-31.69,-33.84,-28.14,-22.35,-19.32,-11.93,-9.65,-2.09,-3.09,-7.39,-11.98,-16.52,-21.1,-27.39,-28.19,-22.29,-20.17,-10.83,-4.8,4.25,9.65,13.52,13.81,10.68,7.84,2.5,-0.54,-2.81,-3.4,1.51,5.82,14.04,21.62,25.69,33.13,35.53,35.1,30.09</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B359" t="str">
+        <v>[R_20_标记]</v>
+      </c>
+      <c r="C359" t="str">
+        <v>幅值: 25.1uv 相位: 50°</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B360" t="str">
+        <v>[L_20_名字]</v>
+      </c>
+      <c r="C360" t="str">
+        <v>FERG(20)_lFlicker</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B361" t="str">
+        <v>[L_20_放大器]</v>
+      </c>
+      <c r="C361" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B362" t="str">
+        <v>[L_20_闪光]</v>
+      </c>
+      <c r="C362" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B363" t="str">
+        <v>[L_20_闪光背景]</v>
+      </c>
+      <c r="C363" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B364" t="str">
+        <v>[L_20_采样]</v>
+      </c>
+      <c r="C364" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B365" t="str">
+        <v>[L_20_分析时间]</v>
+      </c>
+      <c r="C365" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B366" t="str">
+        <v>[L_20_数据长度]</v>
+      </c>
+      <c r="C366" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B367" t="str">
+        <v>[L_20_详细数据(uv)]</v>
+      </c>
+      <c r="C367" t="str">
+        <v>27.21,32.28,39.19,41.22,51.67,55.03,54.48,53.3,56.13,51.28,47.53,50.79,47.11,44.04,39.93,38.33,37.48,36.81,39.84,44.01,42.89,54.72,57.03,58.24,62.12,58.78,62.12,59.64,55.63,48.91,39.91,35.79,27.6,23.71,17.01,12.57,12.1,10.89,9.9,12.19,13.01,16.23,18.37,19.69,19.69,18.48,14.45,10.65,6.85,-0.25,-6.25,-11.79,-19.62,-22.12,-24.82,-30.33,-31.05,-25.94,-26.36,-22.21,-16.8,-14.67,-14.18,-7.67,-8.51,-2.95,-6.3,-6.38,-13.9,-15.66,-19.84,-20.41,-26.61,-29.58,-27.56,-23.34,-22.23,-19.95,-13.59,-13.32,-5.69,-3.7,6.67,11.59,8.22,14.78,12.68,8.31,9.52,6.08,-0.28,-4.3,-5.78,-7.74,-6.26,-7.6,-2.29,-0.87,6.08,9.98,15.29,18.64,22.49,25.53,27.45,27.22,25.26,21.93,20.27,14.93,12.88,7.57,6.82,4.33,6.35,9.67,11.22,14.93,20.86,25.71,28.33,35.7,39.01,40.92,43.94,43.1,42.59,39.39,36.62,28.42,30.38,27.01,21.01,18.83,25.46,22.95,28.93,30.88,33.61,38.54,44.84,48.73,55.32,52.6,51.64,51.37,47.02,39.44,34.04,29.42,27.69,23.92,18.57,14.42,17.92,18.94,20.94,22.18,23.94,28.85,29.97,31,31.07,31.3,27.61,23.54,18.99,12.53,7.66,0.69,-5.12,-7.54,-10.85,-13.75,-11.61,-13.2,-8.49,-5.69,-3.44,3.8,5.24,8.03,7.71,6.48,7.84,3.76,-0.23,-6.28,-9.71,-16.47,-17.12,-18.45,-17.35,-21.83,-16.9,-12.56,-7.15,-5.91,-0.79,6.43,8.97,8.21,10.69,9.36,12.06,8.18,2.32,-2.91,-1.21,-10.56,-11.01,-10.44,-15.7,-13.84,-10.52,-6.83,-2.11,0.29,8.36,10.69,15.38,15.56,13.22,14.34,11.38,7.44,2.52,-1.29,-5.26,-8.13,-11.25,-12.14,-10.42,-10.01,-5.15,0.4,4.1,10.73,16.19,19.79,24.56,27.74,24.05,25.59,22.21,18.48,19.74,16.25,15.99,11.51,14.46,13.12,15.72,21.2,25.77,28.99,34.46,44.72,45.53,50.74,56.55,59.06,54.1,55.51,51.47,50.07,47.15,39.11,42.09,34.14,33.7,34.4,34.29,39.3,43.24,45.48,48.31,49,55.22,56.96,51.94,53.19,50.36,46.19,41.28,32.23,25.52,19.28,13.76,9.69,6.84,4.14,3.66,5.53,7.14,9.13,10.74,12.32,15.74,15.5,14.68,7.86,5.28,0.97,-2.87,-8.97,-18.73,-19.86,-25.19,-29.18,-32.87,-31.09,-29.52,-21.95,-22.27,-16.14,-13.92,-9.82,-6.85,-5.71,-6.41,-2.39,-10.08,-6.72,-12.38,-19.24,-19.85,-21.06,-23.37,-25.82,-23.98,-21.65,-17.41,-13.44,-10.56,-2.9,-1.81,6.34,8.81,7.59,10.03,10.99,7.28,5.2,-2.12,-1.79,-7.32,-7.98,-8.49,-9.5,-6.73,-4.9,-0.32,4.34,10.87,14.95,20.62,23.76,27.73,27.69,27.98,27.57,24.13,21.29,19.44,15.07,13.92,11.96,10.21,11.34,13.13,18.31,25.49,30.67,33.92,43.24,45.36,48.52,51.3,52.15,55.93,49.25,49.43,45.38,42.2,36.8,36.44,35.21,31.91,32.97,29.86,39.16,44.26,46.61,47.94,52.52,52.01,54.12,50.86,52.95,45.96,43.97,39.03,29.13,25.65,21.85,14.52,13.24,8.62,9.2,10.15,8.68,12.94,14.8,17.51,18.65,17.97,17.7,15.54,14.17,8.12,2.28,-3.04,-9.39,-16.92,-19.46,-22.95,-25.66,-26.01,-23.83,-18.18,-15.99,-13.16,-10.67,-4.7,-0.46,2.89,-1.27,-2.2,0.25,-4.49,-8.46,-8.56,-15.41,-15.64,-17.81,-17.62,-22.61,-21.62,-16.6,-11.18,-5.7,3.7,7.47,12.44,12.67,18.32,19.44,18.38,14.93,12.08,9.45,-0.95,-1.07,-5.77,-7.11,-8.16,-7.04,-5.22,-2.5,2.96,6.74,11.09,15.88,17.67,20.66,21.7,21.77,19.79,16.73,12.3,7.92,5.74,-0.13,-3.26,-4.54,-3.89,-3.36,-1.65,1.98,7.76,13.09,18,22.15,25.06,33.9,32.17,33.28,34.38,27.73</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B368" t="str">
+        <v>[L_20_标记]</v>
+      </c>
+      <c r="C368" t="str">
+        <v>幅值: 25.6uv 相位: 49.6°</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B369" t="str">
+        <v>[R_21_名字]</v>
+      </c>
+      <c r="C369" t="str">
+        <v>FERG(21)_lCone</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B370" t="str">
+        <v>[R_21_放大器]</v>
+      </c>
+      <c r="C370" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B371" t="str">
+        <v>[R_21_闪光]</v>
+      </c>
+      <c r="C371" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B372" t="str">
+        <v>[R_21_闪光背景]</v>
+      </c>
+      <c r="C372" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B373" t="str">
+        <v>[R_21_采样]</v>
+      </c>
+      <c r="C373" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B374" t="str">
+        <v>[R_21_分析时间]</v>
+      </c>
+      <c r="C374" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B375" t="str">
+        <v>[R_21_数据长度]</v>
+      </c>
+      <c r="C375" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B376" t="str">
+        <v>[R_21_详细数据(uv)]</v>
+      </c>
+      <c r="C376" t="str">
+        <v>5.67,6.57,11.75,17.86,20.91,18.89,13.02,6.98,4.54,7.18,13.08,18.35,19.48,15.61,9.09,3.96,3.36,7.53,13.64,17.62,16.76,11.46,4.96,1.28,2.62,7.98,13.78,16.15,13.45,7.27,1.46,-0.37,2.84,8.94,13.93,14.52,10.27,3.85,-0.68,-0.45,4.37,10.66,14.4,13.18,7.81,1.76,-1.06,1.23,7.2,13.11,15.23,12.3,6.29,1.18,0.3,4.38,10.89,15.78,16.08,11.69,5.51,1.72,2.83,8.17,14.31,17.69,16.04,10.41,4.25,1.78,4.57,10.82,15.7,17.36,13.4,6.39,1.11,1.19,3.76,8.58,12.69,10.34,5.94,-0.39,-5.44,-5.92,-1.91,4.68,4.57,1.37,-4.06,-15.5,-16.88,-10.37,-10.94,0.81,-5.63,-5.51,-10.94,-23.1,-16.28,-19.54,-13.52,-4.58,-5.3,-12.08,-17.5,-20.83,-19.21,-11.18,1.33,-2.02,-2.43,-6.03,-10.15,-9.42,-5.1,3.71,12.31,12.41,14.54,12.24,6.2,7.89,21.74,28.17,30.82,33.09,31.23,31.06,30.44,35.93,40.88,48.66,50.42,55.08,54.83,43.3,58.59,62.3,65.27,83.23,72.2,83.45,77.38,69.71,69.49,83.82,96.87,95.69,97.97,91.33,99.58,110.29,99.51,118.04,115.05,135.03,112.63,115.95,134.48,129.04,143.53,136.76,134.85,135.35,132.41,151.84,150.91,134.92,127.25,135.17,146.9,146.31,145.41,128.05,135.79,138.5,137.63,142.44,135.3,141.29,131.94,137.56,137.25,114.41,136.77,139.99,141.76,120.44,106.23,104.95,99.36,96.02,118.07,114.37,106.59,83.92,94.01,85.1,87.98,75.65,78.39,72.14,68.27,56,62.58,52.89,51.11,63.31,56.96,50.46,49.37,39.45,31.77,38.93,38.65,43.06,42.47,37.18,27.6,21.34,19.24,25.3,31.71,29.8,31,23.43,17.26,12.78,12.43,17.32,24.22,24.74,20.83,15.75,10.33,7.32,10.67,18.25,22.1,21.82,17.43,11.02,6.91,7.55,12.36,18.6,22.08,20.14,14.33,8.1,5.85,8.88,15.07,20.39,21.93,17.55,11.53,6.9,6.21,9.76,16.98,20.11,19.77,14.66,8.15,5.15,6.67,11.67,16.07,18.59,17.84,10.68,5.04,3.18,6.06,11.33,15.78,16.56,13.16,4.85,-0.38,1.51,5.06,10.18,14.61,10.67,6.27,-0.67,-4.82,-3.36,1.7,10.4,11.84,7.49,2.98,-6.12,-5.05,-4.39,1.27,7.78,5.03,4.56,-1.78,-6.23,-5.75,-4.52,3.88,5.42,2.87,-1.96,-9.07,-8.03,-10.13,-4.08,5.78,6.1,3.95,-1.94,-10.99,-9.87,-7.67,0.36,1.18,7.56,-3.58,-6.44,-9.3,-10.84,-0.57,6.82,2.75,5.05,-1.59,-10.37,-7.89,-11.13,-1.79,3.06,9.43,5.51,-0.66,-5.23,-12.78,-4.52,-0.13,9.58,8.33,-6.63,-3.49,-11.25,-12.95,-1.96,-3.57,4.67,4.88,-5.01,-14.4,-18.23,-5.09,-8.87,-0.18,-4.15,-7.36,-12.55,-11.92,-18.74,-7.87,1,-4.58,-4.52,-3.05,-19.03,-13.12,-14.54,-8.06,-3.06,-3.75,-2.8,-6.9,-19.35,-23.54,-19.31,-5.77,-0.87,-5.2,-4.17,-10.11,-22.82,-23.59,-10.77,-8.42,-0.51,-5.38,-7.58,-15.57,-16.11,-19.68,-7.49,0.21,-6.11,-4.84,-16.38,-16.8,-11.43,-14.51,-4.58,4.44,2.44,-9.14,-8.55,-9.87,-10.25,-2.77,2.49,5.65,-3.2,-0.27,-6.59,-9.09,-2.11,4.04,4.49,10.72,2.82,-6.48,-4.5,-4.07,1.36,9.07,9.98,12.79,7.51,-1.89,-5.55,2.22,5.67,12.11,12.39,10,4.27,-0.17,-2.59,4.94,8.96,15.69,14.18,9,0.37,-1.82,-0.34,5.97,11.83,14.13,14.54,5.22,1.29,0.9,1.15,7.88,11.71,16.27,12.24,4.8,-1.78,-0.9,2.93,9.8,15.41,14.49,7.96,2.05,-0.81,1.29,6.08,11.24,13.96,11.47,4.33,-0.97,-1.99,2.51,8.73,14.06,13.81,10.31,3.85,-0.57,1.64,6.48,13.08,16.01,15.09,9.31,4.16,2.09,4.02,10.78,16.94</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B377" t="str">
+        <v>[R_21_标记]</v>
+      </c>
+      <c r="C377" t="str">
+        <v>a: 51.6ms -27.5uv b: 105.6ms 60.2uv</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B378" t="str">
+        <v>[L_21_名字]</v>
+      </c>
+      <c r="C378" t="str">
+        <v>FERG(21)_lCone</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B379" t="str">
+        <v>[L_21_放大器]</v>
+      </c>
+      <c r="C379" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B380" t="str">
+        <v>[L_21_闪光]</v>
+      </c>
+      <c r="C380" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B381" t="str">
+        <v>[L_21_闪光背景]</v>
+      </c>
+      <c r="C381" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B382" t="str">
+        <v>[L_21_采样]</v>
+      </c>
+      <c r="C382" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B383" t="str">
+        <v>[L_21_分析时间]</v>
+      </c>
+      <c r="C383" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B384" t="str">
+        <v>[L_21_数据长度]</v>
+      </c>
+      <c r="C384" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B385" t="str">
+        <v>[L_21_详细数据(uv)]</v>
+      </c>
+      <c r="C385" t="str">
+        <v>-7.34,-1.81,2.77,4.33,2.14,-2.78,-8.21,-11.66,-11.59,-8.06,-2.74,1.89,3.64,1.64,-3.25,-8.88,-12.74,-13.17,-10.04,-4.9,-0.2,1.8,0.07,-4.69,-10.42,-14.6,-15.43,-12.63,-7.6,-2.75,-0.42,-1.76,-6.28,-11.99,-16.36,-17.49,-14.93,-9.93,-4.87,-2.11,-2.99,-7.16,-12.75,-17.2,-18.57,-16.2,-11.23,-5.9,-2.69,-3.09,-6.8,-12.22,-16.83,-18.39,-16.29,-11.35,-5.87,-2.28,-2.06,-5.63,-10.81,-15.74,-17.31,-15.98,-11.3,-5.37,-1.99,-1.83,-4.28,-10.36,-15.18,-18.03,-16.09,-11.4,-5.81,-2.4,-3.43,-6.06,-12.54,-16.27,-19.31,-20.98,-13.9,-10.86,-6.78,-4.92,-9.33,-13.33,-21.71,-23.46,-24.87,-18.01,-13,-14.12,-12.76,-12.25,-19.09,-30.62,-25.19,-25.45,-26.74,-18.88,-19.09,-17.13,-18.15,-17.67,-28.29,-27.9,-27.28,-20.5,-18.41,-7.62,-7.08,-5.99,-13.5,-11.92,-11.41,-12.58,-13.18,-4.31,7.1,6.96,15.77,10.41,3.56,2.31,7.61,6.23,16.84,23.7,36.82,29.04,35.73,27.68,22.05,25.87,38.98,34.99,44.01,60.35,54.82,68.42,61.09,46.08,61.26,74.74,77.65,88.44,84.32,86.44,75.31,90.37,69.72,70.67,97.65,92.65,112.81,99.71,121.95,122.55,122.42,108.73,88.18,92.45,99.68,105.8,140.36,129.71,126.18,137.51,103.19,135.08,121.41,110.08,140.86,122.38,129.09,132.06,139.71,127.58,112.12,135.67,104.69,121.82,133.51,126.29,120.97,123.13,99.94,103.74,108.77,108.08,105.66,112.53,103.45,102.91,113.92,102.41,95.51,90.01,100.6,86.1,98.69,102.47,87.24,78.16,71.45,80.15,77.31,74.63,61.07,83.43,75.25,73.72,69.44,52.07,47.76,50.8,44.1,44.26,55.61,53.15,45.57,40.64,37.64,27.18,25.1,29.05,24.87,37.3,36.51,31.51,25.38,18.39,14.76,7.58,12.96,12.35,17.53,24.98,21.23,15.69,7.79,5.66,1.17,3.88,8.67,10.44,16.43,15.75,9.67,4.43,0.27,-4.2,-3.05,1.65,7.19,10.83,9.5,6.74,1,-3.22,-6.54,-4.55,-1.4,3.96,8.28,8.43,4.27,-1.55,-5.93,-8.53,-9.17,-4.88,0.36,4.28,3.9,2.73,-3.5,-9.32,-13.03,-12.97,-8.15,-3.08,1.41,0.75,-2.03,-6.46,-12.76,-16.28,-15.52,-14.27,-9.79,-3.55,-3.11,-5.88,-8.71,-14.1,-21.07,-22.41,-18.93,-13.97,-6.64,-8.16,-8.35,-13.65,-18.71,-23.54,-23.08,-22.81,-17.41,-9.32,-9.36,-12.11,-13.83,-23.14,-27.51,-28.3,-24.1,-16.08,-16.1,-10.39,-14.09,-14.6,-20.38,-24.57,-27.2,-27.03,-15.51,-15.65,-6.87,-11.26,-17.32,-23.74,-26.39,-27.8,-24.61,-15.99,-11.39,-11.21,-6.04,-13.35,-14.86,-23.26,-23.02,-21.7,-18.43,-18.62,-7.54,-8.02,-13.75,-15.57,-28.02,-27.99,-22.23,-25.49,-18.27,-14.45,-14.18,-12.15,-24.69,-22.33,-28.66,-25.31,-23.69,-23.34,-11.67,-8,-20.29,-17.85,-24.06,-35.51,-26,-25.01,-24.71,-20.95,-14.59,-21.74,-26.48,-23.86,-36.12,-32.1,-31.63,-28.4,-17.28,-17.32,-17.78,-27.39,-33.75,-30.33,-29.94,-27.32,-26.32,-23.66,-19.15,-15.98,-28.15,-30.09,-31.5,-31.03,-26.37,-20.2,-18.93,-19.94,-20.74,-17.61,-23.53,-33.48,-35.35,-26.03,-26.34,-12.92,-18.1,-11.6,-15.56,-21.3,-24.2,-32.27,-21.17,-20.63,-16.71,-13.82,-9.61,-16.73,-23.46,-25.83,-27.8,-18.47,-14.65,-12.41,-5.4,-10.09,-7.67,-14.36,-18.58,-18.19,-17.02,-15.28,-8.67,-4.17,-4.73,-6.4,-8.13,-14.95,-14.67,-12.63,-8.21,-2.46,-2.59,-0.93,-1.17,-7.34,-13.61,-16.92,-14.54,-10.37,-4.16,1.8,-1.35,-0.47,-6.5,-11.99,-15.71,-12.75,-9.09,-5.97,-0.75,-0.33,-0.92,-5.39,-13.45,-17.1,-14.94,-9.89,-5.92,-0.86,1.55,-1.77,-7.97,-12.5,-14.55,-16.58,-12.63,-7.08,-1.53,0.08,-1.6,-5.68,-11.28,-15.13,-14.73,-11.87,-5.77,-1.54,1,0.24,-4.54,-8.96,-12.94,-12.94</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B386" t="str">
+        <v>[L_21_标记]</v>
+      </c>
+      <c r="C386" t="str">
+        <v>a: 51.6ms -32.4uv b: 105.6ms 67.0uv</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B387" t="str">
+        <v>[R_22_名字]</v>
+      </c>
+      <c r="C387" t="str">
+        <v>FERG(22)_lFlicker</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B388" t="str">
+        <v>[R_22_放大器]</v>
+      </c>
+      <c r="C388" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B389" t="str">
+        <v>[R_22_闪光]</v>
+      </c>
+      <c r="C389" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B390" t="str">
+        <v>[R_22_闪光背景]</v>
+      </c>
+      <c r="C390" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B391" t="str">
+        <v>[R_22_采样]</v>
+      </c>
+      <c r="C391" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B392" t="str">
+        <v>[R_22_分析时间]</v>
+      </c>
+      <c r="C392" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B393" t="str">
+        <v>[R_22_数据长度]</v>
+      </c>
+      <c r="C393" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B394" t="str">
+        <v>[R_22_详细数据(uv)]</v>
+      </c>
+      <c r="C394" t="str">
+        <v>45.39,35.96,23.96,28.4,44.17,51.84,45.74,27.24,28.74,38.06,51.37,46.54,30.81,27.33,33.94,51.21,49.98,32.02,20.03,29.58,39.76,46.28,29.22,17.77,19.81,34.27,42.67,28.29,10.49,8.33,22.9,34.95,27.62,11.53,1.52,13.01,22.6,25.95,10.33,-4.54,2.72,13.26,21.95,6.89,-5.05,-6.25,7.93,17.79,9.5,-6.48,-10.38,3.29,15.64,13.08,-2.77,-11.89,-1.33,12.85,15.24,0.93,-13.02,-4.69,6.47,17.24,4.13,-7.46,-12.47,7.5,15.02,5.87,-6.25,-16.95,-4.89,10.73,7.33,-9.48,-21.24,-11.67,4.12,6.4,-13.81,-20.76,-20.41,-2.4,3.78,-11.96,-23.63,-30.82,-14.19,-5.62,-9.71,-28.68,-34.78,-20.65,-7.15,-10.78,-20.95,-31.76,-25.4,-10.48,-6.4,-18.09,-27.57,-27.9,-13.22,1.32,-8.11,-21.19,-22.68,-9.08,6.85,2.81,-11.96,-16.38,-4.06,13.71,16.64,3.07,-5.64,3.75,21.75,26.88,19.29,4.23,10.32,29.4,38.49,35.55,18.7,16.79,31.6,46.61,40.39,31.19,20.4,31.11,50.06,48.38,38.11,25.58,31,47.13,49.54,42.52,30.23,24.61,42.01,48.26,42.89,24.64,20.86,29.16,41.43,37.93,24.29,13.26,24.15,33.3,37.41,18.17,8.08,7.24,26.91,29.37,15.96,1.45,1.83,12.38,24.16,14.82,0.21,-7.97,4.25,16.69,13.54,-2.56,-13.16,-5.92,8.83,11.5,-3.46,-18.21,-14.94,0.64,6.62,-3.91,-19.91,-20.41,-6.22,0.97,-5.69,-17.87,-24.14,-16.62,-5.86,-7.29,-20.02,-33.09,-26.28,-12.83,-7.23,-21.42,-32.91,-32.76,-20.73,-9.9,-24.34,-33.07,-42.86,-24.86,-15.65,-20.86,-33.28,-43.96,-28.74,-17.34,-15.95,-31.16,-42.19,-33.32,-19.19,-10.94,-23.29,-35.95,-33.93,-19.13,-5.13,-15.35,-27.02,-26.99,-10.91,2.64,-0.39,-11.9,-17.66,-5.94,12.01,14.64,1.93,-5.07,2.24,19.54,27.64,19.01,6.41,10.21,27.39,39.16,35.11,21.33,17.01,32.81,47.02,40.54,29.57,20.61,32.49,48.28,50.28,36.57,23.89,28.11,47.26,54.58,39.48,26.66,24.88,34.75,46.43,41.24,18.92,13.04,23.79,37.17,34.47,19.36,5,15.69,25.26,27.56,14.82,-0.85,-1.71,13.55,20.11,9.61,-5.8,-8.05,4.01,12.02,3.24,-10.21,-19.12,-9.68,5.84,3.07,-14.12,-23.13,-15.6,-0.4,1.07,-11.72,-24.28,-22.14,-7,1.83,-6.89,-22.95,-26.26,-12.5,2.37,-6.07,-20.95,-29.71,-17.07,1.16,0.02,-17.23,-24.11,-16.74,-6.06,-2.06,-11.03,-24.79,-23.19,-13.16,-2.35,-13.22,-29.63,-31.95,-17.23,-8.38,-6.47,-29.42,-30.31,-26.14,-9.51,-11.14,-21.41,-35.49,-26.82,-15.34,-7.2,-17.36,-33.13,-34.08,-16.02,-9.73,-14.68,-34.13,-35.52,-19.94,-4.64,-10.55,-24.72,-31.29,-20.14,-4.09,1.32,-13.16,-22.79,-15.99,1.24,8.78,-0.84,-12.83,-11.04,5.98,16.65,12.38,-1.18,-3.95,9.32,22.17,26.38,11.21,1.76,13.89,26.9,32.35,15.44,8.16,15.57,30.13,37.5,30.21,10.05,14.72,29.16,40.18,35.18,15.08,7.36,19.32,34.81,32.54,14.65,7.49,16.7,26.42,33.87,20.23,1.03,8.03,23.11,28,16,3.23,-4.76,13.49,21.72,12.64,-0.08,-11.61,1.41,17.31,12.94,-1.01,-14.02,-6.64,8.01,12.77,0.12,-14.85,-12.86,1.85,10.09,-0.62,-16.57,-18.59,-5.89,4.81,1.05,-14.66,-24.05,-13.46,2.92,1.7,-14.94,-30.54,-21.41,-6.93,-1.48,-14.24,-29.79,-31.52,-16.47,-5.97,-13.47,-30.26,-38.91,-24,-14.87,-18.88,-35.87,-42.05,-39.78,-21.39,-19.44,-34.89,-51.84,-43.4,-32.5,-25.26,-33.76,-51.07,-51.13,-33.62,-24.96,-34.11,-49.11,-51.87,-38.17,-24.97,-27.08,-41.66,-48.34,-37.92,-20.67,-17.91,-27.87,-38.43,-32.09,-13.27,-5.06,-13.73,-24.62,-22.22,-5.43,7.72,4.45,-9.05,-12.79,2.18,18.53,20.93,6.16,-0.57,11.58,25.84</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B395" t="str">
+        <v>[R_22_标记]</v>
+      </c>
+      <c r="C395" t="str">
+        <v>幅值: 28.1uv 相位: 51.1°</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B396" t="str">
+        <v>[L_22_名字]</v>
+      </c>
+      <c r="C396" t="str">
+        <v>FERG(22)_lFlicker</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B397" t="str">
+        <v>[L_22_放大器]</v>
+      </c>
+      <c r="C397" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B398" t="str">
+        <v>[L_22_闪光]</v>
+      </c>
+      <c r="C398" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B399" t="str">
+        <v>[L_22_闪光背景]</v>
+      </c>
+      <c r="C399" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B400" t="str">
+        <v>[L_22_采样]</v>
+      </c>
+      <c r="C400" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B401" t="str">
+        <v>[L_22_分析时间]</v>
+      </c>
+      <c r="C401" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B402" t="str">
+        <v>[L_22_数据长度]</v>
+      </c>
+      <c r="C402" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B403" t="str">
+        <v>[L_22_详细数据(uv)]</v>
+      </c>
+      <c r="C403" t="str">
+        <v>28.12,40.75,37.85,36.93,29.63,25.34,31.62,40.91,37.76,35.45,28.29,32.23,35.67,45.32,41.45,38.38,31.29,28.43,39.57,42.41,42.16,35,28.42,28.42,32.15,40.87,39.66,29.77,19.59,24.57,28.39,30.63,26.69,18.51,13.58,14.03,17.19,21.07,16.89,7.15,0.18,0.17,6.67,8.81,3.41,-6.99,-12.7,-9.54,-5.57,-3.45,-9.06,-18.56,-22.16,-19.87,-14.85,-12.39,-15.12,-26.41,-29.61,-24.83,-13.79,-9.78,-17.38,-21.88,-29.03,-20.94,-12.85,-13.96,-15.09,-24.92,-24.19,-19.85,-8.4,-8.19,-9.58,-17.74,-19.25,-13.89,-1.34,4.05,-1.63,-5.7,-7.11,0.56,7.49,7.03,3.65,-3.62,-1.65,6.49,14.57,14.61,10.34,3.79,7.22,13.4,19.15,19.84,14.29,8.81,10.2,16.16,23.43,21.83,15.1,10.31,11.49,20.59,23.96,23.88,17.63,10.62,13.46,23.82,25.59,22.67,17.27,10.29,19.78,21.78,29.57,28.01,22.52,17.87,25.06,26.38,36.01,30.74,23.88,23.8,24.03,36.38,42.85,34.5,31.51,24.36,35.43,38.52,41.11,37.02,31.07,31.6,36.59,43.69,44.77,41.82,36.5,28.06,39.31,44.25,45.79,39.49,30.14,27.85,31.5,37.23,38.03,31.39,23.3,17.18,23.37,28.03,27.53,18.83,9.45,7.1,12.21,16.31,15.44,4.76,-2.15,-6.71,-2.62,3.78,1.37,-8.83,-15.33,-19.42,-10.73,-7.34,-14.12,-16.09,-25.19,-22.92,-20.14,-13.72,-16.97,-25.38,-29.58,-26.34,-23.82,-14.19,-21.93,-27.43,-29.55,-27.17,-20.71,-14.92,-13.55,-23.39,-23.37,-22.88,-12.6,-5.71,-4.66,-12.96,-15.47,-13.72,-3.63,1.73,2.79,-4.61,-6.06,-1.08,5.11,12.23,10.43,1.66,0.54,5.83,15.43,17.5,15.39,7.64,5.63,14.05,21.46,24.13,20.24,13.53,11.08,17.62,25.45,29.36,23.02,17.58,14.53,24.42,32.93,30.36,25.37,21.53,21.38,30.25,34.44,39.96,28.82,21.44,28.71,31.59,44.6,39.74,36.21,31.99,28.83,35.55,44.13,47.18,40.92,31.25,33.2,44.27,47.66,45.15,37.36,31.65,37.19,43.21,51.76,44.53,38.71,35.72,35.57,41.97,44.09,43.46,31.98,27.19,27.56,34.56,34.46,33.12,22.99,16.68,17.73,23.92,24.41,19.71,9.55,2.8,5.4,10.97,11.72,4.58,-5.53,-9.81,-7.02,-2.67,-3.77,-8.88,-16.34,-20.73,-16.73,-9.34,-12.15,-16.31,-29.51,-27.56,-25.57,-21.01,-14.17,-22.1,-27.34,-28.38,-28.29,-13.14,-10.98,-18.84,-27.5,-29.12,-16.01,-9.89,-8.48,-14.26,-21.69,-21.33,-9.88,-0.91,2.31,-3.11,-11.97,-10.1,-0.5,6.75,12.35,2.82,-1.47,0.73,10.4,19.53,16.58,12.38,5.72,9.65,17.25,25.96,21.91,16.49,12.51,14.76,24.18,28.24,25.44,19.55,15.11,17.58,25.41,31.16,29.11,20.09,14.87,18.3,25.24,33.23,30.83,19.01,16.08,20.29,34.87,33.99,31.29,24.25,21.15,23.96,31.9,36.7,34.23,22.96,23.49,29.38,38.48,41.9,34.11,25.09,30.01,33.99,40.99,40.26,37.73,30.66,31.46,39.82,44.78,44.19,39.53,34.15,27.58,33.06,41.3,40.32,35.69,28.01,25.36,30.89,39.03,36.68,27.44,21.21,21.55,24.31,29.67,25.93,17.4,9.36,9.06,14.51,17.5,14.25,6.47,-3.08,-2.76,3.67,7.68,3.18,-5.86,-14.6,-9.88,-7.15,-3.28,-7.8,-14.75,-23.3,-19.46,-14.02,-7.76,-9.91,-21.84,-25.75,-22.88,-11.61,-7.57,-10.94,-23.42,-26.25,-18.93,-10.9,-2.83,-11.58,-16.63,-20.2,-10.74,-3.68,-2.59,-5.43,-13.35,-10.06,-5.84,3.61,4.98,-0.25,-2.88,-3.32,2.62,13.55,13.58,7.24,0.47,3.59,10.76,16.99,18.39,14.49,6.06,6.26,15.4,22.13,23.38,16.28,10.84,10.81,19.29,26.21,26.24,19.95,13.1,13.99,25,30.85,28.49,20.48,18.57,18.4,26.18,37.05,35,25.29,23.39,23.78,37.45,40.54</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B404" t="str">
+        <v>[L_22_标记]</v>
+      </c>
+      <c r="C404" t="str">
+        <v>幅值: 27.6uv 相位: 50.6°</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B405" t="str">
+        <v>[R_23_名字]</v>
+      </c>
+      <c r="C405" t="str">
+        <v>FERG(23)_lCone</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B406" t="str">
+        <v>[R_23_放大器]</v>
+      </c>
+      <c r="C406" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B407" t="str">
+        <v>[R_23_闪光]</v>
+      </c>
+      <c r="C407" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B408" t="str">
+        <v>[R_23_闪光背景]</v>
+      </c>
+      <c r="C408" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B409" t="str">
+        <v>[R_23_采样]</v>
+      </c>
+      <c r="C409" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B410" t="str">
+        <v>[R_23_分析时间]</v>
+      </c>
+      <c r="C410" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B411" t="str">
+        <v>[R_23_数据长度]</v>
+      </c>
+      <c r="C411" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B412" t="str">
+        <v>[R_23_详细数据(uv)]</v>
+      </c>
+      <c r="C412" t="str">
+        <v>-6.11,14.14,15.67,-5.3,-7.8,12.49,14.69,-6.11,-9.07,11.28,14.16,-6.44,-9.83,10.56,14.14,-6.23,-10.05,10.37,14.63,-5.49,-9.74,10.68,15.62,-4.26,-8.95,11.44,17.03,-2.62,-7.78,12.55,18.76,-0.68,-6.32,13.88,20.67,1.43,-4.74,15.29,22.61,3.55,-3.19,16.62,24.44,5.52,-1.81,17.74,25.98,7.17,-0.78,18.45,27.07,8.43,-0.2,18.61,27.72,9.13,-0.24,18.33,27.49,8.94,-0.73,17.23,26.81,8.35,-2.21,15.24,25.26,6.25,-4.55,12.42,21.98,3.62,-8.61,9.28,19.3,0.68,-11.24,4.08,13.74,-3.59,-16.65,-2.32,11.87,-5.44,-22.65,-7.29,4.43,-12.33,-23.96,-13.82,0.18,-18.53,-31.87,-11.93,0.87,-16.37,-33.3,-17.43,-1.59,-24.98,-32.62,-20.4,-6.51,-15.3,-30.57,-20.48,-2.92,-14.54,-32.59,-15.02,5.44,-7.63,-17.91,-9.46,6.68,3.13,-10.99,3.22,21.85,8.63,1.33,14.52,30.61,23.84,9.06,26.36,45.68,38.05,22.34,38.24,57.41,45.27,35.3,52.92,74.03,58.91,52.91,59.24,88.78,78.24,53.17,68.17,91.9,78.29,72.52,76.72,114.81,111.19,89.11,93.5,120.73,114.68,107.77,92.98,117.47,127.62,112.3,104.21,132.61,112.55,95.33,116.87,156.6,122.84,98.16,128.31,161.49,142.19,128.79,121.81,161.29,124.84,111.79,118.4,145.69,121.04,122.22,113.08,134.29,122.74,119.3,121.74,157.34,118.71,122.47,120.55,124.81,142.33,108.32,114.97,137.13,130.08,84.66,115.05,111.64,127.82,95.53,86.59,116.63,102.86,96.3,94.33,108.99,103.14,84.46,76.21,90.61,94.96,67.92,63.63,85.77,94.5,57.3,66.41,74.31,67.47,49.51,44.15,67.03,67.38,47.45,39.8,61.65,60.84,42.65,38.45,56.45,56.03,31.56,32.33,53.96,51.35,27.99,24.81,46.68,41.52,20.77,15.52,34.55,41.27,16.3,12.29,30.5,33.39,13.36,6.02,26.55,30.38,7.77,3.28,21.47,24.51,3.01,-2.6,16.49,20.1,-0.48,-7.11,11.55,17.46,-3.5,-11.39,7.95,12.93,-6.48,-14.07,4.85,10.88,-9.48,-17.79,1.36,7.93,-12.09,-18.78,-0.86,7.78,-12.51,-20.18,-2.45,5.25,-12.68,-23.29,-3.53,5.84,-13.64,-21.43,-4.77,6.45,-12.16,-23.62,-4.63,5.85,-12.36,-23.19,-3.91,7.08,-9.17,-22.69,-4.5,5.96,-8.01,-20.18,-1.58,7.63,-7.36,-19.2,-1.95,8.77,-5.71,-21.9,0.14,11.16,-7.03,-19.45,-3.04,11.02,-7.51,-17.32,-1.08,10.39,-3.12,-22.87,-3.29,8.64,-9.06,-19.27,-9.41,8.11,-8.14,-19.86,-5.01,5.88,-5.25,-21.7,-8.33,-0.16,-12.78,-23.53,-17.78,1.69,-11.84,-30.6,-21.21,2.25,-16.99,-27.44,-16.28,-6.55,-21.27,-32.36,-23.56,-9.47,-20.41,-33.59,-30.94,-8.32,-23.94,-35.25,-32.74,-11.39,-25.48,-45.85,-24.92,-9.08,-23.02,-37.68,-30.42,-18.84,-20.36,-40.87,-33.35,-12.53,-27.92,-36.58,-31.65,-10.02,-24.37,-38.14,-33.42,-12.78,-15.95,-36.42,-31.11,-12.89,-21.02,-44.1,-25.23,-10.9,-23.05,-31.11,-30.8,-10.65,-11.25,-30.14,-20.84,-6.7,-9.87,-32.94,-22.48,-1.48,-11.07,-31.23,-19.5,-7.55,-8.55,-26.08,-25.44,-0.59,-8.19,-28.36,-17.78,-4,-1.67,-22.12,-24.66,-3.24,-3.54,-21.05,-24.99,2.76,-0.32,-28.61,-25.77,1.48,-1.84,-23.27,-21.99,-2.85,-1.96,-26.54,-24.7,-1.57,-3.9,-24.55,-24.31,-6.55,-4.24,-24.24,-24.9,-5.02,-7.52,-25.44,-27.43,-10.51,-5.82,-27.04,-29.88,-7.9,-9.95,-28.17,-27.23,-5.66,-5.89,-29.95,-26.56,-6.15,-6.53,-25.91,-26.55,-6.85,-4.6,-25.94,-27.66,-7.5,-5.22,-24.86,-24.88,-3.22,-1.67,-22.23,-24.77,-3.83,-0.02,-19.23,-22.79,0.17,4.59,-15.11,-21.03,1.68,7.41,-13.59,-18.25,2.63,8.48,-11.37,-15.58,5.19,11.73,-7.88,-14.97,6.09,13.11,-6.44,-13.39,6.17,14.3,-5.03,-11.9,6.83</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B413" t="str">
+        <v>[R_23_标记]</v>
+      </c>
+      <c r="C413" t="str">
+        <v>a: 54.9ms -27.1uv b: 114.1ms 64.2uv</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B414" t="str">
+        <v>[L_23_名字]</v>
+      </c>
+      <c r="C414" t="str">
+        <v>FERG(23)_lCone</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B415" t="str">
+        <v>[L_23_放大器]</v>
+      </c>
+      <c r="C415" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B416" t="str">
+        <v>[L_23_闪光]</v>
+      </c>
+      <c r="C416" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B417" t="str">
+        <v>[L_23_闪光背景]</v>
+      </c>
+      <c r="C417" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B418" t="str">
+        <v>[L_23_采样]</v>
+      </c>
+      <c r="C418" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B419" t="str">
+        <v>[L_23_分析时间]</v>
+      </c>
+      <c r="C419" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B420" t="str">
+        <v>[L_23_数据长度]</v>
+      </c>
+      <c r="C420" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B421" t="str">
+        <v>[L_23_详细数据(uv)]</v>
+      </c>
+      <c r="C421" t="str">
+        <v>-5.7,-7.94,-22.79,-25.28,-11.66,-5.91,-18.42,-28.15,-18.81,-6.89,-13.3,-27.36,-25.21,-10.82,-9.21,-23.35,-29.07,-16.66,-7.55,-17.46,-29.33,-22.69,-8.87,-11.52,-25.91,-27.06,-12.74,-7.3,-19.78,-28.34,-17.87,-5.97,-12.68,-25.97,-22.5,-7.72,-6.55,-20.51,-25,-11.85,-3.08,-13.32,-24.48,-16.8,-3.23,-6.57,-20.63,-21.07,-6.44,-2.19,-15.23,-23.24,-12.26,-0.95,-9.36,-22.36,-18.85,-4.24,-4.45,-20.38,-24.8,-12.25,-4.84,-16.81,-26.71,-19.99,-7.16,-13.16,-29.41,-28.66,-18.67,-16.51,-29.47,-39.69,-27.62,-20.34,-25.35,-42.21,-38.23,-20.39,-27.61,-40.44,-44.97,-34.17,-28.51,-38.32,-45.15,-36.58,-23.15,-34.6,-44.37,-44.49,-26.43,-22.21,-38.58,-39.57,-28.23,-13.61,-22.78,-36.9,-33.44,-8.29,-13.33,-26.74,-21.14,-8.93,-2.27,-6.91,-13.28,-9.52,7.81,3.69,-3.78,5.79,17.77,23.46,19.97,7.04,28.99,38.16,39.43,22.46,37.07,50.06,51.42,46.05,34.16,64.66,70.83,65.9,57.16,72.42,88.01,66.26,80.02,76.08,92.35,106.89,91.16,93.84,83.86,111.8,89.97,97.19,95.68,127.63,98.12,99.24,107.65,129.77,117.3,119.4,113.8,106,125.89,137.62,95.4,119.47,120.67,129.78,123.23,125.22,129.45,124.49,126.81,118.17,128.04,127.12,114.94,91.88,84.47,104.78,100.62,112.12,87.35,92.52,90.95,107.61,71.89,75.43,77.96,84.77,68.23,70.17,87.92,85.37,62.64,45.14,64.26,69.74,67.74,49.74,50.71,54.86,45.96,37.2,23.03,34.53,45.39,35.15,12.62,21.27,35.5,27.86,17.69,8.72,20.55,24.93,8.97,4.96,11.37,16.43,10.07,-0.23,-1.79,14.29,12.22,-0.5,-7.25,3.34,10.55,1.7,-11.34,-7.41,7.79,5.39,-9.99,-11.38,0.4,7.02,-5.8,-15.88,-6.82,3.99,-2.14,-15.98,-13.37,0.23,1.33,-13.95,-18.83,-5.99,1.93,-8.8,-21.04,-14.11,-1.49,-5.28,-18.95,-20.76,-6.33,-3.08,-16.46,-24.2,-13.77,-3.03,-11.3,-25.64,-21.47,-8.06,-7.96,-23.02,-27.65,-15.98,-7.26,-19.24,-32.2,-25.4,-9.96,-16.48,-30.83,-30.21,-18.11,-13.81,-27.87,-34.6,-25.89,-15,-21.53,-34.59,-30.17,-17.32,-17.63,-33.32,-38.11,-23.38,-16.39,-26.21,-37.97,-32.99,-15.7,-21.92,-36.75,-35.27,-20.05,-16.54,-33,-36.42,-27.25,-17.75,-28.71,-35.56,-30.74,-15.59,-20.97,-36.16,-36.72,-25.91,-13.76,-31.38,-37.46,-25.29,-14.83,-24.99,-38.54,-37.79,-18.52,-18.25,-32.46,-40.24,-24.67,-14.64,-28.01,-34.59,-33.08,-13.15,-18.33,-32.54,-38.82,-25.25,-21.52,-27.55,-40.53,-33.18,-19.27,-26.06,-39.58,-33.37,-18.24,-26.47,-38.49,-46.15,-35.1,-23.31,-32.37,-49.95,-37.27,-23.99,-28.96,-49.05,-48.68,-35.52,-21.58,-43.92,-44.43,-38.18,-26.48,-40.27,-46.38,-50.2,-37.45,-31.32,-50.34,-49.85,-42.57,-32.8,-46.51,-48.65,-47.58,-25.9,-33.58,-54.61,-44.79,-39.48,-29.41,-49.28,-49.69,-34.97,-32.51,-34.41,-49.38,-41.73,-30.62,-27.79,-44.12,-43.52,-36.18,-22.21,-39.16,-49.91,-39.03,-28.97,-30.29,-39.98,-40.19,-22.1,-25.04,-33.55,-44.08,-33.81,-17.69,-28.79,-40.62,-34.39,-20.86,-22.24,-31.19,-37.78,-20.84,-19.03,-26.13,-36.15,-30.66,-17.55,-19.71,-33.32,-30.67,-17.37,-13.43,-29.73,-32.66,-22.49,-13.81,-20.39,-31.35,-29.06,-15.21,-16.31,-30.54,-33.99,-18.2,-14.27,-22.96,-32.55,-25.69,-14.78,-18.2,-34.1,-32.85,-15.84,-13.69,-29.25,-35.87,-22.19,-13.58,-25.33,-33.51,-27.14,-15.85,-18.48,-34.12,-33.22,-18.65,-14.9,-28.68,-36.52,-24.35,-13.06,-19.76,-33.57,-32.22,-16.72,-16.71,-29.06,-35.29,-20.76,-13.5,-22.31,-34.73,-25.74,-12.91,-16.16,-29.52,-29.82,-13.89,-9.67,-22.96,-31.1,-18.72,-7.1,-14.57,-27.4,-22.43,-8.52,-7.87,-21.6,-25.03,-11.89,-4.04,-14.91,-24.79,-16.35,-2.96,-7.35,-21.95,-20.28,-6.41,-2.82,-15.53,-22.32</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B422" t="str">
+        <v>[L_23_标记]</v>
+      </c>
+      <c r="C422" t="str">
+        <v>a: 54.9ms -32.2uv b: 114.2ms 146.6uv</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B423" t="str">
+        <v>[R_24_名字]</v>
+      </c>
+      <c r="C423" t="str">
+        <v>FERG(24)_lFlicker</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B424" t="str">
+        <v>[R_24_放大器]</v>
+      </c>
+      <c r="C424" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B425" t="str">
+        <v>[R_24_闪光]</v>
+      </c>
+      <c r="C425" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B426" t="str">
+        <v>[R_24_闪光背景]</v>
+      </c>
+      <c r="C426" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B427" t="str">
+        <v>[R_24_采样]</v>
+      </c>
+      <c r="C427" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B428" t="str">
+        <v>[R_24_分析时间]</v>
+      </c>
+      <c r="C428" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B429" t="str">
+        <v>[R_24_数据长度]</v>
+      </c>
+      <c r="C429" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B430" t="str">
+        <v>[R_24_详细数据(uv)]</v>
+      </c>
+      <c r="C430" t="str">
+        <v>8.55,23.02,16.39,8.87,20.04,20.44,5.55,14.53,21.74,2.1,7.94,19.75,5.87,3.3,17.72,7.22,-3.48,15.38,12.09,-1.2,9.98,16.76,0.79,4.1,17.02,2.92,1.55,14.5,6.44,-2.99,11.57,10.83,-4.88,5.92,12.73,-3.36,-0.42,10.79,-3.89,-6.26,8.89,-2.77,-11.3,2.66,1.13,-14.31,-5.3,-3.65,-21.43,-11.49,-3.44,-19.74,-20.93,-8.21,-19.43,-33.34,-17.12,-20.24,-37.16,-26.41,-19,-35.82,-31.7,-21.63,-41.46,-41.37,-24.12,-37.67,-47.04,-29.45,-34.41,-48.68,-35.52,-29.31,-44.71,-35.75,-26.39,-34.25,-34.97,-21.96,-30.87,-39.28,-22.26,-21.25,-33.88,-20.63,-12.27,-27.36,-18.79,-4.21,-16.46,-15.74,1.49,-5.54,-10.86,5.19,6.29,-4.08,7.67,14.96,3.48,11.75,22.7,12.2,11.16,28.31,23.58,14.87,26.26,27.2,15.48,28.53,30.94,22.72,30.58,38.16,25.39,25.36,39.62,27.25,19.96,32.21,29.2,18.95,27.07,36.06,15.53,22.9,35.2,18.09,20.37,28.7,21.13,14.02,27.04,29.77,10.71,24.7,26.21,11.4,18.32,26.05,10.75,9.3,24.63,12.27,6.6,19.88,16.79,3.46,12.64,18.31,1.68,6.98,17.56,2.23,-0.08,14.77,3.12,-4.8,8.52,3.43,-6.92,2.89,6.82,-13.23,-9.09,2.92,-11.29,-13.65,-0.22,-12.9,-21.9,-8.92,-9.41,-24.6,-19.66,-15.61,-32.42,-26.98,-13.86,-31.53,-30.75,-21.62,-30.15,-36.17,-26.93,-25.2,-44.77,-26.7,-27.34,-37.56,-37.19,-23.8,-35.96,-37.38,-22.86,-30.02,-37.58,-23,-24.8,-36.54,-19.2,-14.46,-31.95,-18.94,-12.43,-22.98,-20.76,-3.15,-9.21,-15.97,0.16,-0.69,-10.2,3.37,10.49,-3,6.75,19,7.69,8.48,25.5,18.72,11.62,27.59,26.86,16.72,30.47,35.58,20.97,25.76,36.81,29.58,27.22,42.25,28.9,22.14,42.69,39.59,24.16,33.77,36.06,20.98,28.81,42.03,21.73,25.58,36.79,27.01,15.5,28.38,24.89,11.88,23.04,25.26,10.13,17.69,25.17,12.22,11.52,29.36,16.07,4.9,19.66,14.23,2.31,15.17,19.97,2.25,11.72,18.33,4.11,4.83,18.64,10.55,1.38,16.5,13.03,0.12,13.08,16.23,-0.09,6.78,16.56,1.52,0.43,15.84,4.99,-0.28,10.94,6.41,-3.95,2.22,7.8,-5.81,-3.81,5.62,-7.43,-10.6,3.4,-6.86,-16.3,-2.46,-9.22,-19.89,-13.6,-10.9,-23.37,-17.75,-13.95,-27.66,-26.89,-14.13,-21.4,-31.77,-19.22,-22.13,-35.48,-22.94,-16.2,-37.76,-22.97,-16.7,-28.9,-28.33,-11.69,-25.5,-29.39,-13.5,-15.11,-23.76,-11.41,-5.22,-20.13,-10.07,1.74,-11.23,-8.61,5.72,-2.35,-7.56,9.6,7.84,-1.75,13.34,17.73,4.39,14.26,25.88,14.94,15.92,30.29,21.43,19.55,31.64,28.88,21.31,31.03,35.4,20.16,29.21,38.65,29.08,29.21,39.93,33.43,26.63,38.66,38.95,20.08,34.83,37.85,25.37,27.17,36.64,24.11,30.33,38.82,26.03,18.55,36.63,32.8,16.85,32.39,33.13,18.36,29.73,39.12,17.35,19.91,31.08,22.89,18.58,32.03,25.28,15.73,28.38,29.43,13.99,22.32,29.77,14.05,15.18,28.23,16.25,10.49,24.63,17.89,6.28,18.14,20.45,2.57,9.33,17.21,3.81,5.54,16.05,1.18,-3.87,10.33,2.83,-12.83,0.8,1.94,-13.68,-7.82,-4.54,-19.57,-16.98,-8.88,-20.5,-30.11,-12.7,-21.65,-33.13,-23.01,-19.2,-36.07,-30.03,-20.32,-33.11,-34.13,-15.01,-31.2,-35.79,-18.15,-20.37,-38.08,-21.37,-21.73,-30.7,-19.67,-10.1,-26.62,-22.29,-4.5,-15.7,-18.5,-1.12,-4.4,-11.05,4.5,8.08,-5.48,6.32,18.18,5.98,10.61,25.51,16.96,14.29,32.21,28.62,17.89,35.27,35.92,25.67,34.71,45.9,29.87,36.05,47.22,40.34,31,49.21,45.89,33.78,49.08,51.83,35.57,44.34,50.42,37.08,35.65,50.18,35.2,30.87,46.83,40.96</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B431" t="str">
+        <v>[R_24_标记]</v>
+      </c>
+      <c r="C431" t="str">
+        <v>幅值: 26.1uv 相位: 50.9°</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B432" t="str">
+        <v>[L_24_名字]</v>
+      </c>
+      <c r="C432" t="str">
+        <v>FERG(24)_lFlicker</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B433" t="str">
+        <v>[L_24_放大器]</v>
+      </c>
+      <c r="C433" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B434" t="str">
+        <v>[L_24_闪光]</v>
+      </c>
+      <c r="C434" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B435" t="str">
+        <v>[L_24_闪光背景]</v>
+      </c>
+      <c r="C435" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B436" t="str">
+        <v>[L_24_采样]</v>
+      </c>
+      <c r="C436" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B437" t="str">
+        <v>[L_24_分析时间]</v>
+      </c>
+      <c r="C437" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B438" t="str">
+        <v>[L_24_数据长度]</v>
+      </c>
+      <c r="C438" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B439" t="str">
+        <v>[L_24_详细数据(uv)]</v>
+      </c>
+      <c r="C439" t="str">
+        <v>48.15,39.25,38.71,47.87,44.34,37.69,50.26,51.4,46.92,46.91,58.88,51.82,48.22,49.96,55.03,46.73,49.5,55.9,48.68,43.87,48.28,46.7,39.68,41.88,48.99,39.48,34.02,43.37,40.88,32.25,33.06,34.38,29.87,21.31,30.62,26.62,15.83,18.79,24.23,18.21,12.11,16.43,16.98,6.41,9.82,14.22,5.99,1.31,6.86,8.95,-0.91,3.38,7.49,1.85,-5.92,4.9,3.13,-4.64,0.18,3.01,-4.54,-6,1.85,0.58,-4.51,-2.57,2.16,-5.62,-5.33,-1.03,-2.78,-12.14,-6.85,0.54,-1.36,-4.82,-1.21,-1.7,-9.71,-2.08,-1.57,-5.38,-6.74,-2.8,-6.89,-13.64,-6.36,-3.11,-11.09,-10.98,-5.05,-5.29,-9.56,-4.45,0.12,-10.05,-8.36,0.22,-2.18,-8.17,-3.88,2.79,-4.18,-4.47,7.19,7.2,1.25,5.59,13.26,8.52,6.95,18.03,18.53,10.79,19.75,24.69,22.48,22.1,33.03,32.45,26.63,33.01,40.51,37.67,34.6,43.81,44.18,36.08,49.89,53.78,42.91,43.63,55.49,53.41,42.86,54.13,58.75,50.72,50.96,55.55,56.11,43.35,50.8,54.64,48.83,44.61,49.24,43.87,35.85,42.52,41.12,32.86,33.04,36.86,34.18,22.48,29.44,28.47,17.89,18.41,25.58,17.38,9.59,16.48,15.44,5.63,4.28,12.43,5.87,-2.84,2.8,4.36,-4.24,-4.04,1.38,-4.58,-8.22,-4.33,-1.73,-10.33,-10.11,-3.21,-8.38,-14.65,-6.72,-6.92,-11.82,-7.76,-3.24,-11.17,-14.07,-9.56,-3.04,-9.05,-10.83,-1.26,-4.27,-10.6,-2.22,-1.51,-9.92,-10.15,-1.34,-9.24,-14.14,-0.05,-6.25,-10.56,-6.51,-4.47,-9.89,-11.58,-0.84,-5.15,-12.59,-4.57,-1.95,-6.16,-12.53,-1.12,-0.43,-8.82,-3.75,2.37,-2.53,-6.36,3.4,4.13,-4.29,1.32,9.81,4.34,1.09,12.26,12.77,7.4,12.03,19.36,14.02,14.41,23.35,25.18,19.56,24.4,33.31,27.07,25.09,35.38,38.5,28.2,39.18,40.11,35.85,40.29,46.45,46.12,38.9,45.47,46.34,44.86,43.17,51.69,44.88,41.16,43.97,53.19,38.14,35.53,48.82,42.04,30.41,37.56,38.22,31.45,29.2,37.98,30.15,20.75,27.56,31.95,21.95,19.11,24.06,18.81,13.01,13.38,16.61,9.92,4.31,11.69,7.02,-0.47,4.64,5.9,-2.72,-1.78,5.21,-1.66,-8.01,-2.29,0.87,-7.09,-8.47,-2.19,-6.2,-12.5,-5.39,-2.02,-9.03,-9.42,0.02,-6.05,-15.48,-2.7,-5.08,-9.31,-9.07,-2.97,-6.5,-15.66,-6.1,0.42,-9.33,-12.68,-1.24,-9.58,-12.13,-4.57,-4.27,-13.97,-11.43,-3.05,-10.91,-12.42,-12.29,-5.81,-16.56,-16.52,-4.65,-13.19,-17.45,-10.22,-5.38,-15.99,-15.11,-5.66,-10.08,-15.16,-8.94,-5.08,-14.74,-9.97,-0.79,-7.01,-11.03,-2.42,0.05,-5.76,-1.53,8,1.46,0.33,10.74,12.95,7.84,10.96,20.93,16.74,15.28,25.76,29.7,22.96,26.45,32.96,27.5,25.99,37,40.97,35.75,36.64,42.67,35.07,34.42,44.77,43.74,35.31,42.19,50.6,48.04,38.45,47.44,43.17,33.29,38.15,43.5,38.51,35.92,37.82,38.85,31.04,30.2,34.76,28.27,23.48,29.07,24.9,14.86,18.95,22.1,13.2,9.69,13.59,12.67,1.54,4.23,11.03,1.7,-2.37,4.55,-1.23,-10.6,-4.02,-2.04,-12.04,-13.71,-3.65,-5.63,-14.56,-10.52,-7.5,-14.34,-18.41,-7.68,-12.51,-16.87,-12.45,-8.88,-19.9,-21.67,-8.7,-14.52,-18.04,-13.33,-9.73,-16.77,-17.46,-9.98,-11.3,-22.06,-12.94,-13.86,-17.92,-20.68,-11.15,-15.98,-23.37,-10.15,-11.66,-16.29,-18.97,-8.39,-15.98,-21.62,-15.95,-10.11,-18.93,-18.79,-10.5,-11.35,-18.42,-11.03,-8.34,-15.89,-13.7,-4.19,-8.18,-11.12,-4.92,-1.68,-7.75,-3.76,3.38,2.75,-1.77,5.23,9.18,3.83,7.45,15.75,11.95,9.76,19.21,22.74,18.52,20.11,29.09,25.44,22.21,31.93,37.69</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B440" t="str">
+        <v>[L_24_标记]</v>
+      </c>
+      <c r="C440" t="str">
+        <v>幅值: 28.7uv 相位: 50.8°</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C440"/>
   </ignoredErrors>
 </worksheet>
 </file>